--- a/static/templates/commencement_template.xlsx
+++ b/static/templates/commencement_template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="12"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="환경설정" sheetId="1" state="visible" r:id="rId2"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
   <si>
     <t>사업명</t>
   </si>
@@ -145,7 +145,7 @@
     <t xml:space="preserve">(주) 매 그 나 텍</t>
   </si>
   <si>
-    <t xml:space="preserve">우:57241 전남 장성군 동화면 전자농공단지 2길 55</t>
+    <t xml:space="preserve">우:57241 전남광주 장성군 동화면 전자농공단지 2길 55</t>
   </si>
   <si>
     <t xml:space="preserve"> Tel 061)392-5508</t>
@@ -223,72 +223,75 @@
     <t>㈜매그나텍</t>
   </si>
   <si>
+    <t xml:space="preserve">전남광주 장성군 동화면 전자농공단지2길 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telephone : 061-392-5508  Fax : 061-392-5518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">착     수     계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">공    사    명  :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계 약   금 액  :</t>
+  </si>
+  <si>
+    <t>(</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:  부가세포함  )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">계 약  년월일 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">착 수  년월일 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">납 품  년월일 :</t>
+  </si>
+  <si>
+    <t xml:space="preserve">상기 용역에 대해 위와 같이 착수하였기에 착수계를 제출합니다.</t>
+  </si>
+  <si>
+    <t>붙임.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. 사업자등록증</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. 국세, 지방세 납세증명서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. 공장등록증명서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. 직접생산확인증명서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. 현장대리인계</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. 재직증명서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7. 물품계약서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8. 예정공정표</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9. 납품내역서</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10. 제작도면</t>
+  </si>
+  <si>
     <t xml:space="preserve">전남 장성군 동화면 전자농공단지2길 55</t>
   </si>
   <si>
-    <t xml:space="preserve">Telephone : 061-392-5508  Fax : 061-392-5518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">착     수     계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">공    사    명  :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">계 약   금 액  :</t>
-  </si>
-  <si>
-    <t>(</t>
-  </si>
-  <si>
-    <t xml:space="preserve">:  부가세포함  )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">계 약  년월일 :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">착 수  년월일 :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">납 품  년월일 :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">상기 용역에 대해 위와 같이 착수하였기에 착수계를 제출합니다.</t>
-  </si>
-  <si>
-    <t>붙임.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. 사업자등록증</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. 국세, 지방세 납세증명서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. 공장등록증명서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. 직접생산확인증명서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5. 현장대리인계</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6. 재직증명서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7. 물품계약서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8. 예정공정표</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9. 납품내역서</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10. 제작도면</t>
-  </si>
-  <si>
     <t xml:space="preserve">㈜ 매그나텍</t>
   </si>
   <si>
@@ -334,7 +337,7 @@
     <t xml:space="preserve">차 장</t>
   </si>
   <si>
-    <t xml:space="preserve">광주광역시 광산구 사암로215번길 16</t>
+    <t xml:space="preserve">전남광주 광산구 사암로215번길 16</t>
   </si>
   <si>
     <t xml:space="preserve">주             소   :</t>
@@ -349,16 +352,22 @@
     <t xml:space="preserve">대 리</t>
   </si>
   <si>
-    <t xml:space="preserve">광주광역시 광산구 수등로 287</t>
+    <t xml:space="preserve">전남광주 광산구 수등로 287</t>
   </si>
   <si>
     <t xml:space="preserve">생  년   월  일   :</t>
   </si>
   <si>
-    <t xml:space="preserve">최  한  진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광주광역시 광산구 신창동 1285</t>
+    <t>문정훈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">문  정  훈</t>
+  </si>
+  <si>
+    <t xml:space="preserve">주 임</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전남광주 광산구 신창로48번길 30-8</t>
   </si>
   <si>
     <t xml:space="preserve">재  직  증  명  서</t>
@@ -403,25 +412,10 @@
     <t xml:space="preserve">차 장</t>
   </si>
   <si>
-    <t xml:space="preserve">광주광역시 광산구 사암로215번길 16</t>
-  </si>
-  <si>
     <t>김선중</t>
   </si>
   <si>
     <t xml:space="preserve">김  선  중</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광주광역시 광산구 수등로 287</t>
-  </si>
-  <si>
-    <t>최한진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">최  한  진</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광주광역시 광산구 신창동 1285</t>
   </si>
   <si>
     <t xml:space="preserve">상기 위의 사실이 틀림 없음을 증명합니다.</t>
@@ -1643,7 +1637,7 @@
     <numFmt numFmtId="176" formatCode="yyyy&quot;년&quot;\ mm&quot;월&quot;\ dd&quot;일&quot;;@"/>
     <numFmt numFmtId="177" formatCode="_-&quot;₩&quot;* #,##0.0_-;\-&quot;₩&quot;* #,##0.0_-;_-&quot;₩&quot;* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="45">
+  <fonts count="46">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -1797,6 +1791,10 @@
       <name val="맑은 고딕"/>
     </font>
     <font>
+      <sz val="10.500000"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
       <b/>
       <sz val="13.000000"/>
       <name val="맑은 고딕"/>
@@ -1843,8 +1841,9 @@
       <name val="맑은 고딕"/>
     </font>
     <font>
-      <sz val="10.500000"/>
-      <name val="맑은 고딕"/>
+      <sz val="9.000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12.000000"/>
@@ -2425,7 +2424,7 @@
     <xf fontId="10" fillId="4" borderId="3" numFmtId="173" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="17" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="126">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2691,39 +2690,42 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="6" vertical="center"/>
+    </xf>
+    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" indent="2" vertical="distributed"/>
     </xf>
-    <xf fontId="33" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf fontId="26" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" indent="2" vertical="distributed"/>
     </xf>
-    <xf fontId="34" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf fontId="35" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="35" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf fontId="36" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="36" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="37" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf fontId="38" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="38" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="39" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf fontId="39" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf fontId="40" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf fontId="40" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="41" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="42" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="29" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
@@ -2750,52 +2752,55 @@
     <xf fontId="29" fillId="2" borderId="27" numFmtId="0" xfId="50" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="28" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="28" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
     <xf fontId="22" fillId="0" borderId="24" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="24" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="24" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="29" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="29" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="30" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="30" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="3" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="3" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
     <xf fontId="22" fillId="0" borderId="3" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="31" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="31" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
     <xf fontId="22" fillId="0" borderId="30" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="32" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="32" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
     <xf fontId="22" fillId="0" borderId="33" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="33" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="33" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
-    <xf fontId="42" fillId="0" borderId="34" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf fontId="33" fillId="0" borderId="34" numFmtId="0" xfId="50" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1" vertical="center"/>
     </xf>
     <xf fontId="43" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
-    <xf fontId="35" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+    <xf fontId="44" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1" vertical="center"/>
     </xf>
-    <xf fontId="44" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf fontId="36" fillId="0" borderId="0" numFmtId="0" xfId="50" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" vertical="center"/>
+    </xf>
+    <xf fontId="45" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2919,15 +2924,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>95249</xdr:colOff>
+      <xdr:colOff>95248</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>38099</xdr:rowOff>
+      <xdr:rowOff>38098</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>838199</xdr:colOff>
+      <xdr:colOff>838198</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>142874</xdr:rowOff>
+      <xdr:rowOff>142873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3058,7 +3063,7 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>7039</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>224871</xdr:rowOff>
+      <xdr:rowOff>224868</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5590,6 +5595,12 @@
         <v>6039000</v>
       </c>
     </row>
+    <row r="15" ht="14.25">
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" ht="14.25">
+      <c r="C16" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:D1"/>
@@ -5603,13 +5614,13 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{009D005B-0064-41C7-AB9E-005200660045}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{008A003F-00ED-4AEA-844F-000D0039002A}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$K$1:$K$2</xm:f>
           </x14:formula1>
           <xm:sqref>D7</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{004100CB-0037-4385-AF7F-003400230005}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
+        <x14:dataValidation xr:uid="{00040091-0066-4834-9267-00FB00B8008E}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="1" showInputMessage="1">
           <x14:formula1>
             <xm:f>$J$1:$J$2</xm:f>
           </x14:formula1>
@@ -5625,15 +5636,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="92" width="10.625"/>
-    <col customWidth="1" min="2" max="2" style="92" width="7.25"/>
-    <col customWidth="1" min="3" max="3" style="92" width="10.75"/>
-    <col customWidth="1" min="4" max="4" style="92" width="8.75"/>
-    <col customWidth="1" min="5" max="5" style="92" width="18.25"/>
-    <col customWidth="1" min="6" max="6" style="92" width="1.625"/>
-    <col customWidth="1" min="7" max="7" style="92" width="14.75"/>
-    <col customWidth="1" min="8" max="8" style="92" width="19.25"/>
-    <col min="9" max="16384" style="92" width="9"/>
+    <col customWidth="1" min="1" max="1" style="93" width="10.625"/>
+    <col customWidth="1" min="2" max="2" style="93" width="7.25"/>
+    <col customWidth="1" min="3" max="3" style="93" width="10.75"/>
+    <col customWidth="1" min="4" max="4" style="93" width="8.75"/>
+    <col customWidth="1" min="5" max="5" style="93" width="18.25"/>
+    <col customWidth="1" min="6" max="6" style="93" width="1.625"/>
+    <col customWidth="1" min="7" max="7" style="93" width="14.75"/>
+    <col customWidth="1" min="8" max="8" style="93" width="19.25"/>
+    <col min="9" max="16384" style="93" width="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5" customHeight="1"/>
@@ -5678,604 +5689,604 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="93" width="5.125"/>
-    <col customWidth="1" min="2" max="9" style="93" width="9.625"/>
-    <col customWidth="1" min="10" max="10" style="93" width="5.125"/>
-    <col min="11" max="12" style="93" width="9"/>
-    <col customWidth="1" min="13" max="13" style="93" width="22.75"/>
-    <col customWidth="1" min="14" max="20" style="93" width="13.625"/>
-    <col min="21" max="256" style="93" width="9"/>
-    <col customWidth="1" min="257" max="257" style="93" width="5.125"/>
-    <col customWidth="1" min="258" max="265" style="93" width="9.625"/>
-    <col customWidth="1" min="266" max="266" style="93" width="5.125"/>
-    <col min="267" max="268" style="93" width="9"/>
-    <col customWidth="1" min="269" max="269" style="93" width="22.75"/>
-    <col customWidth="1" min="270" max="276" style="93" width="13.625"/>
-    <col min="277" max="512" style="93" width="9"/>
-    <col customWidth="1" min="513" max="513" style="93" width="5.125"/>
-    <col customWidth="1" min="514" max="521" style="93" width="9.625"/>
-    <col customWidth="1" min="522" max="522" style="93" width="5.125"/>
-    <col min="523" max="524" style="93" width="9"/>
-    <col customWidth="1" min="525" max="525" style="93" width="22.75"/>
-    <col customWidth="1" min="526" max="532" style="93" width="13.625"/>
-    <col min="533" max="768" style="93" width="9"/>
-    <col customWidth="1" min="769" max="769" style="93" width="5.125"/>
-    <col customWidth="1" min="770" max="777" style="93" width="9.625"/>
-    <col customWidth="1" min="778" max="778" style="93" width="5.125"/>
-    <col min="779" max="780" style="93" width="9"/>
-    <col customWidth="1" min="781" max="781" style="93" width="22.75"/>
-    <col customWidth="1" min="782" max="788" style="93" width="13.625"/>
-    <col min="789" max="1024" style="93" width="9"/>
-    <col customWidth="1" min="1025" max="1025" style="93" width="5.125"/>
-    <col customWidth="1" min="1026" max="1033" style="93" width="9.625"/>
-    <col customWidth="1" min="1034" max="1034" style="93" width="5.125"/>
-    <col min="1035" max="1036" style="93" width="9"/>
-    <col customWidth="1" min="1037" max="1037" style="93" width="22.75"/>
-    <col customWidth="1" min="1038" max="1044" style="93" width="13.625"/>
-    <col min="1045" max="1280" style="93" width="9"/>
-    <col customWidth="1" min="1281" max="1281" style="93" width="5.125"/>
-    <col customWidth="1" min="1282" max="1289" style="93" width="9.625"/>
-    <col customWidth="1" min="1290" max="1290" style="93" width="5.125"/>
-    <col min="1291" max="1292" style="93" width="9"/>
-    <col customWidth="1" min="1293" max="1293" style="93" width="22.75"/>
-    <col customWidth="1" min="1294" max="1300" style="93" width="13.625"/>
-    <col min="1301" max="1536" style="93" width="9"/>
-    <col customWidth="1" min="1537" max="1537" style="93" width="5.125"/>
-    <col customWidth="1" min="1538" max="1545" style="93" width="9.625"/>
-    <col customWidth="1" min="1546" max="1546" style="93" width="5.125"/>
-    <col min="1547" max="1548" style="93" width="9"/>
-    <col customWidth="1" min="1549" max="1549" style="93" width="22.75"/>
-    <col customWidth="1" min="1550" max="1556" style="93" width="13.625"/>
-    <col min="1557" max="1792" style="93" width="9"/>
-    <col customWidth="1" min="1793" max="1793" style="93" width="5.125"/>
-    <col customWidth="1" min="1794" max="1801" style="93" width="9.625"/>
-    <col customWidth="1" min="1802" max="1802" style="93" width="5.125"/>
-    <col min="1803" max="1804" style="93" width="9"/>
-    <col customWidth="1" min="1805" max="1805" style="93" width="22.75"/>
-    <col customWidth="1" min="1806" max="1812" style="93" width="13.625"/>
-    <col min="1813" max="2048" style="93" width="9"/>
-    <col customWidth="1" min="2049" max="2049" style="93" width="5.125"/>
-    <col customWidth="1" min="2050" max="2057" style="93" width="9.625"/>
-    <col customWidth="1" min="2058" max="2058" style="93" width="5.125"/>
-    <col min="2059" max="2060" style="93" width="9"/>
-    <col customWidth="1" min="2061" max="2061" style="93" width="22.75"/>
-    <col customWidth="1" min="2062" max="2068" style="93" width="13.625"/>
-    <col min="2069" max="2304" style="93" width="9"/>
-    <col customWidth="1" min="2305" max="2305" style="93" width="5.125"/>
-    <col customWidth="1" min="2306" max="2313" style="93" width="9.625"/>
-    <col customWidth="1" min="2314" max="2314" style="93" width="5.125"/>
-    <col min="2315" max="2316" style="93" width="9"/>
-    <col customWidth="1" min="2317" max="2317" style="93" width="22.75"/>
-    <col customWidth="1" min="2318" max="2324" style="93" width="13.625"/>
-    <col min="2325" max="2560" style="93" width="9"/>
-    <col customWidth="1" min="2561" max="2561" style="93" width="5.125"/>
-    <col customWidth="1" min="2562" max="2569" style="93" width="9.625"/>
-    <col customWidth="1" min="2570" max="2570" style="93" width="5.125"/>
-    <col min="2571" max="2572" style="93" width="9"/>
-    <col customWidth="1" min="2573" max="2573" style="93" width="22.75"/>
-    <col customWidth="1" min="2574" max="2580" style="93" width="13.625"/>
-    <col min="2581" max="2816" style="93" width="9"/>
-    <col customWidth="1" min="2817" max="2817" style="93" width="5.125"/>
-    <col customWidth="1" min="2818" max="2825" style="93" width="9.625"/>
-    <col customWidth="1" min="2826" max="2826" style="93" width="5.125"/>
-    <col min="2827" max="2828" style="93" width="9"/>
-    <col customWidth="1" min="2829" max="2829" style="93" width="22.75"/>
-    <col customWidth="1" min="2830" max="2836" style="93" width="13.625"/>
-    <col min="2837" max="3072" style="93" width="9"/>
-    <col customWidth="1" min="3073" max="3073" style="93" width="5.125"/>
-    <col customWidth="1" min="3074" max="3081" style="93" width="9.625"/>
-    <col customWidth="1" min="3082" max="3082" style="93" width="5.125"/>
-    <col min="3083" max="3084" style="93" width="9"/>
-    <col customWidth="1" min="3085" max="3085" style="93" width="22.75"/>
-    <col customWidth="1" min="3086" max="3092" style="93" width="13.625"/>
-    <col min="3093" max="3328" style="93" width="9"/>
-    <col customWidth="1" min="3329" max="3329" style="93" width="5.125"/>
-    <col customWidth="1" min="3330" max="3337" style="93" width="9.625"/>
-    <col customWidth="1" min="3338" max="3338" style="93" width="5.125"/>
-    <col min="3339" max="3340" style="93" width="9"/>
-    <col customWidth="1" min="3341" max="3341" style="93" width="22.75"/>
-    <col customWidth="1" min="3342" max="3348" style="93" width="13.625"/>
-    <col min="3349" max="3584" style="93" width="9"/>
-    <col customWidth="1" min="3585" max="3585" style="93" width="5.125"/>
-    <col customWidth="1" min="3586" max="3593" style="93" width="9.625"/>
-    <col customWidth="1" min="3594" max="3594" style="93" width="5.125"/>
-    <col min="3595" max="3596" style="93" width="9"/>
-    <col customWidth="1" min="3597" max="3597" style="93" width="22.75"/>
-    <col customWidth="1" min="3598" max="3604" style="93" width="13.625"/>
-    <col min="3605" max="3840" style="93" width="9"/>
-    <col customWidth="1" min="3841" max="3841" style="93" width="5.125"/>
-    <col customWidth="1" min="3842" max="3849" style="93" width="9.625"/>
-    <col customWidth="1" min="3850" max="3850" style="93" width="5.125"/>
-    <col min="3851" max="3852" style="93" width="9"/>
-    <col customWidth="1" min="3853" max="3853" style="93" width="22.75"/>
-    <col customWidth="1" min="3854" max="3860" style="93" width="13.625"/>
-    <col min="3861" max="4096" style="93" width="9"/>
-    <col customWidth="1" min="4097" max="4097" style="93" width="5.125"/>
-    <col customWidth="1" min="4098" max="4105" style="93" width="9.625"/>
-    <col customWidth="1" min="4106" max="4106" style="93" width="5.125"/>
-    <col min="4107" max="4108" style="93" width="9"/>
-    <col customWidth="1" min="4109" max="4109" style="93" width="22.75"/>
-    <col customWidth="1" min="4110" max="4116" style="93" width="13.625"/>
-    <col min="4117" max="4352" style="93" width="9"/>
-    <col customWidth="1" min="4353" max="4353" style="93" width="5.125"/>
-    <col customWidth="1" min="4354" max="4361" style="93" width="9.625"/>
-    <col customWidth="1" min="4362" max="4362" style="93" width="5.125"/>
-    <col min="4363" max="4364" style="93" width="9"/>
-    <col customWidth="1" min="4365" max="4365" style="93" width="22.75"/>
-    <col customWidth="1" min="4366" max="4372" style="93" width="13.625"/>
-    <col min="4373" max="4608" style="93" width="9"/>
-    <col customWidth="1" min="4609" max="4609" style="93" width="5.125"/>
-    <col customWidth="1" min="4610" max="4617" style="93" width="9.625"/>
-    <col customWidth="1" min="4618" max="4618" style="93" width="5.125"/>
-    <col min="4619" max="4620" style="93" width="9"/>
-    <col customWidth="1" min="4621" max="4621" style="93" width="22.75"/>
-    <col customWidth="1" min="4622" max="4628" style="93" width="13.625"/>
-    <col min="4629" max="4864" style="93" width="9"/>
-    <col customWidth="1" min="4865" max="4865" style="93" width="5.125"/>
-    <col customWidth="1" min="4866" max="4873" style="93" width="9.625"/>
-    <col customWidth="1" min="4874" max="4874" style="93" width="5.125"/>
-    <col min="4875" max="4876" style="93" width="9"/>
-    <col customWidth="1" min="4877" max="4877" style="93" width="22.75"/>
-    <col customWidth="1" min="4878" max="4884" style="93" width="13.625"/>
-    <col min="4885" max="5120" style="93" width="9"/>
-    <col customWidth="1" min="5121" max="5121" style="93" width="5.125"/>
-    <col customWidth="1" min="5122" max="5129" style="93" width="9.625"/>
-    <col customWidth="1" min="5130" max="5130" style="93" width="5.125"/>
-    <col min="5131" max="5132" style="93" width="9"/>
-    <col customWidth="1" min="5133" max="5133" style="93" width="22.75"/>
-    <col customWidth="1" min="5134" max="5140" style="93" width="13.625"/>
-    <col min="5141" max="5376" style="93" width="9"/>
-    <col customWidth="1" min="5377" max="5377" style="93" width="5.125"/>
-    <col customWidth="1" min="5378" max="5385" style="93" width="9.625"/>
-    <col customWidth="1" min="5386" max="5386" style="93" width="5.125"/>
-    <col min="5387" max="5388" style="93" width="9"/>
-    <col customWidth="1" min="5389" max="5389" style="93" width="22.75"/>
-    <col customWidth="1" min="5390" max="5396" style="93" width="13.625"/>
-    <col min="5397" max="5632" style="93" width="9"/>
-    <col customWidth="1" min="5633" max="5633" style="93" width="5.125"/>
-    <col customWidth="1" min="5634" max="5641" style="93" width="9.625"/>
-    <col customWidth="1" min="5642" max="5642" style="93" width="5.125"/>
-    <col min="5643" max="5644" style="93" width="9"/>
-    <col customWidth="1" min="5645" max="5645" style="93" width="22.75"/>
-    <col customWidth="1" min="5646" max="5652" style="93" width="13.625"/>
-    <col min="5653" max="5888" style="93" width="9"/>
-    <col customWidth="1" min="5889" max="5889" style="93" width="5.125"/>
-    <col customWidth="1" min="5890" max="5897" style="93" width="9.625"/>
-    <col customWidth="1" min="5898" max="5898" style="93" width="5.125"/>
-    <col min="5899" max="5900" style="93" width="9"/>
-    <col customWidth="1" min="5901" max="5901" style="93" width="22.75"/>
-    <col customWidth="1" min="5902" max="5908" style="93" width="13.625"/>
-    <col min="5909" max="6144" style="93" width="9"/>
-    <col customWidth="1" min="6145" max="6145" style="93" width="5.125"/>
-    <col customWidth="1" min="6146" max="6153" style="93" width="9.625"/>
-    <col customWidth="1" min="6154" max="6154" style="93" width="5.125"/>
-    <col min="6155" max="6156" style="93" width="9"/>
-    <col customWidth="1" min="6157" max="6157" style="93" width="22.75"/>
-    <col customWidth="1" min="6158" max="6164" style="93" width="13.625"/>
-    <col min="6165" max="6400" style="93" width="9"/>
-    <col customWidth="1" min="6401" max="6401" style="93" width="5.125"/>
-    <col customWidth="1" min="6402" max="6409" style="93" width="9.625"/>
-    <col customWidth="1" min="6410" max="6410" style="93" width="5.125"/>
-    <col min="6411" max="6412" style="93" width="9"/>
-    <col customWidth="1" min="6413" max="6413" style="93" width="22.75"/>
-    <col customWidth="1" min="6414" max="6420" style="93" width="13.625"/>
-    <col min="6421" max="6656" style="93" width="9"/>
-    <col customWidth="1" min="6657" max="6657" style="93" width="5.125"/>
-    <col customWidth="1" min="6658" max="6665" style="93" width="9.625"/>
-    <col customWidth="1" min="6666" max="6666" style="93" width="5.125"/>
-    <col min="6667" max="6668" style="93" width="9"/>
-    <col customWidth="1" min="6669" max="6669" style="93" width="22.75"/>
-    <col customWidth="1" min="6670" max="6676" style="93" width="13.625"/>
-    <col min="6677" max="6912" style="93" width="9"/>
-    <col customWidth="1" min="6913" max="6913" style="93" width="5.125"/>
-    <col customWidth="1" min="6914" max="6921" style="93" width="9.625"/>
-    <col customWidth="1" min="6922" max="6922" style="93" width="5.125"/>
-    <col min="6923" max="6924" style="93" width="9"/>
-    <col customWidth="1" min="6925" max="6925" style="93" width="22.75"/>
-    <col customWidth="1" min="6926" max="6932" style="93" width="13.625"/>
-    <col min="6933" max="7168" style="93" width="9"/>
-    <col customWidth="1" min="7169" max="7169" style="93" width="5.125"/>
-    <col customWidth="1" min="7170" max="7177" style="93" width="9.625"/>
-    <col customWidth="1" min="7178" max="7178" style="93" width="5.125"/>
-    <col min="7179" max="7180" style="93" width="9"/>
-    <col customWidth="1" min="7181" max="7181" style="93" width="22.75"/>
-    <col customWidth="1" min="7182" max="7188" style="93" width="13.625"/>
-    <col min="7189" max="7424" style="93" width="9"/>
-    <col customWidth="1" min="7425" max="7425" style="93" width="5.125"/>
-    <col customWidth="1" min="7426" max="7433" style="93" width="9.625"/>
-    <col customWidth="1" min="7434" max="7434" style="93" width="5.125"/>
-    <col min="7435" max="7436" style="93" width="9"/>
-    <col customWidth="1" min="7437" max="7437" style="93" width="22.75"/>
-    <col customWidth="1" min="7438" max="7444" style="93" width="13.625"/>
-    <col min="7445" max="7680" style="93" width="9"/>
-    <col customWidth="1" min="7681" max="7681" style="93" width="5.125"/>
-    <col customWidth="1" min="7682" max="7689" style="93" width="9.625"/>
-    <col customWidth="1" min="7690" max="7690" style="93" width="5.125"/>
-    <col min="7691" max="7692" style="93" width="9"/>
-    <col customWidth="1" min="7693" max="7693" style="93" width="22.75"/>
-    <col customWidth="1" min="7694" max="7700" style="93" width="13.625"/>
-    <col min="7701" max="7936" style="93" width="9"/>
-    <col customWidth="1" min="7937" max="7937" style="93" width="5.125"/>
-    <col customWidth="1" min="7938" max="7945" style="93" width="9.625"/>
-    <col customWidth="1" min="7946" max="7946" style="93" width="5.125"/>
-    <col min="7947" max="7948" style="93" width="9"/>
-    <col customWidth="1" min="7949" max="7949" style="93" width="22.75"/>
-    <col customWidth="1" min="7950" max="7956" style="93" width="13.625"/>
-    <col min="7957" max="8192" style="93" width="9"/>
-    <col customWidth="1" min="8193" max="8193" style="93" width="5.125"/>
-    <col customWidth="1" min="8194" max="8201" style="93" width="9.625"/>
-    <col customWidth="1" min="8202" max="8202" style="93" width="5.125"/>
-    <col min="8203" max="8204" style="93" width="9"/>
-    <col customWidth="1" min="8205" max="8205" style="93" width="22.75"/>
-    <col customWidth="1" min="8206" max="8212" style="93" width="13.625"/>
-    <col min="8213" max="8448" style="93" width="9"/>
-    <col customWidth="1" min="8449" max="8449" style="93" width="5.125"/>
-    <col customWidth="1" min="8450" max="8457" style="93" width="9.625"/>
-    <col customWidth="1" min="8458" max="8458" style="93" width="5.125"/>
-    <col min="8459" max="8460" style="93" width="9"/>
-    <col customWidth="1" min="8461" max="8461" style="93" width="22.75"/>
-    <col customWidth="1" min="8462" max="8468" style="93" width="13.625"/>
-    <col min="8469" max="8704" style="93" width="9"/>
-    <col customWidth="1" min="8705" max="8705" style="93" width="5.125"/>
-    <col customWidth="1" min="8706" max="8713" style="93" width="9.625"/>
-    <col customWidth="1" min="8714" max="8714" style="93" width="5.125"/>
-    <col min="8715" max="8716" style="93" width="9"/>
-    <col customWidth="1" min="8717" max="8717" style="93" width="22.75"/>
-    <col customWidth="1" min="8718" max="8724" style="93" width="13.625"/>
-    <col min="8725" max="8960" style="93" width="9"/>
-    <col customWidth="1" min="8961" max="8961" style="93" width="5.125"/>
-    <col customWidth="1" min="8962" max="8969" style="93" width="9.625"/>
-    <col customWidth="1" min="8970" max="8970" style="93" width="5.125"/>
-    <col min="8971" max="8972" style="93" width="9"/>
-    <col customWidth="1" min="8973" max="8973" style="93" width="22.75"/>
-    <col customWidth="1" min="8974" max="8980" style="93" width="13.625"/>
-    <col min="8981" max="9216" style="93" width="9"/>
-    <col customWidth="1" min="9217" max="9217" style="93" width="5.125"/>
-    <col customWidth="1" min="9218" max="9225" style="93" width="9.625"/>
-    <col customWidth="1" min="9226" max="9226" style="93" width="5.125"/>
-    <col min="9227" max="9228" style="93" width="9"/>
-    <col customWidth="1" min="9229" max="9229" style="93" width="22.75"/>
-    <col customWidth="1" min="9230" max="9236" style="93" width="13.625"/>
-    <col min="9237" max="9472" style="93" width="9"/>
-    <col customWidth="1" min="9473" max="9473" style="93" width="5.125"/>
-    <col customWidth="1" min="9474" max="9481" style="93" width="9.625"/>
-    <col customWidth="1" min="9482" max="9482" style="93" width="5.125"/>
-    <col min="9483" max="9484" style="93" width="9"/>
-    <col customWidth="1" min="9485" max="9485" style="93" width="22.75"/>
-    <col customWidth="1" min="9486" max="9492" style="93" width="13.625"/>
-    <col min="9493" max="9728" style="93" width="9"/>
-    <col customWidth="1" min="9729" max="9729" style="93" width="5.125"/>
-    <col customWidth="1" min="9730" max="9737" style="93" width="9.625"/>
-    <col customWidth="1" min="9738" max="9738" style="93" width="5.125"/>
-    <col min="9739" max="9740" style="93" width="9"/>
-    <col customWidth="1" min="9741" max="9741" style="93" width="22.75"/>
-    <col customWidth="1" min="9742" max="9748" style="93" width="13.625"/>
-    <col min="9749" max="9984" style="93" width="9"/>
-    <col customWidth="1" min="9985" max="9985" style="93" width="5.125"/>
-    <col customWidth="1" min="9986" max="9993" style="93" width="9.625"/>
-    <col customWidth="1" min="9994" max="9994" style="93" width="5.125"/>
-    <col min="9995" max="9996" style="93" width="9"/>
-    <col customWidth="1" min="9997" max="9997" style="93" width="22.75"/>
-    <col customWidth="1" min="9998" max="10004" style="93" width="13.625"/>
-    <col min="10005" max="10240" style="93" width="9"/>
-    <col customWidth="1" min="10241" max="10241" style="93" width="5.125"/>
-    <col customWidth="1" min="10242" max="10249" style="93" width="9.625"/>
-    <col customWidth="1" min="10250" max="10250" style="93" width="5.125"/>
-    <col min="10251" max="10252" style="93" width="9"/>
-    <col customWidth="1" min="10253" max="10253" style="93" width="22.75"/>
-    <col customWidth="1" min="10254" max="10260" style="93" width="13.625"/>
-    <col min="10261" max="10496" style="93" width="9"/>
-    <col customWidth="1" min="10497" max="10497" style="93" width="5.125"/>
-    <col customWidth="1" min="10498" max="10505" style="93" width="9.625"/>
-    <col customWidth="1" min="10506" max="10506" style="93" width="5.125"/>
-    <col min="10507" max="10508" style="93" width="9"/>
-    <col customWidth="1" min="10509" max="10509" style="93" width="22.75"/>
-    <col customWidth="1" min="10510" max="10516" style="93" width="13.625"/>
-    <col min="10517" max="10752" style="93" width="9"/>
-    <col customWidth="1" min="10753" max="10753" style="93" width="5.125"/>
-    <col customWidth="1" min="10754" max="10761" style="93" width="9.625"/>
-    <col customWidth="1" min="10762" max="10762" style="93" width="5.125"/>
-    <col min="10763" max="10764" style="93" width="9"/>
-    <col customWidth="1" min="10765" max="10765" style="93" width="22.75"/>
-    <col customWidth="1" min="10766" max="10772" style="93" width="13.625"/>
-    <col min="10773" max="11008" style="93" width="9"/>
-    <col customWidth="1" min="11009" max="11009" style="93" width="5.125"/>
-    <col customWidth="1" min="11010" max="11017" style="93" width="9.625"/>
-    <col customWidth="1" min="11018" max="11018" style="93" width="5.125"/>
-    <col min="11019" max="11020" style="93" width="9"/>
-    <col customWidth="1" min="11021" max="11021" style="93" width="22.75"/>
-    <col customWidth="1" min="11022" max="11028" style="93" width="13.625"/>
-    <col min="11029" max="11264" style="93" width="9"/>
-    <col customWidth="1" min="11265" max="11265" style="93" width="5.125"/>
-    <col customWidth="1" min="11266" max="11273" style="93" width="9.625"/>
-    <col customWidth="1" min="11274" max="11274" style="93" width="5.125"/>
-    <col min="11275" max="11276" style="93" width="9"/>
-    <col customWidth="1" min="11277" max="11277" style="93" width="22.75"/>
-    <col customWidth="1" min="11278" max="11284" style="93" width="13.625"/>
-    <col min="11285" max="11520" style="93" width="9"/>
-    <col customWidth="1" min="11521" max="11521" style="93" width="5.125"/>
-    <col customWidth="1" min="11522" max="11529" style="93" width="9.625"/>
-    <col customWidth="1" min="11530" max="11530" style="93" width="5.125"/>
-    <col min="11531" max="11532" style="93" width="9"/>
-    <col customWidth="1" min="11533" max="11533" style="93" width="22.75"/>
-    <col customWidth="1" min="11534" max="11540" style="93" width="13.625"/>
-    <col min="11541" max="11776" style="93" width="9"/>
-    <col customWidth="1" min="11777" max="11777" style="93" width="5.125"/>
-    <col customWidth="1" min="11778" max="11785" style="93" width="9.625"/>
-    <col customWidth="1" min="11786" max="11786" style="93" width="5.125"/>
-    <col min="11787" max="11788" style="93" width="9"/>
-    <col customWidth="1" min="11789" max="11789" style="93" width="22.75"/>
-    <col customWidth="1" min="11790" max="11796" style="93" width="13.625"/>
-    <col min="11797" max="12032" style="93" width="9"/>
-    <col customWidth="1" min="12033" max="12033" style="93" width="5.125"/>
-    <col customWidth="1" min="12034" max="12041" style="93" width="9.625"/>
-    <col customWidth="1" min="12042" max="12042" style="93" width="5.125"/>
-    <col min="12043" max="12044" style="93" width="9"/>
-    <col customWidth="1" min="12045" max="12045" style="93" width="22.75"/>
-    <col customWidth="1" min="12046" max="12052" style="93" width="13.625"/>
-    <col min="12053" max="12288" style="93" width="9"/>
-    <col customWidth="1" min="12289" max="12289" style="93" width="5.125"/>
-    <col customWidth="1" min="12290" max="12297" style="93" width="9.625"/>
-    <col customWidth="1" min="12298" max="12298" style="93" width="5.125"/>
-    <col min="12299" max="12300" style="93" width="9"/>
-    <col customWidth="1" min="12301" max="12301" style="93" width="22.75"/>
-    <col customWidth="1" min="12302" max="12308" style="93" width="13.625"/>
-    <col min="12309" max="12544" style="93" width="9"/>
-    <col customWidth="1" min="12545" max="12545" style="93" width="5.125"/>
-    <col customWidth="1" min="12546" max="12553" style="93" width="9.625"/>
-    <col customWidth="1" min="12554" max="12554" style="93" width="5.125"/>
-    <col min="12555" max="12556" style="93" width="9"/>
-    <col customWidth="1" min="12557" max="12557" style="93" width="22.75"/>
-    <col customWidth="1" min="12558" max="12564" style="93" width="13.625"/>
-    <col min="12565" max="12800" style="93" width="9"/>
-    <col customWidth="1" min="12801" max="12801" style="93" width="5.125"/>
-    <col customWidth="1" min="12802" max="12809" style="93" width="9.625"/>
-    <col customWidth="1" min="12810" max="12810" style="93" width="5.125"/>
-    <col min="12811" max="12812" style="93" width="9"/>
-    <col customWidth="1" min="12813" max="12813" style="93" width="22.75"/>
-    <col customWidth="1" min="12814" max="12820" style="93" width="13.625"/>
-    <col min="12821" max="13056" style="93" width="9"/>
-    <col customWidth="1" min="13057" max="13057" style="93" width="5.125"/>
-    <col customWidth="1" min="13058" max="13065" style="93" width="9.625"/>
-    <col customWidth="1" min="13066" max="13066" style="93" width="5.125"/>
-    <col min="13067" max="13068" style="93" width="9"/>
-    <col customWidth="1" min="13069" max="13069" style="93" width="22.75"/>
-    <col customWidth="1" min="13070" max="13076" style="93" width="13.625"/>
-    <col min="13077" max="13312" style="93" width="9"/>
-    <col customWidth="1" min="13313" max="13313" style="93" width="5.125"/>
-    <col customWidth="1" min="13314" max="13321" style="93" width="9.625"/>
-    <col customWidth="1" min="13322" max="13322" style="93" width="5.125"/>
-    <col min="13323" max="13324" style="93" width="9"/>
-    <col customWidth="1" min="13325" max="13325" style="93" width="22.75"/>
-    <col customWidth="1" min="13326" max="13332" style="93" width="13.625"/>
-    <col min="13333" max="13568" style="93" width="9"/>
-    <col customWidth="1" min="13569" max="13569" style="93" width="5.125"/>
-    <col customWidth="1" min="13570" max="13577" style="93" width="9.625"/>
-    <col customWidth="1" min="13578" max="13578" style="93" width="5.125"/>
-    <col min="13579" max="13580" style="93" width="9"/>
-    <col customWidth="1" min="13581" max="13581" style="93" width="22.75"/>
-    <col customWidth="1" min="13582" max="13588" style="93" width="13.625"/>
-    <col min="13589" max="13824" style="93" width="9"/>
-    <col customWidth="1" min="13825" max="13825" style="93" width="5.125"/>
-    <col customWidth="1" min="13826" max="13833" style="93" width="9.625"/>
-    <col customWidth="1" min="13834" max="13834" style="93" width="5.125"/>
-    <col min="13835" max="13836" style="93" width="9"/>
-    <col customWidth="1" min="13837" max="13837" style="93" width="22.75"/>
-    <col customWidth="1" min="13838" max="13844" style="93" width="13.625"/>
-    <col min="13845" max="14080" style="93" width="9"/>
-    <col customWidth="1" min="14081" max="14081" style="93" width="5.125"/>
-    <col customWidth="1" min="14082" max="14089" style="93" width="9.625"/>
-    <col customWidth="1" min="14090" max="14090" style="93" width="5.125"/>
-    <col min="14091" max="14092" style="93" width="9"/>
-    <col customWidth="1" min="14093" max="14093" style="93" width="22.75"/>
-    <col customWidth="1" min="14094" max="14100" style="93" width="13.625"/>
-    <col min="14101" max="14336" style="93" width="9"/>
-    <col customWidth="1" min="14337" max="14337" style="93" width="5.125"/>
-    <col customWidth="1" min="14338" max="14345" style="93" width="9.625"/>
-    <col customWidth="1" min="14346" max="14346" style="93" width="5.125"/>
-    <col min="14347" max="14348" style="93" width="9"/>
-    <col customWidth="1" min="14349" max="14349" style="93" width="22.75"/>
-    <col customWidth="1" min="14350" max="14356" style="93" width="13.625"/>
-    <col min="14357" max="14592" style="93" width="9"/>
-    <col customWidth="1" min="14593" max="14593" style="93" width="5.125"/>
-    <col customWidth="1" min="14594" max="14601" style="93" width="9.625"/>
-    <col customWidth="1" min="14602" max="14602" style="93" width="5.125"/>
-    <col min="14603" max="14604" style="93" width="9"/>
-    <col customWidth="1" min="14605" max="14605" style="93" width="22.75"/>
-    <col customWidth="1" min="14606" max="14612" style="93" width="13.625"/>
-    <col min="14613" max="14848" style="93" width="9"/>
-    <col customWidth="1" min="14849" max="14849" style="93" width="5.125"/>
-    <col customWidth="1" min="14850" max="14857" style="93" width="9.625"/>
-    <col customWidth="1" min="14858" max="14858" style="93" width="5.125"/>
-    <col min="14859" max="14860" style="93" width="9"/>
-    <col customWidth="1" min="14861" max="14861" style="93" width="22.75"/>
-    <col customWidth="1" min="14862" max="14868" style="93" width="13.625"/>
-    <col min="14869" max="15104" style="93" width="9"/>
-    <col customWidth="1" min="15105" max="15105" style="93" width="5.125"/>
-    <col customWidth="1" min="15106" max="15113" style="93" width="9.625"/>
-    <col customWidth="1" min="15114" max="15114" style="93" width="5.125"/>
-    <col min="15115" max="15116" style="93" width="9"/>
-    <col customWidth="1" min="15117" max="15117" style="93" width="22.75"/>
-    <col customWidth="1" min="15118" max="15124" style="93" width="13.625"/>
-    <col min="15125" max="15360" style="93" width="9"/>
-    <col customWidth="1" min="15361" max="15361" style="93" width="5.125"/>
-    <col customWidth="1" min="15362" max="15369" style="93" width="9.625"/>
-    <col customWidth="1" min="15370" max="15370" style="93" width="5.125"/>
-    <col min="15371" max="15372" style="93" width="9"/>
-    <col customWidth="1" min="15373" max="15373" style="93" width="22.75"/>
-    <col customWidth="1" min="15374" max="15380" style="93" width="13.625"/>
-    <col min="15381" max="15616" style="93" width="9"/>
-    <col customWidth="1" min="15617" max="15617" style="93" width="5.125"/>
-    <col customWidth="1" min="15618" max="15625" style="93" width="9.625"/>
-    <col customWidth="1" min="15626" max="15626" style="93" width="5.125"/>
-    <col min="15627" max="15628" style="93" width="9"/>
-    <col customWidth="1" min="15629" max="15629" style="93" width="22.75"/>
-    <col customWidth="1" min="15630" max="15636" style="93" width="13.625"/>
-    <col min="15637" max="15872" style="93" width="9"/>
-    <col customWidth="1" min="15873" max="15873" style="93" width="5.125"/>
-    <col customWidth="1" min="15874" max="15881" style="93" width="9.625"/>
-    <col customWidth="1" min="15882" max="15882" style="93" width="5.125"/>
-    <col min="15883" max="15884" style="93" width="9"/>
-    <col customWidth="1" min="15885" max="15885" style="93" width="22.75"/>
-    <col customWidth="1" min="15886" max="15892" style="93" width="13.625"/>
-    <col min="15893" max="16128" style="93" width="9"/>
-    <col customWidth="1" min="16129" max="16129" style="93" width="5.125"/>
-    <col customWidth="1" min="16130" max="16137" style="93" width="9.625"/>
-    <col customWidth="1" min="16138" max="16138" style="93" width="5.125"/>
-    <col min="16139" max="16140" style="93" width="9"/>
-    <col customWidth="1" min="16141" max="16141" style="93" width="22.75"/>
-    <col customWidth="1" min="16142" max="16148" style="93" width="13.625"/>
-    <col min="16149" max="16384" style="93" width="9"/>
+    <col customWidth="1" min="1" max="1" style="94" width="5.125"/>
+    <col customWidth="1" min="2" max="9" style="94" width="9.625"/>
+    <col customWidth="1" min="10" max="10" style="94" width="5.125"/>
+    <col min="11" max="12" style="94" width="9"/>
+    <col customWidth="1" min="13" max="13" style="94" width="22.75"/>
+    <col customWidth="1" min="14" max="20" style="94" width="13.625"/>
+    <col min="21" max="256" style="94" width="9"/>
+    <col customWidth="1" min="257" max="257" style="94" width="5.125"/>
+    <col customWidth="1" min="258" max="265" style="94" width="9.625"/>
+    <col customWidth="1" min="266" max="266" style="94" width="5.125"/>
+    <col min="267" max="268" style="94" width="9"/>
+    <col customWidth="1" min="269" max="269" style="94" width="22.75"/>
+    <col customWidth="1" min="270" max="276" style="94" width="13.625"/>
+    <col min="277" max="512" style="94" width="9"/>
+    <col customWidth="1" min="513" max="513" style="94" width="5.125"/>
+    <col customWidth="1" min="514" max="521" style="94" width="9.625"/>
+    <col customWidth="1" min="522" max="522" style="94" width="5.125"/>
+    <col min="523" max="524" style="94" width="9"/>
+    <col customWidth="1" min="525" max="525" style="94" width="22.75"/>
+    <col customWidth="1" min="526" max="532" style="94" width="13.625"/>
+    <col min="533" max="768" style="94" width="9"/>
+    <col customWidth="1" min="769" max="769" style="94" width="5.125"/>
+    <col customWidth="1" min="770" max="777" style="94" width="9.625"/>
+    <col customWidth="1" min="778" max="778" style="94" width="5.125"/>
+    <col min="779" max="780" style="94" width="9"/>
+    <col customWidth="1" min="781" max="781" style="94" width="22.75"/>
+    <col customWidth="1" min="782" max="788" style="94" width="13.625"/>
+    <col min="789" max="1024" style="94" width="9"/>
+    <col customWidth="1" min="1025" max="1025" style="94" width="5.125"/>
+    <col customWidth="1" min="1026" max="1033" style="94" width="9.625"/>
+    <col customWidth="1" min="1034" max="1034" style="94" width="5.125"/>
+    <col min="1035" max="1036" style="94" width="9"/>
+    <col customWidth="1" min="1037" max="1037" style="94" width="22.75"/>
+    <col customWidth="1" min="1038" max="1044" style="94" width="13.625"/>
+    <col min="1045" max="1280" style="94" width="9"/>
+    <col customWidth="1" min="1281" max="1281" style="94" width="5.125"/>
+    <col customWidth="1" min="1282" max="1289" style="94" width="9.625"/>
+    <col customWidth="1" min="1290" max="1290" style="94" width="5.125"/>
+    <col min="1291" max="1292" style="94" width="9"/>
+    <col customWidth="1" min="1293" max="1293" style="94" width="22.75"/>
+    <col customWidth="1" min="1294" max="1300" style="94" width="13.625"/>
+    <col min="1301" max="1536" style="94" width="9"/>
+    <col customWidth="1" min="1537" max="1537" style="94" width="5.125"/>
+    <col customWidth="1" min="1538" max="1545" style="94" width="9.625"/>
+    <col customWidth="1" min="1546" max="1546" style="94" width="5.125"/>
+    <col min="1547" max="1548" style="94" width="9"/>
+    <col customWidth="1" min="1549" max="1549" style="94" width="22.75"/>
+    <col customWidth="1" min="1550" max="1556" style="94" width="13.625"/>
+    <col min="1557" max="1792" style="94" width="9"/>
+    <col customWidth="1" min="1793" max="1793" style="94" width="5.125"/>
+    <col customWidth="1" min="1794" max="1801" style="94" width="9.625"/>
+    <col customWidth="1" min="1802" max="1802" style="94" width="5.125"/>
+    <col min="1803" max="1804" style="94" width="9"/>
+    <col customWidth="1" min="1805" max="1805" style="94" width="22.75"/>
+    <col customWidth="1" min="1806" max="1812" style="94" width="13.625"/>
+    <col min="1813" max="2048" style="94" width="9"/>
+    <col customWidth="1" min="2049" max="2049" style="94" width="5.125"/>
+    <col customWidth="1" min="2050" max="2057" style="94" width="9.625"/>
+    <col customWidth="1" min="2058" max="2058" style="94" width="5.125"/>
+    <col min="2059" max="2060" style="94" width="9"/>
+    <col customWidth="1" min="2061" max="2061" style="94" width="22.75"/>
+    <col customWidth="1" min="2062" max="2068" style="94" width="13.625"/>
+    <col min="2069" max="2304" style="94" width="9"/>
+    <col customWidth="1" min="2305" max="2305" style="94" width="5.125"/>
+    <col customWidth="1" min="2306" max="2313" style="94" width="9.625"/>
+    <col customWidth="1" min="2314" max="2314" style="94" width="5.125"/>
+    <col min="2315" max="2316" style="94" width="9"/>
+    <col customWidth="1" min="2317" max="2317" style="94" width="22.75"/>
+    <col customWidth="1" min="2318" max="2324" style="94" width="13.625"/>
+    <col min="2325" max="2560" style="94" width="9"/>
+    <col customWidth="1" min="2561" max="2561" style="94" width="5.125"/>
+    <col customWidth="1" min="2562" max="2569" style="94" width="9.625"/>
+    <col customWidth="1" min="2570" max="2570" style="94" width="5.125"/>
+    <col min="2571" max="2572" style="94" width="9"/>
+    <col customWidth="1" min="2573" max="2573" style="94" width="22.75"/>
+    <col customWidth="1" min="2574" max="2580" style="94" width="13.625"/>
+    <col min="2581" max="2816" style="94" width="9"/>
+    <col customWidth="1" min="2817" max="2817" style="94" width="5.125"/>
+    <col customWidth="1" min="2818" max="2825" style="94" width="9.625"/>
+    <col customWidth="1" min="2826" max="2826" style="94" width="5.125"/>
+    <col min="2827" max="2828" style="94" width="9"/>
+    <col customWidth="1" min="2829" max="2829" style="94" width="22.75"/>
+    <col customWidth="1" min="2830" max="2836" style="94" width="13.625"/>
+    <col min="2837" max="3072" style="94" width="9"/>
+    <col customWidth="1" min="3073" max="3073" style="94" width="5.125"/>
+    <col customWidth="1" min="3074" max="3081" style="94" width="9.625"/>
+    <col customWidth="1" min="3082" max="3082" style="94" width="5.125"/>
+    <col min="3083" max="3084" style="94" width="9"/>
+    <col customWidth="1" min="3085" max="3085" style="94" width="22.75"/>
+    <col customWidth="1" min="3086" max="3092" style="94" width="13.625"/>
+    <col min="3093" max="3328" style="94" width="9"/>
+    <col customWidth="1" min="3329" max="3329" style="94" width="5.125"/>
+    <col customWidth="1" min="3330" max="3337" style="94" width="9.625"/>
+    <col customWidth="1" min="3338" max="3338" style="94" width="5.125"/>
+    <col min="3339" max="3340" style="94" width="9"/>
+    <col customWidth="1" min="3341" max="3341" style="94" width="22.75"/>
+    <col customWidth="1" min="3342" max="3348" style="94" width="13.625"/>
+    <col min="3349" max="3584" style="94" width="9"/>
+    <col customWidth="1" min="3585" max="3585" style="94" width="5.125"/>
+    <col customWidth="1" min="3586" max="3593" style="94" width="9.625"/>
+    <col customWidth="1" min="3594" max="3594" style="94" width="5.125"/>
+    <col min="3595" max="3596" style="94" width="9"/>
+    <col customWidth="1" min="3597" max="3597" style="94" width="22.75"/>
+    <col customWidth="1" min="3598" max="3604" style="94" width="13.625"/>
+    <col min="3605" max="3840" style="94" width="9"/>
+    <col customWidth="1" min="3841" max="3841" style="94" width="5.125"/>
+    <col customWidth="1" min="3842" max="3849" style="94" width="9.625"/>
+    <col customWidth="1" min="3850" max="3850" style="94" width="5.125"/>
+    <col min="3851" max="3852" style="94" width="9"/>
+    <col customWidth="1" min="3853" max="3853" style="94" width="22.75"/>
+    <col customWidth="1" min="3854" max="3860" style="94" width="13.625"/>
+    <col min="3861" max="4096" style="94" width="9"/>
+    <col customWidth="1" min="4097" max="4097" style="94" width="5.125"/>
+    <col customWidth="1" min="4098" max="4105" style="94" width="9.625"/>
+    <col customWidth="1" min="4106" max="4106" style="94" width="5.125"/>
+    <col min="4107" max="4108" style="94" width="9"/>
+    <col customWidth="1" min="4109" max="4109" style="94" width="22.75"/>
+    <col customWidth="1" min="4110" max="4116" style="94" width="13.625"/>
+    <col min="4117" max="4352" style="94" width="9"/>
+    <col customWidth="1" min="4353" max="4353" style="94" width="5.125"/>
+    <col customWidth="1" min="4354" max="4361" style="94" width="9.625"/>
+    <col customWidth="1" min="4362" max="4362" style="94" width="5.125"/>
+    <col min="4363" max="4364" style="94" width="9"/>
+    <col customWidth="1" min="4365" max="4365" style="94" width="22.75"/>
+    <col customWidth="1" min="4366" max="4372" style="94" width="13.625"/>
+    <col min="4373" max="4608" style="94" width="9"/>
+    <col customWidth="1" min="4609" max="4609" style="94" width="5.125"/>
+    <col customWidth="1" min="4610" max="4617" style="94" width="9.625"/>
+    <col customWidth="1" min="4618" max="4618" style="94" width="5.125"/>
+    <col min="4619" max="4620" style="94" width="9"/>
+    <col customWidth="1" min="4621" max="4621" style="94" width="22.75"/>
+    <col customWidth="1" min="4622" max="4628" style="94" width="13.625"/>
+    <col min="4629" max="4864" style="94" width="9"/>
+    <col customWidth="1" min="4865" max="4865" style="94" width="5.125"/>
+    <col customWidth="1" min="4866" max="4873" style="94" width="9.625"/>
+    <col customWidth="1" min="4874" max="4874" style="94" width="5.125"/>
+    <col min="4875" max="4876" style="94" width="9"/>
+    <col customWidth="1" min="4877" max="4877" style="94" width="22.75"/>
+    <col customWidth="1" min="4878" max="4884" style="94" width="13.625"/>
+    <col min="4885" max="5120" style="94" width="9"/>
+    <col customWidth="1" min="5121" max="5121" style="94" width="5.125"/>
+    <col customWidth="1" min="5122" max="5129" style="94" width="9.625"/>
+    <col customWidth="1" min="5130" max="5130" style="94" width="5.125"/>
+    <col min="5131" max="5132" style="94" width="9"/>
+    <col customWidth="1" min="5133" max="5133" style="94" width="22.75"/>
+    <col customWidth="1" min="5134" max="5140" style="94" width="13.625"/>
+    <col min="5141" max="5376" style="94" width="9"/>
+    <col customWidth="1" min="5377" max="5377" style="94" width="5.125"/>
+    <col customWidth="1" min="5378" max="5385" style="94" width="9.625"/>
+    <col customWidth="1" min="5386" max="5386" style="94" width="5.125"/>
+    <col min="5387" max="5388" style="94" width="9"/>
+    <col customWidth="1" min="5389" max="5389" style="94" width="22.75"/>
+    <col customWidth="1" min="5390" max="5396" style="94" width="13.625"/>
+    <col min="5397" max="5632" style="94" width="9"/>
+    <col customWidth="1" min="5633" max="5633" style="94" width="5.125"/>
+    <col customWidth="1" min="5634" max="5641" style="94" width="9.625"/>
+    <col customWidth="1" min="5642" max="5642" style="94" width="5.125"/>
+    <col min="5643" max="5644" style="94" width="9"/>
+    <col customWidth="1" min="5645" max="5645" style="94" width="22.75"/>
+    <col customWidth="1" min="5646" max="5652" style="94" width="13.625"/>
+    <col min="5653" max="5888" style="94" width="9"/>
+    <col customWidth="1" min="5889" max="5889" style="94" width="5.125"/>
+    <col customWidth="1" min="5890" max="5897" style="94" width="9.625"/>
+    <col customWidth="1" min="5898" max="5898" style="94" width="5.125"/>
+    <col min="5899" max="5900" style="94" width="9"/>
+    <col customWidth="1" min="5901" max="5901" style="94" width="22.75"/>
+    <col customWidth="1" min="5902" max="5908" style="94" width="13.625"/>
+    <col min="5909" max="6144" style="94" width="9"/>
+    <col customWidth="1" min="6145" max="6145" style="94" width="5.125"/>
+    <col customWidth="1" min="6146" max="6153" style="94" width="9.625"/>
+    <col customWidth="1" min="6154" max="6154" style="94" width="5.125"/>
+    <col min="6155" max="6156" style="94" width="9"/>
+    <col customWidth="1" min="6157" max="6157" style="94" width="22.75"/>
+    <col customWidth="1" min="6158" max="6164" style="94" width="13.625"/>
+    <col min="6165" max="6400" style="94" width="9"/>
+    <col customWidth="1" min="6401" max="6401" style="94" width="5.125"/>
+    <col customWidth="1" min="6402" max="6409" style="94" width="9.625"/>
+    <col customWidth="1" min="6410" max="6410" style="94" width="5.125"/>
+    <col min="6411" max="6412" style="94" width="9"/>
+    <col customWidth="1" min="6413" max="6413" style="94" width="22.75"/>
+    <col customWidth="1" min="6414" max="6420" style="94" width="13.625"/>
+    <col min="6421" max="6656" style="94" width="9"/>
+    <col customWidth="1" min="6657" max="6657" style="94" width="5.125"/>
+    <col customWidth="1" min="6658" max="6665" style="94" width="9.625"/>
+    <col customWidth="1" min="6666" max="6666" style="94" width="5.125"/>
+    <col min="6667" max="6668" style="94" width="9"/>
+    <col customWidth="1" min="6669" max="6669" style="94" width="22.75"/>
+    <col customWidth="1" min="6670" max="6676" style="94" width="13.625"/>
+    <col min="6677" max="6912" style="94" width="9"/>
+    <col customWidth="1" min="6913" max="6913" style="94" width="5.125"/>
+    <col customWidth="1" min="6914" max="6921" style="94" width="9.625"/>
+    <col customWidth="1" min="6922" max="6922" style="94" width="5.125"/>
+    <col min="6923" max="6924" style="94" width="9"/>
+    <col customWidth="1" min="6925" max="6925" style="94" width="22.75"/>
+    <col customWidth="1" min="6926" max="6932" style="94" width="13.625"/>
+    <col min="6933" max="7168" style="94" width="9"/>
+    <col customWidth="1" min="7169" max="7169" style="94" width="5.125"/>
+    <col customWidth="1" min="7170" max="7177" style="94" width="9.625"/>
+    <col customWidth="1" min="7178" max="7178" style="94" width="5.125"/>
+    <col min="7179" max="7180" style="94" width="9"/>
+    <col customWidth="1" min="7181" max="7181" style="94" width="22.75"/>
+    <col customWidth="1" min="7182" max="7188" style="94" width="13.625"/>
+    <col min="7189" max="7424" style="94" width="9"/>
+    <col customWidth="1" min="7425" max="7425" style="94" width="5.125"/>
+    <col customWidth="1" min="7426" max="7433" style="94" width="9.625"/>
+    <col customWidth="1" min="7434" max="7434" style="94" width="5.125"/>
+    <col min="7435" max="7436" style="94" width="9"/>
+    <col customWidth="1" min="7437" max="7437" style="94" width="22.75"/>
+    <col customWidth="1" min="7438" max="7444" style="94" width="13.625"/>
+    <col min="7445" max="7680" style="94" width="9"/>
+    <col customWidth="1" min="7681" max="7681" style="94" width="5.125"/>
+    <col customWidth="1" min="7682" max="7689" style="94" width="9.625"/>
+    <col customWidth="1" min="7690" max="7690" style="94" width="5.125"/>
+    <col min="7691" max="7692" style="94" width="9"/>
+    <col customWidth="1" min="7693" max="7693" style="94" width="22.75"/>
+    <col customWidth="1" min="7694" max="7700" style="94" width="13.625"/>
+    <col min="7701" max="7936" style="94" width="9"/>
+    <col customWidth="1" min="7937" max="7937" style="94" width="5.125"/>
+    <col customWidth="1" min="7938" max="7945" style="94" width="9.625"/>
+    <col customWidth="1" min="7946" max="7946" style="94" width="5.125"/>
+    <col min="7947" max="7948" style="94" width="9"/>
+    <col customWidth="1" min="7949" max="7949" style="94" width="22.75"/>
+    <col customWidth="1" min="7950" max="7956" style="94" width="13.625"/>
+    <col min="7957" max="8192" style="94" width="9"/>
+    <col customWidth="1" min="8193" max="8193" style="94" width="5.125"/>
+    <col customWidth="1" min="8194" max="8201" style="94" width="9.625"/>
+    <col customWidth="1" min="8202" max="8202" style="94" width="5.125"/>
+    <col min="8203" max="8204" style="94" width="9"/>
+    <col customWidth="1" min="8205" max="8205" style="94" width="22.75"/>
+    <col customWidth="1" min="8206" max="8212" style="94" width="13.625"/>
+    <col min="8213" max="8448" style="94" width="9"/>
+    <col customWidth="1" min="8449" max="8449" style="94" width="5.125"/>
+    <col customWidth="1" min="8450" max="8457" style="94" width="9.625"/>
+    <col customWidth="1" min="8458" max="8458" style="94" width="5.125"/>
+    <col min="8459" max="8460" style="94" width="9"/>
+    <col customWidth="1" min="8461" max="8461" style="94" width="22.75"/>
+    <col customWidth="1" min="8462" max="8468" style="94" width="13.625"/>
+    <col min="8469" max="8704" style="94" width="9"/>
+    <col customWidth="1" min="8705" max="8705" style="94" width="5.125"/>
+    <col customWidth="1" min="8706" max="8713" style="94" width="9.625"/>
+    <col customWidth="1" min="8714" max="8714" style="94" width="5.125"/>
+    <col min="8715" max="8716" style="94" width="9"/>
+    <col customWidth="1" min="8717" max="8717" style="94" width="22.75"/>
+    <col customWidth="1" min="8718" max="8724" style="94" width="13.625"/>
+    <col min="8725" max="8960" style="94" width="9"/>
+    <col customWidth="1" min="8961" max="8961" style="94" width="5.125"/>
+    <col customWidth="1" min="8962" max="8969" style="94" width="9.625"/>
+    <col customWidth="1" min="8970" max="8970" style="94" width="5.125"/>
+    <col min="8971" max="8972" style="94" width="9"/>
+    <col customWidth="1" min="8973" max="8973" style="94" width="22.75"/>
+    <col customWidth="1" min="8974" max="8980" style="94" width="13.625"/>
+    <col min="8981" max="9216" style="94" width="9"/>
+    <col customWidth="1" min="9217" max="9217" style="94" width="5.125"/>
+    <col customWidth="1" min="9218" max="9225" style="94" width="9.625"/>
+    <col customWidth="1" min="9226" max="9226" style="94" width="5.125"/>
+    <col min="9227" max="9228" style="94" width="9"/>
+    <col customWidth="1" min="9229" max="9229" style="94" width="22.75"/>
+    <col customWidth="1" min="9230" max="9236" style="94" width="13.625"/>
+    <col min="9237" max="9472" style="94" width="9"/>
+    <col customWidth="1" min="9473" max="9473" style="94" width="5.125"/>
+    <col customWidth="1" min="9474" max="9481" style="94" width="9.625"/>
+    <col customWidth="1" min="9482" max="9482" style="94" width="5.125"/>
+    <col min="9483" max="9484" style="94" width="9"/>
+    <col customWidth="1" min="9485" max="9485" style="94" width="22.75"/>
+    <col customWidth="1" min="9486" max="9492" style="94" width="13.625"/>
+    <col min="9493" max="9728" style="94" width="9"/>
+    <col customWidth="1" min="9729" max="9729" style="94" width="5.125"/>
+    <col customWidth="1" min="9730" max="9737" style="94" width="9.625"/>
+    <col customWidth="1" min="9738" max="9738" style="94" width="5.125"/>
+    <col min="9739" max="9740" style="94" width="9"/>
+    <col customWidth="1" min="9741" max="9741" style="94" width="22.75"/>
+    <col customWidth="1" min="9742" max="9748" style="94" width="13.625"/>
+    <col min="9749" max="9984" style="94" width="9"/>
+    <col customWidth="1" min="9985" max="9985" style="94" width="5.125"/>
+    <col customWidth="1" min="9986" max="9993" style="94" width="9.625"/>
+    <col customWidth="1" min="9994" max="9994" style="94" width="5.125"/>
+    <col min="9995" max="9996" style="94" width="9"/>
+    <col customWidth="1" min="9997" max="9997" style="94" width="22.75"/>
+    <col customWidth="1" min="9998" max="10004" style="94" width="13.625"/>
+    <col min="10005" max="10240" style="94" width="9"/>
+    <col customWidth="1" min="10241" max="10241" style="94" width="5.125"/>
+    <col customWidth="1" min="10242" max="10249" style="94" width="9.625"/>
+    <col customWidth="1" min="10250" max="10250" style="94" width="5.125"/>
+    <col min="10251" max="10252" style="94" width="9"/>
+    <col customWidth="1" min="10253" max="10253" style="94" width="22.75"/>
+    <col customWidth="1" min="10254" max="10260" style="94" width="13.625"/>
+    <col min="10261" max="10496" style="94" width="9"/>
+    <col customWidth="1" min="10497" max="10497" style="94" width="5.125"/>
+    <col customWidth="1" min="10498" max="10505" style="94" width="9.625"/>
+    <col customWidth="1" min="10506" max="10506" style="94" width="5.125"/>
+    <col min="10507" max="10508" style="94" width="9"/>
+    <col customWidth="1" min="10509" max="10509" style="94" width="22.75"/>
+    <col customWidth="1" min="10510" max="10516" style="94" width="13.625"/>
+    <col min="10517" max="10752" style="94" width="9"/>
+    <col customWidth="1" min="10753" max="10753" style="94" width="5.125"/>
+    <col customWidth="1" min="10754" max="10761" style="94" width="9.625"/>
+    <col customWidth="1" min="10762" max="10762" style="94" width="5.125"/>
+    <col min="10763" max="10764" style="94" width="9"/>
+    <col customWidth="1" min="10765" max="10765" style="94" width="22.75"/>
+    <col customWidth="1" min="10766" max="10772" style="94" width="13.625"/>
+    <col min="10773" max="11008" style="94" width="9"/>
+    <col customWidth="1" min="11009" max="11009" style="94" width="5.125"/>
+    <col customWidth="1" min="11010" max="11017" style="94" width="9.625"/>
+    <col customWidth="1" min="11018" max="11018" style="94" width="5.125"/>
+    <col min="11019" max="11020" style="94" width="9"/>
+    <col customWidth="1" min="11021" max="11021" style="94" width="22.75"/>
+    <col customWidth="1" min="11022" max="11028" style="94" width="13.625"/>
+    <col min="11029" max="11264" style="94" width="9"/>
+    <col customWidth="1" min="11265" max="11265" style="94" width="5.125"/>
+    <col customWidth="1" min="11266" max="11273" style="94" width="9.625"/>
+    <col customWidth="1" min="11274" max="11274" style="94" width="5.125"/>
+    <col min="11275" max="11276" style="94" width="9"/>
+    <col customWidth="1" min="11277" max="11277" style="94" width="22.75"/>
+    <col customWidth="1" min="11278" max="11284" style="94" width="13.625"/>
+    <col min="11285" max="11520" style="94" width="9"/>
+    <col customWidth="1" min="11521" max="11521" style="94" width="5.125"/>
+    <col customWidth="1" min="11522" max="11529" style="94" width="9.625"/>
+    <col customWidth="1" min="11530" max="11530" style="94" width="5.125"/>
+    <col min="11531" max="11532" style="94" width="9"/>
+    <col customWidth="1" min="11533" max="11533" style="94" width="22.75"/>
+    <col customWidth="1" min="11534" max="11540" style="94" width="13.625"/>
+    <col min="11541" max="11776" style="94" width="9"/>
+    <col customWidth="1" min="11777" max="11777" style="94" width="5.125"/>
+    <col customWidth="1" min="11778" max="11785" style="94" width="9.625"/>
+    <col customWidth="1" min="11786" max="11786" style="94" width="5.125"/>
+    <col min="11787" max="11788" style="94" width="9"/>
+    <col customWidth="1" min="11789" max="11789" style="94" width="22.75"/>
+    <col customWidth="1" min="11790" max="11796" style="94" width="13.625"/>
+    <col min="11797" max="12032" style="94" width="9"/>
+    <col customWidth="1" min="12033" max="12033" style="94" width="5.125"/>
+    <col customWidth="1" min="12034" max="12041" style="94" width="9.625"/>
+    <col customWidth="1" min="12042" max="12042" style="94" width="5.125"/>
+    <col min="12043" max="12044" style="94" width="9"/>
+    <col customWidth="1" min="12045" max="12045" style="94" width="22.75"/>
+    <col customWidth="1" min="12046" max="12052" style="94" width="13.625"/>
+    <col min="12053" max="12288" style="94" width="9"/>
+    <col customWidth="1" min="12289" max="12289" style="94" width="5.125"/>
+    <col customWidth="1" min="12290" max="12297" style="94" width="9.625"/>
+    <col customWidth="1" min="12298" max="12298" style="94" width="5.125"/>
+    <col min="12299" max="12300" style="94" width="9"/>
+    <col customWidth="1" min="12301" max="12301" style="94" width="22.75"/>
+    <col customWidth="1" min="12302" max="12308" style="94" width="13.625"/>
+    <col min="12309" max="12544" style="94" width="9"/>
+    <col customWidth="1" min="12545" max="12545" style="94" width="5.125"/>
+    <col customWidth="1" min="12546" max="12553" style="94" width="9.625"/>
+    <col customWidth="1" min="12554" max="12554" style="94" width="5.125"/>
+    <col min="12555" max="12556" style="94" width="9"/>
+    <col customWidth="1" min="12557" max="12557" style="94" width="22.75"/>
+    <col customWidth="1" min="12558" max="12564" style="94" width="13.625"/>
+    <col min="12565" max="12800" style="94" width="9"/>
+    <col customWidth="1" min="12801" max="12801" style="94" width="5.125"/>
+    <col customWidth="1" min="12802" max="12809" style="94" width="9.625"/>
+    <col customWidth="1" min="12810" max="12810" style="94" width="5.125"/>
+    <col min="12811" max="12812" style="94" width="9"/>
+    <col customWidth="1" min="12813" max="12813" style="94" width="22.75"/>
+    <col customWidth="1" min="12814" max="12820" style="94" width="13.625"/>
+    <col min="12821" max="13056" style="94" width="9"/>
+    <col customWidth="1" min="13057" max="13057" style="94" width="5.125"/>
+    <col customWidth="1" min="13058" max="13065" style="94" width="9.625"/>
+    <col customWidth="1" min="13066" max="13066" style="94" width="5.125"/>
+    <col min="13067" max="13068" style="94" width="9"/>
+    <col customWidth="1" min="13069" max="13069" style="94" width="22.75"/>
+    <col customWidth="1" min="13070" max="13076" style="94" width="13.625"/>
+    <col min="13077" max="13312" style="94" width="9"/>
+    <col customWidth="1" min="13313" max="13313" style="94" width="5.125"/>
+    <col customWidth="1" min="13314" max="13321" style="94" width="9.625"/>
+    <col customWidth="1" min="13322" max="13322" style="94" width="5.125"/>
+    <col min="13323" max="13324" style="94" width="9"/>
+    <col customWidth="1" min="13325" max="13325" style="94" width="22.75"/>
+    <col customWidth="1" min="13326" max="13332" style="94" width="13.625"/>
+    <col min="13333" max="13568" style="94" width="9"/>
+    <col customWidth="1" min="13569" max="13569" style="94" width="5.125"/>
+    <col customWidth="1" min="13570" max="13577" style="94" width="9.625"/>
+    <col customWidth="1" min="13578" max="13578" style="94" width="5.125"/>
+    <col min="13579" max="13580" style="94" width="9"/>
+    <col customWidth="1" min="13581" max="13581" style="94" width="22.75"/>
+    <col customWidth="1" min="13582" max="13588" style="94" width="13.625"/>
+    <col min="13589" max="13824" style="94" width="9"/>
+    <col customWidth="1" min="13825" max="13825" style="94" width="5.125"/>
+    <col customWidth="1" min="13826" max="13833" style="94" width="9.625"/>
+    <col customWidth="1" min="13834" max="13834" style="94" width="5.125"/>
+    <col min="13835" max="13836" style="94" width="9"/>
+    <col customWidth="1" min="13837" max="13837" style="94" width="22.75"/>
+    <col customWidth="1" min="13838" max="13844" style="94" width="13.625"/>
+    <col min="13845" max="14080" style="94" width="9"/>
+    <col customWidth="1" min="14081" max="14081" style="94" width="5.125"/>
+    <col customWidth="1" min="14082" max="14089" style="94" width="9.625"/>
+    <col customWidth="1" min="14090" max="14090" style="94" width="5.125"/>
+    <col min="14091" max="14092" style="94" width="9"/>
+    <col customWidth="1" min="14093" max="14093" style="94" width="22.75"/>
+    <col customWidth="1" min="14094" max="14100" style="94" width="13.625"/>
+    <col min="14101" max="14336" style="94" width="9"/>
+    <col customWidth="1" min="14337" max="14337" style="94" width="5.125"/>
+    <col customWidth="1" min="14338" max="14345" style="94" width="9.625"/>
+    <col customWidth="1" min="14346" max="14346" style="94" width="5.125"/>
+    <col min="14347" max="14348" style="94" width="9"/>
+    <col customWidth="1" min="14349" max="14349" style="94" width="22.75"/>
+    <col customWidth="1" min="14350" max="14356" style="94" width="13.625"/>
+    <col min="14357" max="14592" style="94" width="9"/>
+    <col customWidth="1" min="14593" max="14593" style="94" width="5.125"/>
+    <col customWidth="1" min="14594" max="14601" style="94" width="9.625"/>
+    <col customWidth="1" min="14602" max="14602" style="94" width="5.125"/>
+    <col min="14603" max="14604" style="94" width="9"/>
+    <col customWidth="1" min="14605" max="14605" style="94" width="22.75"/>
+    <col customWidth="1" min="14606" max="14612" style="94" width="13.625"/>
+    <col min="14613" max="14848" style="94" width="9"/>
+    <col customWidth="1" min="14849" max="14849" style="94" width="5.125"/>
+    <col customWidth="1" min="14850" max="14857" style="94" width="9.625"/>
+    <col customWidth="1" min="14858" max="14858" style="94" width="5.125"/>
+    <col min="14859" max="14860" style="94" width="9"/>
+    <col customWidth="1" min="14861" max="14861" style="94" width="22.75"/>
+    <col customWidth="1" min="14862" max="14868" style="94" width="13.625"/>
+    <col min="14869" max="15104" style="94" width="9"/>
+    <col customWidth="1" min="15105" max="15105" style="94" width="5.125"/>
+    <col customWidth="1" min="15106" max="15113" style="94" width="9.625"/>
+    <col customWidth="1" min="15114" max="15114" style="94" width="5.125"/>
+    <col min="15115" max="15116" style="94" width="9"/>
+    <col customWidth="1" min="15117" max="15117" style="94" width="22.75"/>
+    <col customWidth="1" min="15118" max="15124" style="94" width="13.625"/>
+    <col min="15125" max="15360" style="94" width="9"/>
+    <col customWidth="1" min="15361" max="15361" style="94" width="5.125"/>
+    <col customWidth="1" min="15362" max="15369" style="94" width="9.625"/>
+    <col customWidth="1" min="15370" max="15370" style="94" width="5.125"/>
+    <col min="15371" max="15372" style="94" width="9"/>
+    <col customWidth="1" min="15373" max="15373" style="94" width="22.75"/>
+    <col customWidth="1" min="15374" max="15380" style="94" width="13.625"/>
+    <col min="15381" max="15616" style="94" width="9"/>
+    <col customWidth="1" min="15617" max="15617" style="94" width="5.125"/>
+    <col customWidth="1" min="15618" max="15625" style="94" width="9.625"/>
+    <col customWidth="1" min="15626" max="15626" style="94" width="5.125"/>
+    <col min="15627" max="15628" style="94" width="9"/>
+    <col customWidth="1" min="15629" max="15629" style="94" width="22.75"/>
+    <col customWidth="1" min="15630" max="15636" style="94" width="13.625"/>
+    <col min="15637" max="15872" style="94" width="9"/>
+    <col customWidth="1" min="15873" max="15873" style="94" width="5.125"/>
+    <col customWidth="1" min="15874" max="15881" style="94" width="9.625"/>
+    <col customWidth="1" min="15882" max="15882" style="94" width="5.125"/>
+    <col min="15883" max="15884" style="94" width="9"/>
+    <col customWidth="1" min="15885" max="15885" style="94" width="22.75"/>
+    <col customWidth="1" min="15886" max="15892" style="94" width="13.625"/>
+    <col min="15893" max="16128" style="94" width="9"/>
+    <col customWidth="1" min="16129" max="16129" style="94" width="5.125"/>
+    <col customWidth="1" min="16130" max="16137" style="94" width="9.625"/>
+    <col customWidth="1" min="16138" max="16138" style="94" width="5.125"/>
+    <col min="16139" max="16140" style="94" width="9"/>
+    <col customWidth="1" min="16141" max="16141" style="94" width="22.75"/>
+    <col customWidth="1" min="16142" max="16148" style="94" width="13.625"/>
+    <col min="16149" max="16384" style="94" width="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
     </row>
     <row r="3" ht="15"/>
     <row r="4" ht="15"/>
     <row r="5" ht="15">
-      <c r="A5" s="93" t="str">
+      <c r="A5" s="94" t="str">
         <f>CONCATENATE("■ 계  약  명 : ",환경설정!$B$1)</f>
         <v xml:space="preserve">■ 계  약  명 : 전라남도청 민원인 전용주차장 건립 전기공사 보안등주 등 구매</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="C6" s="95"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="93" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
+      <c r="A7" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
-    </row>
-    <row r="9" ht="15"/>
-    <row r="10" ht="15"/>
-    <row r="11" ht="15"/>
-    <row r="12" ht="15"/>
-    <row r="13" ht="15">
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
-    </row>
-    <row r="14" ht="15">
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
-    </row>
-    <row r="15" ht="15"/>
-    <row r="16" ht="15"/>
-    <row r="17" ht="15"/>
-    <row r="18" ht="15"/>
-    <row r="19" ht="15">
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
-    </row>
-    <row r="20" ht="15">
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-    </row>
-    <row r="21" ht="15"/>
-    <row r="22" ht="15"/>
-    <row r="23" ht="15"/>
-    <row r="24" ht="15"/>
-    <row r="25" ht="15">
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
-    </row>
-    <row r="26" ht="15">
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-    </row>
-    <row r="27" ht="15"/>
-    <row r="28" ht="15"/>
-    <row r="29" ht="15"/>
-    <row r="30" ht="15"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+    </row>
+    <row r="9" ht="19.5" customHeight="1"/>
+    <row r="10" ht="19.5" customHeight="1"/>
+    <row r="11" ht="19.5" customHeight="1"/>
+    <row r="12" ht="19.5" customHeight="1"/>
+    <row r="13" ht="19.5" customHeight="1">
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
+    </row>
+    <row r="14" ht="19.5" customHeight="1">
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
+    </row>
+    <row r="15" ht="19.5" customHeight="1"/>
+    <row r="16" ht="19.5" customHeight="1"/>
+    <row r="17" ht="19.5" customHeight="1"/>
+    <row r="18" ht="19.5" customHeight="1"/>
+    <row r="19" ht="19.5" customHeight="1">
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
+    </row>
+    <row r="21" ht="19.5" customHeight="1"/>
+    <row r="22" ht="19.5" customHeight="1"/>
+    <row r="23" ht="19.5" customHeight="1"/>
+    <row r="24" ht="19.5" customHeight="1"/>
+    <row r="25" ht="19.5" customHeight="1">
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
+    </row>
+    <row r="26" ht="19.5" customHeight="1">
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
+    </row>
+    <row r="27" ht="19.5" customHeight="1"/>
+    <row r="28" ht="19.5" customHeight="1"/>
+    <row r="29" ht="19.5" customHeight="1"/>
+    <row r="30" ht="19.5" customHeight="1"/>
     <row r="31" ht="15">
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="94"/>
     </row>
     <row r="32" ht="15">
-      <c r="C32" s="93"/>
-      <c r="D32" s="93"/>
-      <c r="E32" s="93"/>
-      <c r="F32" s="93"/>
-      <c r="G32" s="93"/>
+      <c r="C32" s="94"/>
+      <c r="D32" s="94"/>
+      <c r="E32" s="94"/>
+      <c r="F32" s="94"/>
+      <c r="G32" s="94"/>
     </row>
     <row r="33" ht="15"/>
     <row r="34" ht="15"/>
     <row r="35" ht="15"/>
     <row r="36" ht="15"/>
     <row r="37" ht="15">
-      <c r="C37" s="93"/>
-      <c r="D37" s="93"/>
-      <c r="E37" s="93"/>
-      <c r="F37" s="93"/>
-      <c r="G37" s="93"/>
+      <c r="C37" s="94"/>
+      <c r="D37" s="94"/>
+      <c r="E37" s="94"/>
+      <c r="F37" s="94"/>
+      <c r="G37" s="94"/>
     </row>
     <row r="38" ht="15"/>
     <row r="39" ht="15"/>
@@ -6304,608 +6315,608 @@
   </sheetPr>
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="93" width="5.125"/>
-    <col customWidth="1" min="2" max="9" style="93" width="9.625"/>
-    <col customWidth="1" min="10" max="10" style="93" width="5.125"/>
-    <col min="11" max="12" style="93" width="9"/>
-    <col customWidth="1" min="13" max="13" style="93" width="22.75"/>
-    <col customWidth="1" min="14" max="20" style="93" width="13.625"/>
-    <col min="21" max="256" style="93" width="9"/>
-    <col customWidth="1" min="257" max="257" style="93" width="5.125"/>
-    <col customWidth="1" min="258" max="265" style="93" width="9.625"/>
-    <col customWidth="1" min="266" max="266" style="93" width="5.125"/>
-    <col min="267" max="268" style="93" width="9"/>
-    <col customWidth="1" min="269" max="269" style="93" width="22.75"/>
-    <col customWidth="1" min="270" max="276" style="93" width="13.625"/>
-    <col min="277" max="512" style="93" width="9"/>
-    <col customWidth="1" min="513" max="513" style="93" width="5.125"/>
-    <col customWidth="1" min="514" max="521" style="93" width="9.625"/>
-    <col customWidth="1" min="522" max="522" style="93" width="5.125"/>
-    <col min="523" max="524" style="93" width="9"/>
-    <col customWidth="1" min="525" max="525" style="93" width="22.75"/>
-    <col customWidth="1" min="526" max="532" style="93" width="13.625"/>
-    <col min="533" max="768" style="93" width="9"/>
-    <col customWidth="1" min="769" max="769" style="93" width="5.125"/>
-    <col customWidth="1" min="770" max="777" style="93" width="9.625"/>
-    <col customWidth="1" min="778" max="778" style="93" width="5.125"/>
-    <col min="779" max="780" style="93" width="9"/>
-    <col customWidth="1" min="781" max="781" style="93" width="22.75"/>
-    <col customWidth="1" min="782" max="788" style="93" width="13.625"/>
-    <col min="789" max="1024" style="93" width="9"/>
-    <col customWidth="1" min="1025" max="1025" style="93" width="5.125"/>
-    <col customWidth="1" min="1026" max="1033" style="93" width="9.625"/>
-    <col customWidth="1" min="1034" max="1034" style="93" width="5.125"/>
-    <col min="1035" max="1036" style="93" width="9"/>
-    <col customWidth="1" min="1037" max="1037" style="93" width="22.75"/>
-    <col customWidth="1" min="1038" max="1044" style="93" width="13.625"/>
-    <col min="1045" max="1280" style="93" width="9"/>
-    <col customWidth="1" min="1281" max="1281" style="93" width="5.125"/>
-    <col customWidth="1" min="1282" max="1289" style="93" width="9.625"/>
-    <col customWidth="1" min="1290" max="1290" style="93" width="5.125"/>
-    <col min="1291" max="1292" style="93" width="9"/>
-    <col customWidth="1" min="1293" max="1293" style="93" width="22.75"/>
-    <col customWidth="1" min="1294" max="1300" style="93" width="13.625"/>
-    <col min="1301" max="1536" style="93" width="9"/>
-    <col customWidth="1" min="1537" max="1537" style="93" width="5.125"/>
-    <col customWidth="1" min="1538" max="1545" style="93" width="9.625"/>
-    <col customWidth="1" min="1546" max="1546" style="93" width="5.125"/>
-    <col min="1547" max="1548" style="93" width="9"/>
-    <col customWidth="1" min="1549" max="1549" style="93" width="22.75"/>
-    <col customWidth="1" min="1550" max="1556" style="93" width="13.625"/>
-    <col min="1557" max="1792" style="93" width="9"/>
-    <col customWidth="1" min="1793" max="1793" style="93" width="5.125"/>
-    <col customWidth="1" min="1794" max="1801" style="93" width="9.625"/>
-    <col customWidth="1" min="1802" max="1802" style="93" width="5.125"/>
-    <col min="1803" max="1804" style="93" width="9"/>
-    <col customWidth="1" min="1805" max="1805" style="93" width="22.75"/>
-    <col customWidth="1" min="1806" max="1812" style="93" width="13.625"/>
-    <col min="1813" max="2048" style="93" width="9"/>
-    <col customWidth="1" min="2049" max="2049" style="93" width="5.125"/>
-    <col customWidth="1" min="2050" max="2057" style="93" width="9.625"/>
-    <col customWidth="1" min="2058" max="2058" style="93" width="5.125"/>
-    <col min="2059" max="2060" style="93" width="9"/>
-    <col customWidth="1" min="2061" max="2061" style="93" width="22.75"/>
-    <col customWidth="1" min="2062" max="2068" style="93" width="13.625"/>
-    <col min="2069" max="2304" style="93" width="9"/>
-    <col customWidth="1" min="2305" max="2305" style="93" width="5.125"/>
-    <col customWidth="1" min="2306" max="2313" style="93" width="9.625"/>
-    <col customWidth="1" min="2314" max="2314" style="93" width="5.125"/>
-    <col min="2315" max="2316" style="93" width="9"/>
-    <col customWidth="1" min="2317" max="2317" style="93" width="22.75"/>
-    <col customWidth="1" min="2318" max="2324" style="93" width="13.625"/>
-    <col min="2325" max="2560" style="93" width="9"/>
-    <col customWidth="1" min="2561" max="2561" style="93" width="5.125"/>
-    <col customWidth="1" min="2562" max="2569" style="93" width="9.625"/>
-    <col customWidth="1" min="2570" max="2570" style="93" width="5.125"/>
-    <col min="2571" max="2572" style="93" width="9"/>
-    <col customWidth="1" min="2573" max="2573" style="93" width="22.75"/>
-    <col customWidth="1" min="2574" max="2580" style="93" width="13.625"/>
-    <col min="2581" max="2816" style="93" width="9"/>
-    <col customWidth="1" min="2817" max="2817" style="93" width="5.125"/>
-    <col customWidth="1" min="2818" max="2825" style="93" width="9.625"/>
-    <col customWidth="1" min="2826" max="2826" style="93" width="5.125"/>
-    <col min="2827" max="2828" style="93" width="9"/>
-    <col customWidth="1" min="2829" max="2829" style="93" width="22.75"/>
-    <col customWidth="1" min="2830" max="2836" style="93" width="13.625"/>
-    <col min="2837" max="3072" style="93" width="9"/>
-    <col customWidth="1" min="3073" max="3073" style="93" width="5.125"/>
-    <col customWidth="1" min="3074" max="3081" style="93" width="9.625"/>
-    <col customWidth="1" min="3082" max="3082" style="93" width="5.125"/>
-    <col min="3083" max="3084" style="93" width="9"/>
-    <col customWidth="1" min="3085" max="3085" style="93" width="22.75"/>
-    <col customWidth="1" min="3086" max="3092" style="93" width="13.625"/>
-    <col min="3093" max="3328" style="93" width="9"/>
-    <col customWidth="1" min="3329" max="3329" style="93" width="5.125"/>
-    <col customWidth="1" min="3330" max="3337" style="93" width="9.625"/>
-    <col customWidth="1" min="3338" max="3338" style="93" width="5.125"/>
-    <col min="3339" max="3340" style="93" width="9"/>
-    <col customWidth="1" min="3341" max="3341" style="93" width="22.75"/>
-    <col customWidth="1" min="3342" max="3348" style="93" width="13.625"/>
-    <col min="3349" max="3584" style="93" width="9"/>
-    <col customWidth="1" min="3585" max="3585" style="93" width="5.125"/>
-    <col customWidth="1" min="3586" max="3593" style="93" width="9.625"/>
-    <col customWidth="1" min="3594" max="3594" style="93" width="5.125"/>
-    <col min="3595" max="3596" style="93" width="9"/>
-    <col customWidth="1" min="3597" max="3597" style="93" width="22.75"/>
-    <col customWidth="1" min="3598" max="3604" style="93" width="13.625"/>
-    <col min="3605" max="3840" style="93" width="9"/>
-    <col customWidth="1" min="3841" max="3841" style="93" width="5.125"/>
-    <col customWidth="1" min="3842" max="3849" style="93" width="9.625"/>
-    <col customWidth="1" min="3850" max="3850" style="93" width="5.125"/>
-    <col min="3851" max="3852" style="93" width="9"/>
-    <col customWidth="1" min="3853" max="3853" style="93" width="22.75"/>
-    <col customWidth="1" min="3854" max="3860" style="93" width="13.625"/>
-    <col min="3861" max="4096" style="93" width="9"/>
-    <col customWidth="1" min="4097" max="4097" style="93" width="5.125"/>
-    <col customWidth="1" min="4098" max="4105" style="93" width="9.625"/>
-    <col customWidth="1" min="4106" max="4106" style="93" width="5.125"/>
-    <col min="4107" max="4108" style="93" width="9"/>
-    <col customWidth="1" min="4109" max="4109" style="93" width="22.75"/>
-    <col customWidth="1" min="4110" max="4116" style="93" width="13.625"/>
-    <col min="4117" max="4352" style="93" width="9"/>
-    <col customWidth="1" min="4353" max="4353" style="93" width="5.125"/>
-    <col customWidth="1" min="4354" max="4361" style="93" width="9.625"/>
-    <col customWidth="1" min="4362" max="4362" style="93" width="5.125"/>
-    <col min="4363" max="4364" style="93" width="9"/>
-    <col customWidth="1" min="4365" max="4365" style="93" width="22.75"/>
-    <col customWidth="1" min="4366" max="4372" style="93" width="13.625"/>
-    <col min="4373" max="4608" style="93" width="9"/>
-    <col customWidth="1" min="4609" max="4609" style="93" width="5.125"/>
-    <col customWidth="1" min="4610" max="4617" style="93" width="9.625"/>
-    <col customWidth="1" min="4618" max="4618" style="93" width="5.125"/>
-    <col min="4619" max="4620" style="93" width="9"/>
-    <col customWidth="1" min="4621" max="4621" style="93" width="22.75"/>
-    <col customWidth="1" min="4622" max="4628" style="93" width="13.625"/>
-    <col min="4629" max="4864" style="93" width="9"/>
-    <col customWidth="1" min="4865" max="4865" style="93" width="5.125"/>
-    <col customWidth="1" min="4866" max="4873" style="93" width="9.625"/>
-    <col customWidth="1" min="4874" max="4874" style="93" width="5.125"/>
-    <col min="4875" max="4876" style="93" width="9"/>
-    <col customWidth="1" min="4877" max="4877" style="93" width="22.75"/>
-    <col customWidth="1" min="4878" max="4884" style="93" width="13.625"/>
-    <col min="4885" max="5120" style="93" width="9"/>
-    <col customWidth="1" min="5121" max="5121" style="93" width="5.125"/>
-    <col customWidth="1" min="5122" max="5129" style="93" width="9.625"/>
-    <col customWidth="1" min="5130" max="5130" style="93" width="5.125"/>
-    <col min="5131" max="5132" style="93" width="9"/>
-    <col customWidth="1" min="5133" max="5133" style="93" width="22.75"/>
-    <col customWidth="1" min="5134" max="5140" style="93" width="13.625"/>
-    <col min="5141" max="5376" style="93" width="9"/>
-    <col customWidth="1" min="5377" max="5377" style="93" width="5.125"/>
-    <col customWidth="1" min="5378" max="5385" style="93" width="9.625"/>
-    <col customWidth="1" min="5386" max="5386" style="93" width="5.125"/>
-    <col min="5387" max="5388" style="93" width="9"/>
-    <col customWidth="1" min="5389" max="5389" style="93" width="22.75"/>
-    <col customWidth="1" min="5390" max="5396" style="93" width="13.625"/>
-    <col min="5397" max="5632" style="93" width="9"/>
-    <col customWidth="1" min="5633" max="5633" style="93" width="5.125"/>
-    <col customWidth="1" min="5634" max="5641" style="93" width="9.625"/>
-    <col customWidth="1" min="5642" max="5642" style="93" width="5.125"/>
-    <col min="5643" max="5644" style="93" width="9"/>
-    <col customWidth="1" min="5645" max="5645" style="93" width="22.75"/>
-    <col customWidth="1" min="5646" max="5652" style="93" width="13.625"/>
-    <col min="5653" max="5888" style="93" width="9"/>
-    <col customWidth="1" min="5889" max="5889" style="93" width="5.125"/>
-    <col customWidth="1" min="5890" max="5897" style="93" width="9.625"/>
-    <col customWidth="1" min="5898" max="5898" style="93" width="5.125"/>
-    <col min="5899" max="5900" style="93" width="9"/>
-    <col customWidth="1" min="5901" max="5901" style="93" width="22.75"/>
-    <col customWidth="1" min="5902" max="5908" style="93" width="13.625"/>
-    <col min="5909" max="6144" style="93" width="9"/>
-    <col customWidth="1" min="6145" max="6145" style="93" width="5.125"/>
-    <col customWidth="1" min="6146" max="6153" style="93" width="9.625"/>
-    <col customWidth="1" min="6154" max="6154" style="93" width="5.125"/>
-    <col min="6155" max="6156" style="93" width="9"/>
-    <col customWidth="1" min="6157" max="6157" style="93" width="22.75"/>
-    <col customWidth="1" min="6158" max="6164" style="93" width="13.625"/>
-    <col min="6165" max="6400" style="93" width="9"/>
-    <col customWidth="1" min="6401" max="6401" style="93" width="5.125"/>
-    <col customWidth="1" min="6402" max="6409" style="93" width="9.625"/>
-    <col customWidth="1" min="6410" max="6410" style="93" width="5.125"/>
-    <col min="6411" max="6412" style="93" width="9"/>
-    <col customWidth="1" min="6413" max="6413" style="93" width="22.75"/>
-    <col customWidth="1" min="6414" max="6420" style="93" width="13.625"/>
-    <col min="6421" max="6656" style="93" width="9"/>
-    <col customWidth="1" min="6657" max="6657" style="93" width="5.125"/>
-    <col customWidth="1" min="6658" max="6665" style="93" width="9.625"/>
-    <col customWidth="1" min="6666" max="6666" style="93" width="5.125"/>
-    <col min="6667" max="6668" style="93" width="9"/>
-    <col customWidth="1" min="6669" max="6669" style="93" width="22.75"/>
-    <col customWidth="1" min="6670" max="6676" style="93" width="13.625"/>
-    <col min="6677" max="6912" style="93" width="9"/>
-    <col customWidth="1" min="6913" max="6913" style="93" width="5.125"/>
-    <col customWidth="1" min="6914" max="6921" style="93" width="9.625"/>
-    <col customWidth="1" min="6922" max="6922" style="93" width="5.125"/>
-    <col min="6923" max="6924" style="93" width="9"/>
-    <col customWidth="1" min="6925" max="6925" style="93" width="22.75"/>
-    <col customWidth="1" min="6926" max="6932" style="93" width="13.625"/>
-    <col min="6933" max="7168" style="93" width="9"/>
-    <col customWidth="1" min="7169" max="7169" style="93" width="5.125"/>
-    <col customWidth="1" min="7170" max="7177" style="93" width="9.625"/>
-    <col customWidth="1" min="7178" max="7178" style="93" width="5.125"/>
-    <col min="7179" max="7180" style="93" width="9"/>
-    <col customWidth="1" min="7181" max="7181" style="93" width="22.75"/>
-    <col customWidth="1" min="7182" max="7188" style="93" width="13.625"/>
-    <col min="7189" max="7424" style="93" width="9"/>
-    <col customWidth="1" min="7425" max="7425" style="93" width="5.125"/>
-    <col customWidth="1" min="7426" max="7433" style="93" width="9.625"/>
-    <col customWidth="1" min="7434" max="7434" style="93" width="5.125"/>
-    <col min="7435" max="7436" style="93" width="9"/>
-    <col customWidth="1" min="7437" max="7437" style="93" width="22.75"/>
-    <col customWidth="1" min="7438" max="7444" style="93" width="13.625"/>
-    <col min="7445" max="7680" style="93" width="9"/>
-    <col customWidth="1" min="7681" max="7681" style="93" width="5.125"/>
-    <col customWidth="1" min="7682" max="7689" style="93" width="9.625"/>
-    <col customWidth="1" min="7690" max="7690" style="93" width="5.125"/>
-    <col min="7691" max="7692" style="93" width="9"/>
-    <col customWidth="1" min="7693" max="7693" style="93" width="22.75"/>
-    <col customWidth="1" min="7694" max="7700" style="93" width="13.625"/>
-    <col min="7701" max="7936" style="93" width="9"/>
-    <col customWidth="1" min="7937" max="7937" style="93" width="5.125"/>
-    <col customWidth="1" min="7938" max="7945" style="93" width="9.625"/>
-    <col customWidth="1" min="7946" max="7946" style="93" width="5.125"/>
-    <col min="7947" max="7948" style="93" width="9"/>
-    <col customWidth="1" min="7949" max="7949" style="93" width="22.75"/>
-    <col customWidth="1" min="7950" max="7956" style="93" width="13.625"/>
-    <col min="7957" max="8192" style="93" width="9"/>
-    <col customWidth="1" min="8193" max="8193" style="93" width="5.125"/>
-    <col customWidth="1" min="8194" max="8201" style="93" width="9.625"/>
-    <col customWidth="1" min="8202" max="8202" style="93" width="5.125"/>
-    <col min="8203" max="8204" style="93" width="9"/>
-    <col customWidth="1" min="8205" max="8205" style="93" width="22.75"/>
-    <col customWidth="1" min="8206" max="8212" style="93" width="13.625"/>
-    <col min="8213" max="8448" style="93" width="9"/>
-    <col customWidth="1" min="8449" max="8449" style="93" width="5.125"/>
-    <col customWidth="1" min="8450" max="8457" style="93" width="9.625"/>
-    <col customWidth="1" min="8458" max="8458" style="93" width="5.125"/>
-    <col min="8459" max="8460" style="93" width="9"/>
-    <col customWidth="1" min="8461" max="8461" style="93" width="22.75"/>
-    <col customWidth="1" min="8462" max="8468" style="93" width="13.625"/>
-    <col min="8469" max="8704" style="93" width="9"/>
-    <col customWidth="1" min="8705" max="8705" style="93" width="5.125"/>
-    <col customWidth="1" min="8706" max="8713" style="93" width="9.625"/>
-    <col customWidth="1" min="8714" max="8714" style="93" width="5.125"/>
-    <col min="8715" max="8716" style="93" width="9"/>
-    <col customWidth="1" min="8717" max="8717" style="93" width="22.75"/>
-    <col customWidth="1" min="8718" max="8724" style="93" width="13.625"/>
-    <col min="8725" max="8960" style="93" width="9"/>
-    <col customWidth="1" min="8961" max="8961" style="93" width="5.125"/>
-    <col customWidth="1" min="8962" max="8969" style="93" width="9.625"/>
-    <col customWidth="1" min="8970" max="8970" style="93" width="5.125"/>
-    <col min="8971" max="8972" style="93" width="9"/>
-    <col customWidth="1" min="8973" max="8973" style="93" width="22.75"/>
-    <col customWidth="1" min="8974" max="8980" style="93" width="13.625"/>
-    <col min="8981" max="9216" style="93" width="9"/>
-    <col customWidth="1" min="9217" max="9217" style="93" width="5.125"/>
-    <col customWidth="1" min="9218" max="9225" style="93" width="9.625"/>
-    <col customWidth="1" min="9226" max="9226" style="93" width="5.125"/>
-    <col min="9227" max="9228" style="93" width="9"/>
-    <col customWidth="1" min="9229" max="9229" style="93" width="22.75"/>
-    <col customWidth="1" min="9230" max="9236" style="93" width="13.625"/>
-    <col min="9237" max="9472" style="93" width="9"/>
-    <col customWidth="1" min="9473" max="9473" style="93" width="5.125"/>
-    <col customWidth="1" min="9474" max="9481" style="93" width="9.625"/>
-    <col customWidth="1" min="9482" max="9482" style="93" width="5.125"/>
-    <col min="9483" max="9484" style="93" width="9"/>
-    <col customWidth="1" min="9485" max="9485" style="93" width="22.75"/>
-    <col customWidth="1" min="9486" max="9492" style="93" width="13.625"/>
-    <col min="9493" max="9728" style="93" width="9"/>
-    <col customWidth="1" min="9729" max="9729" style="93" width="5.125"/>
-    <col customWidth="1" min="9730" max="9737" style="93" width="9.625"/>
-    <col customWidth="1" min="9738" max="9738" style="93" width="5.125"/>
-    <col min="9739" max="9740" style="93" width="9"/>
-    <col customWidth="1" min="9741" max="9741" style="93" width="22.75"/>
-    <col customWidth="1" min="9742" max="9748" style="93" width="13.625"/>
-    <col min="9749" max="9984" style="93" width="9"/>
-    <col customWidth="1" min="9985" max="9985" style="93" width="5.125"/>
-    <col customWidth="1" min="9986" max="9993" style="93" width="9.625"/>
-    <col customWidth="1" min="9994" max="9994" style="93" width="5.125"/>
-    <col min="9995" max="9996" style="93" width="9"/>
-    <col customWidth="1" min="9997" max="9997" style="93" width="22.75"/>
-    <col customWidth="1" min="9998" max="10004" style="93" width="13.625"/>
-    <col min="10005" max="10240" style="93" width="9"/>
-    <col customWidth="1" min="10241" max="10241" style="93" width="5.125"/>
-    <col customWidth="1" min="10242" max="10249" style="93" width="9.625"/>
-    <col customWidth="1" min="10250" max="10250" style="93" width="5.125"/>
-    <col min="10251" max="10252" style="93" width="9"/>
-    <col customWidth="1" min="10253" max="10253" style="93" width="22.75"/>
-    <col customWidth="1" min="10254" max="10260" style="93" width="13.625"/>
-    <col min="10261" max="10496" style="93" width="9"/>
-    <col customWidth="1" min="10497" max="10497" style="93" width="5.125"/>
-    <col customWidth="1" min="10498" max="10505" style="93" width="9.625"/>
-    <col customWidth="1" min="10506" max="10506" style="93" width="5.125"/>
-    <col min="10507" max="10508" style="93" width="9"/>
-    <col customWidth="1" min="10509" max="10509" style="93" width="22.75"/>
-    <col customWidth="1" min="10510" max="10516" style="93" width="13.625"/>
-    <col min="10517" max="10752" style="93" width="9"/>
-    <col customWidth="1" min="10753" max="10753" style="93" width="5.125"/>
-    <col customWidth="1" min="10754" max="10761" style="93" width="9.625"/>
-    <col customWidth="1" min="10762" max="10762" style="93" width="5.125"/>
-    <col min="10763" max="10764" style="93" width="9"/>
-    <col customWidth="1" min="10765" max="10765" style="93" width="22.75"/>
-    <col customWidth="1" min="10766" max="10772" style="93" width="13.625"/>
-    <col min="10773" max="11008" style="93" width="9"/>
-    <col customWidth="1" min="11009" max="11009" style="93" width="5.125"/>
-    <col customWidth="1" min="11010" max="11017" style="93" width="9.625"/>
-    <col customWidth="1" min="11018" max="11018" style="93" width="5.125"/>
-    <col min="11019" max="11020" style="93" width="9"/>
-    <col customWidth="1" min="11021" max="11021" style="93" width="22.75"/>
-    <col customWidth="1" min="11022" max="11028" style="93" width="13.625"/>
-    <col min="11029" max="11264" style="93" width="9"/>
-    <col customWidth="1" min="11265" max="11265" style="93" width="5.125"/>
-    <col customWidth="1" min="11266" max="11273" style="93" width="9.625"/>
-    <col customWidth="1" min="11274" max="11274" style="93" width="5.125"/>
-    <col min="11275" max="11276" style="93" width="9"/>
-    <col customWidth="1" min="11277" max="11277" style="93" width="22.75"/>
-    <col customWidth="1" min="11278" max="11284" style="93" width="13.625"/>
-    <col min="11285" max="11520" style="93" width="9"/>
-    <col customWidth="1" min="11521" max="11521" style="93" width="5.125"/>
-    <col customWidth="1" min="11522" max="11529" style="93" width="9.625"/>
-    <col customWidth="1" min="11530" max="11530" style="93" width="5.125"/>
-    <col min="11531" max="11532" style="93" width="9"/>
-    <col customWidth="1" min="11533" max="11533" style="93" width="22.75"/>
-    <col customWidth="1" min="11534" max="11540" style="93" width="13.625"/>
-    <col min="11541" max="11776" style="93" width="9"/>
-    <col customWidth="1" min="11777" max="11777" style="93" width="5.125"/>
-    <col customWidth="1" min="11778" max="11785" style="93" width="9.625"/>
-    <col customWidth="1" min="11786" max="11786" style="93" width="5.125"/>
-    <col min="11787" max="11788" style="93" width="9"/>
-    <col customWidth="1" min="11789" max="11789" style="93" width="22.75"/>
-    <col customWidth="1" min="11790" max="11796" style="93" width="13.625"/>
-    <col min="11797" max="12032" style="93" width="9"/>
-    <col customWidth="1" min="12033" max="12033" style="93" width="5.125"/>
-    <col customWidth="1" min="12034" max="12041" style="93" width="9.625"/>
-    <col customWidth="1" min="12042" max="12042" style="93" width="5.125"/>
-    <col min="12043" max="12044" style="93" width="9"/>
-    <col customWidth="1" min="12045" max="12045" style="93" width="22.75"/>
-    <col customWidth="1" min="12046" max="12052" style="93" width="13.625"/>
-    <col min="12053" max="12288" style="93" width="9"/>
-    <col customWidth="1" min="12289" max="12289" style="93" width="5.125"/>
-    <col customWidth="1" min="12290" max="12297" style="93" width="9.625"/>
-    <col customWidth="1" min="12298" max="12298" style="93" width="5.125"/>
-    <col min="12299" max="12300" style="93" width="9"/>
-    <col customWidth="1" min="12301" max="12301" style="93" width="22.75"/>
-    <col customWidth="1" min="12302" max="12308" style="93" width="13.625"/>
-    <col min="12309" max="12544" style="93" width="9"/>
-    <col customWidth="1" min="12545" max="12545" style="93" width="5.125"/>
-    <col customWidth="1" min="12546" max="12553" style="93" width="9.625"/>
-    <col customWidth="1" min="12554" max="12554" style="93" width="5.125"/>
-    <col min="12555" max="12556" style="93" width="9"/>
-    <col customWidth="1" min="12557" max="12557" style="93" width="22.75"/>
-    <col customWidth="1" min="12558" max="12564" style="93" width="13.625"/>
-    <col min="12565" max="12800" style="93" width="9"/>
-    <col customWidth="1" min="12801" max="12801" style="93" width="5.125"/>
-    <col customWidth="1" min="12802" max="12809" style="93" width="9.625"/>
-    <col customWidth="1" min="12810" max="12810" style="93" width="5.125"/>
-    <col min="12811" max="12812" style="93" width="9"/>
-    <col customWidth="1" min="12813" max="12813" style="93" width="22.75"/>
-    <col customWidth="1" min="12814" max="12820" style="93" width="13.625"/>
-    <col min="12821" max="13056" style="93" width="9"/>
-    <col customWidth="1" min="13057" max="13057" style="93" width="5.125"/>
-    <col customWidth="1" min="13058" max="13065" style="93" width="9.625"/>
-    <col customWidth="1" min="13066" max="13066" style="93" width="5.125"/>
-    <col min="13067" max="13068" style="93" width="9"/>
-    <col customWidth="1" min="13069" max="13069" style="93" width="22.75"/>
-    <col customWidth="1" min="13070" max="13076" style="93" width="13.625"/>
-    <col min="13077" max="13312" style="93" width="9"/>
-    <col customWidth="1" min="13313" max="13313" style="93" width="5.125"/>
-    <col customWidth="1" min="13314" max="13321" style="93" width="9.625"/>
-    <col customWidth="1" min="13322" max="13322" style="93" width="5.125"/>
-    <col min="13323" max="13324" style="93" width="9"/>
-    <col customWidth="1" min="13325" max="13325" style="93" width="22.75"/>
-    <col customWidth="1" min="13326" max="13332" style="93" width="13.625"/>
-    <col min="13333" max="13568" style="93" width="9"/>
-    <col customWidth="1" min="13569" max="13569" style="93" width="5.125"/>
-    <col customWidth="1" min="13570" max="13577" style="93" width="9.625"/>
-    <col customWidth="1" min="13578" max="13578" style="93" width="5.125"/>
-    <col min="13579" max="13580" style="93" width="9"/>
-    <col customWidth="1" min="13581" max="13581" style="93" width="22.75"/>
-    <col customWidth="1" min="13582" max="13588" style="93" width="13.625"/>
-    <col min="13589" max="13824" style="93" width="9"/>
-    <col customWidth="1" min="13825" max="13825" style="93" width="5.125"/>
-    <col customWidth="1" min="13826" max="13833" style="93" width="9.625"/>
-    <col customWidth="1" min="13834" max="13834" style="93" width="5.125"/>
-    <col min="13835" max="13836" style="93" width="9"/>
-    <col customWidth="1" min="13837" max="13837" style="93" width="22.75"/>
-    <col customWidth="1" min="13838" max="13844" style="93" width="13.625"/>
-    <col min="13845" max="14080" style="93" width="9"/>
-    <col customWidth="1" min="14081" max="14081" style="93" width="5.125"/>
-    <col customWidth="1" min="14082" max="14089" style="93" width="9.625"/>
-    <col customWidth="1" min="14090" max="14090" style="93" width="5.125"/>
-    <col min="14091" max="14092" style="93" width="9"/>
-    <col customWidth="1" min="14093" max="14093" style="93" width="22.75"/>
-    <col customWidth="1" min="14094" max="14100" style="93" width="13.625"/>
-    <col min="14101" max="14336" style="93" width="9"/>
-    <col customWidth="1" min="14337" max="14337" style="93" width="5.125"/>
-    <col customWidth="1" min="14338" max="14345" style="93" width="9.625"/>
-    <col customWidth="1" min="14346" max="14346" style="93" width="5.125"/>
-    <col min="14347" max="14348" style="93" width="9"/>
-    <col customWidth="1" min="14349" max="14349" style="93" width="22.75"/>
-    <col customWidth="1" min="14350" max="14356" style="93" width="13.625"/>
-    <col min="14357" max="14592" style="93" width="9"/>
-    <col customWidth="1" min="14593" max="14593" style="93" width="5.125"/>
-    <col customWidth="1" min="14594" max="14601" style="93" width="9.625"/>
-    <col customWidth="1" min="14602" max="14602" style="93" width="5.125"/>
-    <col min="14603" max="14604" style="93" width="9"/>
-    <col customWidth="1" min="14605" max="14605" style="93" width="22.75"/>
-    <col customWidth="1" min="14606" max="14612" style="93" width="13.625"/>
-    <col min="14613" max="14848" style="93" width="9"/>
-    <col customWidth="1" min="14849" max="14849" style="93" width="5.125"/>
-    <col customWidth="1" min="14850" max="14857" style="93" width="9.625"/>
-    <col customWidth="1" min="14858" max="14858" style="93" width="5.125"/>
-    <col min="14859" max="14860" style="93" width="9"/>
-    <col customWidth="1" min="14861" max="14861" style="93" width="22.75"/>
-    <col customWidth="1" min="14862" max="14868" style="93" width="13.625"/>
-    <col min="14869" max="15104" style="93" width="9"/>
-    <col customWidth="1" min="15105" max="15105" style="93" width="5.125"/>
-    <col customWidth="1" min="15106" max="15113" style="93" width="9.625"/>
-    <col customWidth="1" min="15114" max="15114" style="93" width="5.125"/>
-    <col min="15115" max="15116" style="93" width="9"/>
-    <col customWidth="1" min="15117" max="15117" style="93" width="22.75"/>
-    <col customWidth="1" min="15118" max="15124" style="93" width="13.625"/>
-    <col min="15125" max="15360" style="93" width="9"/>
-    <col customWidth="1" min="15361" max="15361" style="93" width="5.125"/>
-    <col customWidth="1" min="15362" max="15369" style="93" width="9.625"/>
-    <col customWidth="1" min="15370" max="15370" style="93" width="5.125"/>
-    <col min="15371" max="15372" style="93" width="9"/>
-    <col customWidth="1" min="15373" max="15373" style="93" width="22.75"/>
-    <col customWidth="1" min="15374" max="15380" style="93" width="13.625"/>
-    <col min="15381" max="15616" style="93" width="9"/>
-    <col customWidth="1" min="15617" max="15617" style="93" width="5.125"/>
-    <col customWidth="1" min="15618" max="15625" style="93" width="9.625"/>
-    <col customWidth="1" min="15626" max="15626" style="93" width="5.125"/>
-    <col min="15627" max="15628" style="93" width="9"/>
-    <col customWidth="1" min="15629" max="15629" style="93" width="22.75"/>
-    <col customWidth="1" min="15630" max="15636" style="93" width="13.625"/>
-    <col min="15637" max="15872" style="93" width="9"/>
-    <col customWidth="1" min="15873" max="15873" style="93" width="5.125"/>
-    <col customWidth="1" min="15874" max="15881" style="93" width="9.625"/>
-    <col customWidth="1" min="15882" max="15882" style="93" width="5.125"/>
-    <col min="15883" max="15884" style="93" width="9"/>
-    <col customWidth="1" min="15885" max="15885" style="93" width="22.75"/>
-    <col customWidth="1" min="15886" max="15892" style="93" width="13.625"/>
-    <col min="15893" max="16128" style="93" width="9"/>
-    <col customWidth="1" min="16129" max="16129" style="93" width="5.125"/>
-    <col customWidth="1" min="16130" max="16137" style="93" width="9.625"/>
-    <col customWidth="1" min="16138" max="16138" style="93" width="5.125"/>
-    <col min="16139" max="16140" style="93" width="9"/>
-    <col customWidth="1" min="16141" max="16141" style="93" width="22.75"/>
-    <col customWidth="1" min="16142" max="16148" style="93" width="13.625"/>
-    <col min="16149" max="16384" style="93" width="9"/>
+    <col customWidth="1" min="1" max="1" style="94" width="5.125"/>
+    <col customWidth="1" min="2" max="9" style="94" width="9.625"/>
+    <col customWidth="1" min="10" max="10" style="94" width="5.125"/>
+    <col min="11" max="12" style="94" width="9"/>
+    <col customWidth="1" min="13" max="13" style="94" width="22.75"/>
+    <col customWidth="1" min="14" max="20" style="94" width="13.625"/>
+    <col min="21" max="256" style="94" width="9"/>
+    <col customWidth="1" min="257" max="257" style="94" width="5.125"/>
+    <col customWidth="1" min="258" max="265" style="94" width="9.625"/>
+    <col customWidth="1" min="266" max="266" style="94" width="5.125"/>
+    <col min="267" max="268" style="94" width="9"/>
+    <col customWidth="1" min="269" max="269" style="94" width="22.75"/>
+    <col customWidth="1" min="270" max="276" style="94" width="13.625"/>
+    <col min="277" max="512" style="94" width="9"/>
+    <col customWidth="1" min="513" max="513" style="94" width="5.125"/>
+    <col customWidth="1" min="514" max="521" style="94" width="9.625"/>
+    <col customWidth="1" min="522" max="522" style="94" width="5.125"/>
+    <col min="523" max="524" style="94" width="9"/>
+    <col customWidth="1" min="525" max="525" style="94" width="22.75"/>
+    <col customWidth="1" min="526" max="532" style="94" width="13.625"/>
+    <col min="533" max="768" style="94" width="9"/>
+    <col customWidth="1" min="769" max="769" style="94" width="5.125"/>
+    <col customWidth="1" min="770" max="777" style="94" width="9.625"/>
+    <col customWidth="1" min="778" max="778" style="94" width="5.125"/>
+    <col min="779" max="780" style="94" width="9"/>
+    <col customWidth="1" min="781" max="781" style="94" width="22.75"/>
+    <col customWidth="1" min="782" max="788" style="94" width="13.625"/>
+    <col min="789" max="1024" style="94" width="9"/>
+    <col customWidth="1" min="1025" max="1025" style="94" width="5.125"/>
+    <col customWidth="1" min="1026" max="1033" style="94" width="9.625"/>
+    <col customWidth="1" min="1034" max="1034" style="94" width="5.125"/>
+    <col min="1035" max="1036" style="94" width="9"/>
+    <col customWidth="1" min="1037" max="1037" style="94" width="22.75"/>
+    <col customWidth="1" min="1038" max="1044" style="94" width="13.625"/>
+    <col min="1045" max="1280" style="94" width="9"/>
+    <col customWidth="1" min="1281" max="1281" style="94" width="5.125"/>
+    <col customWidth="1" min="1282" max="1289" style="94" width="9.625"/>
+    <col customWidth="1" min="1290" max="1290" style="94" width="5.125"/>
+    <col min="1291" max="1292" style="94" width="9"/>
+    <col customWidth="1" min="1293" max="1293" style="94" width="22.75"/>
+    <col customWidth="1" min="1294" max="1300" style="94" width="13.625"/>
+    <col min="1301" max="1536" style="94" width="9"/>
+    <col customWidth="1" min="1537" max="1537" style="94" width="5.125"/>
+    <col customWidth="1" min="1538" max="1545" style="94" width="9.625"/>
+    <col customWidth="1" min="1546" max="1546" style="94" width="5.125"/>
+    <col min="1547" max="1548" style="94" width="9"/>
+    <col customWidth="1" min="1549" max="1549" style="94" width="22.75"/>
+    <col customWidth="1" min="1550" max="1556" style="94" width="13.625"/>
+    <col min="1557" max="1792" style="94" width="9"/>
+    <col customWidth="1" min="1793" max="1793" style="94" width="5.125"/>
+    <col customWidth="1" min="1794" max="1801" style="94" width="9.625"/>
+    <col customWidth="1" min="1802" max="1802" style="94" width="5.125"/>
+    <col min="1803" max="1804" style="94" width="9"/>
+    <col customWidth="1" min="1805" max="1805" style="94" width="22.75"/>
+    <col customWidth="1" min="1806" max="1812" style="94" width="13.625"/>
+    <col min="1813" max="2048" style="94" width="9"/>
+    <col customWidth="1" min="2049" max="2049" style="94" width="5.125"/>
+    <col customWidth="1" min="2050" max="2057" style="94" width="9.625"/>
+    <col customWidth="1" min="2058" max="2058" style="94" width="5.125"/>
+    <col min="2059" max="2060" style="94" width="9"/>
+    <col customWidth="1" min="2061" max="2061" style="94" width="22.75"/>
+    <col customWidth="1" min="2062" max="2068" style="94" width="13.625"/>
+    <col min="2069" max="2304" style="94" width="9"/>
+    <col customWidth="1" min="2305" max="2305" style="94" width="5.125"/>
+    <col customWidth="1" min="2306" max="2313" style="94" width="9.625"/>
+    <col customWidth="1" min="2314" max="2314" style="94" width="5.125"/>
+    <col min="2315" max="2316" style="94" width="9"/>
+    <col customWidth="1" min="2317" max="2317" style="94" width="22.75"/>
+    <col customWidth="1" min="2318" max="2324" style="94" width="13.625"/>
+    <col min="2325" max="2560" style="94" width="9"/>
+    <col customWidth="1" min="2561" max="2561" style="94" width="5.125"/>
+    <col customWidth="1" min="2562" max="2569" style="94" width="9.625"/>
+    <col customWidth="1" min="2570" max="2570" style="94" width="5.125"/>
+    <col min="2571" max="2572" style="94" width="9"/>
+    <col customWidth="1" min="2573" max="2573" style="94" width="22.75"/>
+    <col customWidth="1" min="2574" max="2580" style="94" width="13.625"/>
+    <col min="2581" max="2816" style="94" width="9"/>
+    <col customWidth="1" min="2817" max="2817" style="94" width="5.125"/>
+    <col customWidth="1" min="2818" max="2825" style="94" width="9.625"/>
+    <col customWidth="1" min="2826" max="2826" style="94" width="5.125"/>
+    <col min="2827" max="2828" style="94" width="9"/>
+    <col customWidth="1" min="2829" max="2829" style="94" width="22.75"/>
+    <col customWidth="1" min="2830" max="2836" style="94" width="13.625"/>
+    <col min="2837" max="3072" style="94" width="9"/>
+    <col customWidth="1" min="3073" max="3073" style="94" width="5.125"/>
+    <col customWidth="1" min="3074" max="3081" style="94" width="9.625"/>
+    <col customWidth="1" min="3082" max="3082" style="94" width="5.125"/>
+    <col min="3083" max="3084" style="94" width="9"/>
+    <col customWidth="1" min="3085" max="3085" style="94" width="22.75"/>
+    <col customWidth="1" min="3086" max="3092" style="94" width="13.625"/>
+    <col min="3093" max="3328" style="94" width="9"/>
+    <col customWidth="1" min="3329" max="3329" style="94" width="5.125"/>
+    <col customWidth="1" min="3330" max="3337" style="94" width="9.625"/>
+    <col customWidth="1" min="3338" max="3338" style="94" width="5.125"/>
+    <col min="3339" max="3340" style="94" width="9"/>
+    <col customWidth="1" min="3341" max="3341" style="94" width="22.75"/>
+    <col customWidth="1" min="3342" max="3348" style="94" width="13.625"/>
+    <col min="3349" max="3584" style="94" width="9"/>
+    <col customWidth="1" min="3585" max="3585" style="94" width="5.125"/>
+    <col customWidth="1" min="3586" max="3593" style="94" width="9.625"/>
+    <col customWidth="1" min="3594" max="3594" style="94" width="5.125"/>
+    <col min="3595" max="3596" style="94" width="9"/>
+    <col customWidth="1" min="3597" max="3597" style="94" width="22.75"/>
+    <col customWidth="1" min="3598" max="3604" style="94" width="13.625"/>
+    <col min="3605" max="3840" style="94" width="9"/>
+    <col customWidth="1" min="3841" max="3841" style="94" width="5.125"/>
+    <col customWidth="1" min="3842" max="3849" style="94" width="9.625"/>
+    <col customWidth="1" min="3850" max="3850" style="94" width="5.125"/>
+    <col min="3851" max="3852" style="94" width="9"/>
+    <col customWidth="1" min="3853" max="3853" style="94" width="22.75"/>
+    <col customWidth="1" min="3854" max="3860" style="94" width="13.625"/>
+    <col min="3861" max="4096" style="94" width="9"/>
+    <col customWidth="1" min="4097" max="4097" style="94" width="5.125"/>
+    <col customWidth="1" min="4098" max="4105" style="94" width="9.625"/>
+    <col customWidth="1" min="4106" max="4106" style="94" width="5.125"/>
+    <col min="4107" max="4108" style="94" width="9"/>
+    <col customWidth="1" min="4109" max="4109" style="94" width="22.75"/>
+    <col customWidth="1" min="4110" max="4116" style="94" width="13.625"/>
+    <col min="4117" max="4352" style="94" width="9"/>
+    <col customWidth="1" min="4353" max="4353" style="94" width="5.125"/>
+    <col customWidth="1" min="4354" max="4361" style="94" width="9.625"/>
+    <col customWidth="1" min="4362" max="4362" style="94" width="5.125"/>
+    <col min="4363" max="4364" style="94" width="9"/>
+    <col customWidth="1" min="4365" max="4365" style="94" width="22.75"/>
+    <col customWidth="1" min="4366" max="4372" style="94" width="13.625"/>
+    <col min="4373" max="4608" style="94" width="9"/>
+    <col customWidth="1" min="4609" max="4609" style="94" width="5.125"/>
+    <col customWidth="1" min="4610" max="4617" style="94" width="9.625"/>
+    <col customWidth="1" min="4618" max="4618" style="94" width="5.125"/>
+    <col min="4619" max="4620" style="94" width="9"/>
+    <col customWidth="1" min="4621" max="4621" style="94" width="22.75"/>
+    <col customWidth="1" min="4622" max="4628" style="94" width="13.625"/>
+    <col min="4629" max="4864" style="94" width="9"/>
+    <col customWidth="1" min="4865" max="4865" style="94" width="5.125"/>
+    <col customWidth="1" min="4866" max="4873" style="94" width="9.625"/>
+    <col customWidth="1" min="4874" max="4874" style="94" width="5.125"/>
+    <col min="4875" max="4876" style="94" width="9"/>
+    <col customWidth="1" min="4877" max="4877" style="94" width="22.75"/>
+    <col customWidth="1" min="4878" max="4884" style="94" width="13.625"/>
+    <col min="4885" max="5120" style="94" width="9"/>
+    <col customWidth="1" min="5121" max="5121" style="94" width="5.125"/>
+    <col customWidth="1" min="5122" max="5129" style="94" width="9.625"/>
+    <col customWidth="1" min="5130" max="5130" style="94" width="5.125"/>
+    <col min="5131" max="5132" style="94" width="9"/>
+    <col customWidth="1" min="5133" max="5133" style="94" width="22.75"/>
+    <col customWidth="1" min="5134" max="5140" style="94" width="13.625"/>
+    <col min="5141" max="5376" style="94" width="9"/>
+    <col customWidth="1" min="5377" max="5377" style="94" width="5.125"/>
+    <col customWidth="1" min="5378" max="5385" style="94" width="9.625"/>
+    <col customWidth="1" min="5386" max="5386" style="94" width="5.125"/>
+    <col min="5387" max="5388" style="94" width="9"/>
+    <col customWidth="1" min="5389" max="5389" style="94" width="22.75"/>
+    <col customWidth="1" min="5390" max="5396" style="94" width="13.625"/>
+    <col min="5397" max="5632" style="94" width="9"/>
+    <col customWidth="1" min="5633" max="5633" style="94" width="5.125"/>
+    <col customWidth="1" min="5634" max="5641" style="94" width="9.625"/>
+    <col customWidth="1" min="5642" max="5642" style="94" width="5.125"/>
+    <col min="5643" max="5644" style="94" width="9"/>
+    <col customWidth="1" min="5645" max="5645" style="94" width="22.75"/>
+    <col customWidth="1" min="5646" max="5652" style="94" width="13.625"/>
+    <col min="5653" max="5888" style="94" width="9"/>
+    <col customWidth="1" min="5889" max="5889" style="94" width="5.125"/>
+    <col customWidth="1" min="5890" max="5897" style="94" width="9.625"/>
+    <col customWidth="1" min="5898" max="5898" style="94" width="5.125"/>
+    <col min="5899" max="5900" style="94" width="9"/>
+    <col customWidth="1" min="5901" max="5901" style="94" width="22.75"/>
+    <col customWidth="1" min="5902" max="5908" style="94" width="13.625"/>
+    <col min="5909" max="6144" style="94" width="9"/>
+    <col customWidth="1" min="6145" max="6145" style="94" width="5.125"/>
+    <col customWidth="1" min="6146" max="6153" style="94" width="9.625"/>
+    <col customWidth="1" min="6154" max="6154" style="94" width="5.125"/>
+    <col min="6155" max="6156" style="94" width="9"/>
+    <col customWidth="1" min="6157" max="6157" style="94" width="22.75"/>
+    <col customWidth="1" min="6158" max="6164" style="94" width="13.625"/>
+    <col min="6165" max="6400" style="94" width="9"/>
+    <col customWidth="1" min="6401" max="6401" style="94" width="5.125"/>
+    <col customWidth="1" min="6402" max="6409" style="94" width="9.625"/>
+    <col customWidth="1" min="6410" max="6410" style="94" width="5.125"/>
+    <col min="6411" max="6412" style="94" width="9"/>
+    <col customWidth="1" min="6413" max="6413" style="94" width="22.75"/>
+    <col customWidth="1" min="6414" max="6420" style="94" width="13.625"/>
+    <col min="6421" max="6656" style="94" width="9"/>
+    <col customWidth="1" min="6657" max="6657" style="94" width="5.125"/>
+    <col customWidth="1" min="6658" max="6665" style="94" width="9.625"/>
+    <col customWidth="1" min="6666" max="6666" style="94" width="5.125"/>
+    <col min="6667" max="6668" style="94" width="9"/>
+    <col customWidth="1" min="6669" max="6669" style="94" width="22.75"/>
+    <col customWidth="1" min="6670" max="6676" style="94" width="13.625"/>
+    <col min="6677" max="6912" style="94" width="9"/>
+    <col customWidth="1" min="6913" max="6913" style="94" width="5.125"/>
+    <col customWidth="1" min="6914" max="6921" style="94" width="9.625"/>
+    <col customWidth="1" min="6922" max="6922" style="94" width="5.125"/>
+    <col min="6923" max="6924" style="94" width="9"/>
+    <col customWidth="1" min="6925" max="6925" style="94" width="22.75"/>
+    <col customWidth="1" min="6926" max="6932" style="94" width="13.625"/>
+    <col min="6933" max="7168" style="94" width="9"/>
+    <col customWidth="1" min="7169" max="7169" style="94" width="5.125"/>
+    <col customWidth="1" min="7170" max="7177" style="94" width="9.625"/>
+    <col customWidth="1" min="7178" max="7178" style="94" width="5.125"/>
+    <col min="7179" max="7180" style="94" width="9"/>
+    <col customWidth="1" min="7181" max="7181" style="94" width="22.75"/>
+    <col customWidth="1" min="7182" max="7188" style="94" width="13.625"/>
+    <col min="7189" max="7424" style="94" width="9"/>
+    <col customWidth="1" min="7425" max="7425" style="94" width="5.125"/>
+    <col customWidth="1" min="7426" max="7433" style="94" width="9.625"/>
+    <col customWidth="1" min="7434" max="7434" style="94" width="5.125"/>
+    <col min="7435" max="7436" style="94" width="9"/>
+    <col customWidth="1" min="7437" max="7437" style="94" width="22.75"/>
+    <col customWidth="1" min="7438" max="7444" style="94" width="13.625"/>
+    <col min="7445" max="7680" style="94" width="9"/>
+    <col customWidth="1" min="7681" max="7681" style="94" width="5.125"/>
+    <col customWidth="1" min="7682" max="7689" style="94" width="9.625"/>
+    <col customWidth="1" min="7690" max="7690" style="94" width="5.125"/>
+    <col min="7691" max="7692" style="94" width="9"/>
+    <col customWidth="1" min="7693" max="7693" style="94" width="22.75"/>
+    <col customWidth="1" min="7694" max="7700" style="94" width="13.625"/>
+    <col min="7701" max="7936" style="94" width="9"/>
+    <col customWidth="1" min="7937" max="7937" style="94" width="5.125"/>
+    <col customWidth="1" min="7938" max="7945" style="94" width="9.625"/>
+    <col customWidth="1" min="7946" max="7946" style="94" width="5.125"/>
+    <col min="7947" max="7948" style="94" width="9"/>
+    <col customWidth="1" min="7949" max="7949" style="94" width="22.75"/>
+    <col customWidth="1" min="7950" max="7956" style="94" width="13.625"/>
+    <col min="7957" max="8192" style="94" width="9"/>
+    <col customWidth="1" min="8193" max="8193" style="94" width="5.125"/>
+    <col customWidth="1" min="8194" max="8201" style="94" width="9.625"/>
+    <col customWidth="1" min="8202" max="8202" style="94" width="5.125"/>
+    <col min="8203" max="8204" style="94" width="9"/>
+    <col customWidth="1" min="8205" max="8205" style="94" width="22.75"/>
+    <col customWidth="1" min="8206" max="8212" style="94" width="13.625"/>
+    <col min="8213" max="8448" style="94" width="9"/>
+    <col customWidth="1" min="8449" max="8449" style="94" width="5.125"/>
+    <col customWidth="1" min="8450" max="8457" style="94" width="9.625"/>
+    <col customWidth="1" min="8458" max="8458" style="94" width="5.125"/>
+    <col min="8459" max="8460" style="94" width="9"/>
+    <col customWidth="1" min="8461" max="8461" style="94" width="22.75"/>
+    <col customWidth="1" min="8462" max="8468" style="94" width="13.625"/>
+    <col min="8469" max="8704" style="94" width="9"/>
+    <col customWidth="1" min="8705" max="8705" style="94" width="5.125"/>
+    <col customWidth="1" min="8706" max="8713" style="94" width="9.625"/>
+    <col customWidth="1" min="8714" max="8714" style="94" width="5.125"/>
+    <col min="8715" max="8716" style="94" width="9"/>
+    <col customWidth="1" min="8717" max="8717" style="94" width="22.75"/>
+    <col customWidth="1" min="8718" max="8724" style="94" width="13.625"/>
+    <col min="8725" max="8960" style="94" width="9"/>
+    <col customWidth="1" min="8961" max="8961" style="94" width="5.125"/>
+    <col customWidth="1" min="8962" max="8969" style="94" width="9.625"/>
+    <col customWidth="1" min="8970" max="8970" style="94" width="5.125"/>
+    <col min="8971" max="8972" style="94" width="9"/>
+    <col customWidth="1" min="8973" max="8973" style="94" width="22.75"/>
+    <col customWidth="1" min="8974" max="8980" style="94" width="13.625"/>
+    <col min="8981" max="9216" style="94" width="9"/>
+    <col customWidth="1" min="9217" max="9217" style="94" width="5.125"/>
+    <col customWidth="1" min="9218" max="9225" style="94" width="9.625"/>
+    <col customWidth="1" min="9226" max="9226" style="94" width="5.125"/>
+    <col min="9227" max="9228" style="94" width="9"/>
+    <col customWidth="1" min="9229" max="9229" style="94" width="22.75"/>
+    <col customWidth="1" min="9230" max="9236" style="94" width="13.625"/>
+    <col min="9237" max="9472" style="94" width="9"/>
+    <col customWidth="1" min="9473" max="9473" style="94" width="5.125"/>
+    <col customWidth="1" min="9474" max="9481" style="94" width="9.625"/>
+    <col customWidth="1" min="9482" max="9482" style="94" width="5.125"/>
+    <col min="9483" max="9484" style="94" width="9"/>
+    <col customWidth="1" min="9485" max="9485" style="94" width="22.75"/>
+    <col customWidth="1" min="9486" max="9492" style="94" width="13.625"/>
+    <col min="9493" max="9728" style="94" width="9"/>
+    <col customWidth="1" min="9729" max="9729" style="94" width="5.125"/>
+    <col customWidth="1" min="9730" max="9737" style="94" width="9.625"/>
+    <col customWidth="1" min="9738" max="9738" style="94" width="5.125"/>
+    <col min="9739" max="9740" style="94" width="9"/>
+    <col customWidth="1" min="9741" max="9741" style="94" width="22.75"/>
+    <col customWidth="1" min="9742" max="9748" style="94" width="13.625"/>
+    <col min="9749" max="9984" style="94" width="9"/>
+    <col customWidth="1" min="9985" max="9985" style="94" width="5.125"/>
+    <col customWidth="1" min="9986" max="9993" style="94" width="9.625"/>
+    <col customWidth="1" min="9994" max="9994" style="94" width="5.125"/>
+    <col min="9995" max="9996" style="94" width="9"/>
+    <col customWidth="1" min="9997" max="9997" style="94" width="22.75"/>
+    <col customWidth="1" min="9998" max="10004" style="94" width="13.625"/>
+    <col min="10005" max="10240" style="94" width="9"/>
+    <col customWidth="1" min="10241" max="10241" style="94" width="5.125"/>
+    <col customWidth="1" min="10242" max="10249" style="94" width="9.625"/>
+    <col customWidth="1" min="10250" max="10250" style="94" width="5.125"/>
+    <col min="10251" max="10252" style="94" width="9"/>
+    <col customWidth="1" min="10253" max="10253" style="94" width="22.75"/>
+    <col customWidth="1" min="10254" max="10260" style="94" width="13.625"/>
+    <col min="10261" max="10496" style="94" width="9"/>
+    <col customWidth="1" min="10497" max="10497" style="94" width="5.125"/>
+    <col customWidth="1" min="10498" max="10505" style="94" width="9.625"/>
+    <col customWidth="1" min="10506" max="10506" style="94" width="5.125"/>
+    <col min="10507" max="10508" style="94" width="9"/>
+    <col customWidth="1" min="10509" max="10509" style="94" width="22.75"/>
+    <col customWidth="1" min="10510" max="10516" style="94" width="13.625"/>
+    <col min="10517" max="10752" style="94" width="9"/>
+    <col customWidth="1" min="10753" max="10753" style="94" width="5.125"/>
+    <col customWidth="1" min="10754" max="10761" style="94" width="9.625"/>
+    <col customWidth="1" min="10762" max="10762" style="94" width="5.125"/>
+    <col min="10763" max="10764" style="94" width="9"/>
+    <col customWidth="1" min="10765" max="10765" style="94" width="22.75"/>
+    <col customWidth="1" min="10766" max="10772" style="94" width="13.625"/>
+    <col min="10773" max="11008" style="94" width="9"/>
+    <col customWidth="1" min="11009" max="11009" style="94" width="5.125"/>
+    <col customWidth="1" min="11010" max="11017" style="94" width="9.625"/>
+    <col customWidth="1" min="11018" max="11018" style="94" width="5.125"/>
+    <col min="11019" max="11020" style="94" width="9"/>
+    <col customWidth="1" min="11021" max="11021" style="94" width="22.75"/>
+    <col customWidth="1" min="11022" max="11028" style="94" width="13.625"/>
+    <col min="11029" max="11264" style="94" width="9"/>
+    <col customWidth="1" min="11265" max="11265" style="94" width="5.125"/>
+    <col customWidth="1" min="11266" max="11273" style="94" width="9.625"/>
+    <col customWidth="1" min="11274" max="11274" style="94" width="5.125"/>
+    <col min="11275" max="11276" style="94" width="9"/>
+    <col customWidth="1" min="11277" max="11277" style="94" width="22.75"/>
+    <col customWidth="1" min="11278" max="11284" style="94" width="13.625"/>
+    <col min="11285" max="11520" style="94" width="9"/>
+    <col customWidth="1" min="11521" max="11521" style="94" width="5.125"/>
+    <col customWidth="1" min="11522" max="11529" style="94" width="9.625"/>
+    <col customWidth="1" min="11530" max="11530" style="94" width="5.125"/>
+    <col min="11531" max="11532" style="94" width="9"/>
+    <col customWidth="1" min="11533" max="11533" style="94" width="22.75"/>
+    <col customWidth="1" min="11534" max="11540" style="94" width="13.625"/>
+    <col min="11541" max="11776" style="94" width="9"/>
+    <col customWidth="1" min="11777" max="11777" style="94" width="5.125"/>
+    <col customWidth="1" min="11778" max="11785" style="94" width="9.625"/>
+    <col customWidth="1" min="11786" max="11786" style="94" width="5.125"/>
+    <col min="11787" max="11788" style="94" width="9"/>
+    <col customWidth="1" min="11789" max="11789" style="94" width="22.75"/>
+    <col customWidth="1" min="11790" max="11796" style="94" width="13.625"/>
+    <col min="11797" max="12032" style="94" width="9"/>
+    <col customWidth="1" min="12033" max="12033" style="94" width="5.125"/>
+    <col customWidth="1" min="12034" max="12041" style="94" width="9.625"/>
+    <col customWidth="1" min="12042" max="12042" style="94" width="5.125"/>
+    <col min="12043" max="12044" style="94" width="9"/>
+    <col customWidth="1" min="12045" max="12045" style="94" width="22.75"/>
+    <col customWidth="1" min="12046" max="12052" style="94" width="13.625"/>
+    <col min="12053" max="12288" style="94" width="9"/>
+    <col customWidth="1" min="12289" max="12289" style="94" width="5.125"/>
+    <col customWidth="1" min="12290" max="12297" style="94" width="9.625"/>
+    <col customWidth="1" min="12298" max="12298" style="94" width="5.125"/>
+    <col min="12299" max="12300" style="94" width="9"/>
+    <col customWidth="1" min="12301" max="12301" style="94" width="22.75"/>
+    <col customWidth="1" min="12302" max="12308" style="94" width="13.625"/>
+    <col min="12309" max="12544" style="94" width="9"/>
+    <col customWidth="1" min="12545" max="12545" style="94" width="5.125"/>
+    <col customWidth="1" min="12546" max="12553" style="94" width="9.625"/>
+    <col customWidth="1" min="12554" max="12554" style="94" width="5.125"/>
+    <col min="12555" max="12556" style="94" width="9"/>
+    <col customWidth="1" min="12557" max="12557" style="94" width="22.75"/>
+    <col customWidth="1" min="12558" max="12564" style="94" width="13.625"/>
+    <col min="12565" max="12800" style="94" width="9"/>
+    <col customWidth="1" min="12801" max="12801" style="94" width="5.125"/>
+    <col customWidth="1" min="12802" max="12809" style="94" width="9.625"/>
+    <col customWidth="1" min="12810" max="12810" style="94" width="5.125"/>
+    <col min="12811" max="12812" style="94" width="9"/>
+    <col customWidth="1" min="12813" max="12813" style="94" width="22.75"/>
+    <col customWidth="1" min="12814" max="12820" style="94" width="13.625"/>
+    <col min="12821" max="13056" style="94" width="9"/>
+    <col customWidth="1" min="13057" max="13057" style="94" width="5.125"/>
+    <col customWidth="1" min="13058" max="13065" style="94" width="9.625"/>
+    <col customWidth="1" min="13066" max="13066" style="94" width="5.125"/>
+    <col min="13067" max="13068" style="94" width="9"/>
+    <col customWidth="1" min="13069" max="13069" style="94" width="22.75"/>
+    <col customWidth="1" min="13070" max="13076" style="94" width="13.625"/>
+    <col min="13077" max="13312" style="94" width="9"/>
+    <col customWidth="1" min="13313" max="13313" style="94" width="5.125"/>
+    <col customWidth="1" min="13314" max="13321" style="94" width="9.625"/>
+    <col customWidth="1" min="13322" max="13322" style="94" width="5.125"/>
+    <col min="13323" max="13324" style="94" width="9"/>
+    <col customWidth="1" min="13325" max="13325" style="94" width="22.75"/>
+    <col customWidth="1" min="13326" max="13332" style="94" width="13.625"/>
+    <col min="13333" max="13568" style="94" width="9"/>
+    <col customWidth="1" min="13569" max="13569" style="94" width="5.125"/>
+    <col customWidth="1" min="13570" max="13577" style="94" width="9.625"/>
+    <col customWidth="1" min="13578" max="13578" style="94" width="5.125"/>
+    <col min="13579" max="13580" style="94" width="9"/>
+    <col customWidth="1" min="13581" max="13581" style="94" width="22.75"/>
+    <col customWidth="1" min="13582" max="13588" style="94" width="13.625"/>
+    <col min="13589" max="13824" style="94" width="9"/>
+    <col customWidth="1" min="13825" max="13825" style="94" width="5.125"/>
+    <col customWidth="1" min="13826" max="13833" style="94" width="9.625"/>
+    <col customWidth="1" min="13834" max="13834" style="94" width="5.125"/>
+    <col min="13835" max="13836" style="94" width="9"/>
+    <col customWidth="1" min="13837" max="13837" style="94" width="22.75"/>
+    <col customWidth="1" min="13838" max="13844" style="94" width="13.625"/>
+    <col min="13845" max="14080" style="94" width="9"/>
+    <col customWidth="1" min="14081" max="14081" style="94" width="5.125"/>
+    <col customWidth="1" min="14082" max="14089" style="94" width="9.625"/>
+    <col customWidth="1" min="14090" max="14090" style="94" width="5.125"/>
+    <col min="14091" max="14092" style="94" width="9"/>
+    <col customWidth="1" min="14093" max="14093" style="94" width="22.75"/>
+    <col customWidth="1" min="14094" max="14100" style="94" width="13.625"/>
+    <col min="14101" max="14336" style="94" width="9"/>
+    <col customWidth="1" min="14337" max="14337" style="94" width="5.125"/>
+    <col customWidth="1" min="14338" max="14345" style="94" width="9.625"/>
+    <col customWidth="1" min="14346" max="14346" style="94" width="5.125"/>
+    <col min="14347" max="14348" style="94" width="9"/>
+    <col customWidth="1" min="14349" max="14349" style="94" width="22.75"/>
+    <col customWidth="1" min="14350" max="14356" style="94" width="13.625"/>
+    <col min="14357" max="14592" style="94" width="9"/>
+    <col customWidth="1" min="14593" max="14593" style="94" width="5.125"/>
+    <col customWidth="1" min="14594" max="14601" style="94" width="9.625"/>
+    <col customWidth="1" min="14602" max="14602" style="94" width="5.125"/>
+    <col min="14603" max="14604" style="94" width="9"/>
+    <col customWidth="1" min="14605" max="14605" style="94" width="22.75"/>
+    <col customWidth="1" min="14606" max="14612" style="94" width="13.625"/>
+    <col min="14613" max="14848" style="94" width="9"/>
+    <col customWidth="1" min="14849" max="14849" style="94" width="5.125"/>
+    <col customWidth="1" min="14850" max="14857" style="94" width="9.625"/>
+    <col customWidth="1" min="14858" max="14858" style="94" width="5.125"/>
+    <col min="14859" max="14860" style="94" width="9"/>
+    <col customWidth="1" min="14861" max="14861" style="94" width="22.75"/>
+    <col customWidth="1" min="14862" max="14868" style="94" width="13.625"/>
+    <col min="14869" max="15104" style="94" width="9"/>
+    <col customWidth="1" min="15105" max="15105" style="94" width="5.125"/>
+    <col customWidth="1" min="15106" max="15113" style="94" width="9.625"/>
+    <col customWidth="1" min="15114" max="15114" style="94" width="5.125"/>
+    <col min="15115" max="15116" style="94" width="9"/>
+    <col customWidth="1" min="15117" max="15117" style="94" width="22.75"/>
+    <col customWidth="1" min="15118" max="15124" style="94" width="13.625"/>
+    <col min="15125" max="15360" style="94" width="9"/>
+    <col customWidth="1" min="15361" max="15361" style="94" width="5.125"/>
+    <col customWidth="1" min="15362" max="15369" style="94" width="9.625"/>
+    <col customWidth="1" min="15370" max="15370" style="94" width="5.125"/>
+    <col min="15371" max="15372" style="94" width="9"/>
+    <col customWidth="1" min="15373" max="15373" style="94" width="22.75"/>
+    <col customWidth="1" min="15374" max="15380" style="94" width="13.625"/>
+    <col min="15381" max="15616" style="94" width="9"/>
+    <col customWidth="1" min="15617" max="15617" style="94" width="5.125"/>
+    <col customWidth="1" min="15618" max="15625" style="94" width="9.625"/>
+    <col customWidth="1" min="15626" max="15626" style="94" width="5.125"/>
+    <col min="15627" max="15628" style="94" width="9"/>
+    <col customWidth="1" min="15629" max="15629" style="94" width="22.75"/>
+    <col customWidth="1" min="15630" max="15636" style="94" width="13.625"/>
+    <col min="15637" max="15872" style="94" width="9"/>
+    <col customWidth="1" min="15873" max="15873" style="94" width="5.125"/>
+    <col customWidth="1" min="15874" max="15881" style="94" width="9.625"/>
+    <col customWidth="1" min="15882" max="15882" style="94" width="5.125"/>
+    <col min="15883" max="15884" style="94" width="9"/>
+    <col customWidth="1" min="15885" max="15885" style="94" width="22.75"/>
+    <col customWidth="1" min="15886" max="15892" style="94" width="13.625"/>
+    <col min="15893" max="16128" style="94" width="9"/>
+    <col customWidth="1" min="16129" max="16129" style="94" width="5.125"/>
+    <col customWidth="1" min="16130" max="16137" style="94" width="9.625"/>
+    <col customWidth="1" min="16138" max="16138" style="94" width="5.125"/>
+    <col min="16139" max="16140" style="94" width="9"/>
+    <col customWidth="1" min="16141" max="16141" style="94" width="22.75"/>
+    <col customWidth="1" min="16142" max="16148" style="94" width="13.625"/>
+    <col min="16149" max="16384" style="94" width="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
     </row>
     <row r="3" ht="15"/>
     <row r="4" ht="15"/>
     <row r="5" ht="15">
-      <c r="A5" s="93" t="str">
+      <c r="A5" s="94" t="str">
         <f>CONCATENATE("■ 계  약  명 : ",환경설정!$B$1)</f>
         <v xml:space="preserve">■ 계  약  명 : 전라남도청 민원인 전용주차장 건립 전기공사 보안등주 등 구매</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="C6" s="95"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="93" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
+      <c r="A7" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
     </row>
     <row r="9" ht="15"/>
     <row r="10" ht="15"/>
     <row r="11" ht="15"/>
     <row r="12" ht="15"/>
     <row r="13" ht="15">
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
     </row>
     <row r="14" ht="15">
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
     </row>
     <row r="15" ht="15"/>
     <row r="16" ht="15"/>
     <row r="17" ht="15"/>
     <row r="18" ht="15"/>
     <row r="19" ht="15">
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
     </row>
     <row r="20" ht="15">
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
     </row>
     <row r="21" ht="15"/>
     <row r="22" ht="15"/>
     <row r="23" ht="15"/>
     <row r="24" ht="15"/>
     <row r="25" ht="15">
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
     </row>
     <row r="26" ht="15">
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
     </row>
     <row r="27" ht="15"/>
     <row r="28" ht="15"/>
     <row r="29" ht="15"/>
     <row r="30" ht="15"/>
     <row r="31" ht="15">
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
     </row>
     <row r="32" ht="15">
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
     </row>
     <row r="33" ht="15"/>
     <row r="34" ht="15"/>
     <row r="35" ht="15"/>
     <row r="36" ht="15"/>
     <row r="37" ht="26.25">
-      <c r="C37" s="97"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="97"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
     </row>
     <row r="38" ht="15"/>
     <row r="39" ht="15">
-      <c r="S39" s="93"/>
+      <c r="S39" s="94"/>
     </row>
     <row r="40" ht="15"/>
     <row r="41" ht="15"/>
@@ -6937,604 +6948,604 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" style="93" width="5.125"/>
-    <col customWidth="1" min="2" max="9" style="93" width="9.625"/>
-    <col customWidth="1" min="10" max="10" style="93" width="5.125"/>
-    <col min="11" max="12" style="93" width="9"/>
-    <col customWidth="1" min="13" max="13" style="93" width="22.75"/>
-    <col customWidth="1" min="14" max="20" style="93" width="13.625"/>
-    <col min="21" max="256" style="93" width="9"/>
-    <col customWidth="1" min="257" max="257" style="93" width="5.125"/>
-    <col customWidth="1" min="258" max="265" style="93" width="9.625"/>
-    <col customWidth="1" min="266" max="266" style="93" width="5.125"/>
-    <col min="267" max="268" style="93" width="9"/>
-    <col customWidth="1" min="269" max="269" style="93" width="22.75"/>
-    <col customWidth="1" min="270" max="276" style="93" width="13.625"/>
-    <col min="277" max="512" style="93" width="9"/>
-    <col customWidth="1" min="513" max="513" style="93" width="5.125"/>
-    <col customWidth="1" min="514" max="521" style="93" width="9.625"/>
-    <col customWidth="1" min="522" max="522" style="93" width="5.125"/>
-    <col min="523" max="524" style="93" width="9"/>
-    <col customWidth="1" min="525" max="525" style="93" width="22.75"/>
-    <col customWidth="1" min="526" max="532" style="93" width="13.625"/>
-    <col min="533" max="768" style="93" width="9"/>
-    <col customWidth="1" min="769" max="769" style="93" width="5.125"/>
-    <col customWidth="1" min="770" max="777" style="93" width="9.625"/>
-    <col customWidth="1" min="778" max="778" style="93" width="5.125"/>
-    <col min="779" max="780" style="93" width="9"/>
-    <col customWidth="1" min="781" max="781" style="93" width="22.75"/>
-    <col customWidth="1" min="782" max="788" style="93" width="13.625"/>
-    <col min="789" max="1024" style="93" width="9"/>
-    <col customWidth="1" min="1025" max="1025" style="93" width="5.125"/>
-    <col customWidth="1" min="1026" max="1033" style="93" width="9.625"/>
-    <col customWidth="1" min="1034" max="1034" style="93" width="5.125"/>
-    <col min="1035" max="1036" style="93" width="9"/>
-    <col customWidth="1" min="1037" max="1037" style="93" width="22.75"/>
-    <col customWidth="1" min="1038" max="1044" style="93" width="13.625"/>
-    <col min="1045" max="1280" style="93" width="9"/>
-    <col customWidth="1" min="1281" max="1281" style="93" width="5.125"/>
-    <col customWidth="1" min="1282" max="1289" style="93" width="9.625"/>
-    <col customWidth="1" min="1290" max="1290" style="93" width="5.125"/>
-    <col min="1291" max="1292" style="93" width="9"/>
-    <col customWidth="1" min="1293" max="1293" style="93" width="22.75"/>
-    <col customWidth="1" min="1294" max="1300" style="93" width="13.625"/>
-    <col min="1301" max="1536" style="93" width="9"/>
-    <col customWidth="1" min="1537" max="1537" style="93" width="5.125"/>
-    <col customWidth="1" min="1538" max="1545" style="93" width="9.625"/>
-    <col customWidth="1" min="1546" max="1546" style="93" width="5.125"/>
-    <col min="1547" max="1548" style="93" width="9"/>
-    <col customWidth="1" min="1549" max="1549" style="93" width="22.75"/>
-    <col customWidth="1" min="1550" max="1556" style="93" width="13.625"/>
-    <col min="1557" max="1792" style="93" width="9"/>
-    <col customWidth="1" min="1793" max="1793" style="93" width="5.125"/>
-    <col customWidth="1" min="1794" max="1801" style="93" width="9.625"/>
-    <col customWidth="1" min="1802" max="1802" style="93" width="5.125"/>
-    <col min="1803" max="1804" style="93" width="9"/>
-    <col customWidth="1" min="1805" max="1805" style="93" width="22.75"/>
-    <col customWidth="1" min="1806" max="1812" style="93" width="13.625"/>
-    <col min="1813" max="2048" style="93" width="9"/>
-    <col customWidth="1" min="2049" max="2049" style="93" width="5.125"/>
-    <col customWidth="1" min="2050" max="2057" style="93" width="9.625"/>
-    <col customWidth="1" min="2058" max="2058" style="93" width="5.125"/>
-    <col min="2059" max="2060" style="93" width="9"/>
-    <col customWidth="1" min="2061" max="2061" style="93" width="22.75"/>
-    <col customWidth="1" min="2062" max="2068" style="93" width="13.625"/>
-    <col min="2069" max="2304" style="93" width="9"/>
-    <col customWidth="1" min="2305" max="2305" style="93" width="5.125"/>
-    <col customWidth="1" min="2306" max="2313" style="93" width="9.625"/>
-    <col customWidth="1" min="2314" max="2314" style="93" width="5.125"/>
-    <col min="2315" max="2316" style="93" width="9"/>
-    <col customWidth="1" min="2317" max="2317" style="93" width="22.75"/>
-    <col customWidth="1" min="2318" max="2324" style="93" width="13.625"/>
-    <col min="2325" max="2560" style="93" width="9"/>
-    <col customWidth="1" min="2561" max="2561" style="93" width="5.125"/>
-    <col customWidth="1" min="2562" max="2569" style="93" width="9.625"/>
-    <col customWidth="1" min="2570" max="2570" style="93" width="5.125"/>
-    <col min="2571" max="2572" style="93" width="9"/>
-    <col customWidth="1" min="2573" max="2573" style="93" width="22.75"/>
-    <col customWidth="1" min="2574" max="2580" style="93" width="13.625"/>
-    <col min="2581" max="2816" style="93" width="9"/>
-    <col customWidth="1" min="2817" max="2817" style="93" width="5.125"/>
-    <col customWidth="1" min="2818" max="2825" style="93" width="9.625"/>
-    <col customWidth="1" min="2826" max="2826" style="93" width="5.125"/>
-    <col min="2827" max="2828" style="93" width="9"/>
-    <col customWidth="1" min="2829" max="2829" style="93" width="22.75"/>
-    <col customWidth="1" min="2830" max="2836" style="93" width="13.625"/>
-    <col min="2837" max="3072" style="93" width="9"/>
-    <col customWidth="1" min="3073" max="3073" style="93" width="5.125"/>
-    <col customWidth="1" min="3074" max="3081" style="93" width="9.625"/>
-    <col customWidth="1" min="3082" max="3082" style="93" width="5.125"/>
-    <col min="3083" max="3084" style="93" width="9"/>
-    <col customWidth="1" min="3085" max="3085" style="93" width="22.75"/>
-    <col customWidth="1" min="3086" max="3092" style="93" width="13.625"/>
-    <col min="3093" max="3328" style="93" width="9"/>
-    <col customWidth="1" min="3329" max="3329" style="93" width="5.125"/>
-    <col customWidth="1" min="3330" max="3337" style="93" width="9.625"/>
-    <col customWidth="1" min="3338" max="3338" style="93" width="5.125"/>
-    <col min="3339" max="3340" style="93" width="9"/>
-    <col customWidth="1" min="3341" max="3341" style="93" width="22.75"/>
-    <col customWidth="1" min="3342" max="3348" style="93" width="13.625"/>
-    <col min="3349" max="3584" style="93" width="9"/>
-    <col customWidth="1" min="3585" max="3585" style="93" width="5.125"/>
-    <col customWidth="1" min="3586" max="3593" style="93" width="9.625"/>
-    <col customWidth="1" min="3594" max="3594" style="93" width="5.125"/>
-    <col min="3595" max="3596" style="93" width="9"/>
-    <col customWidth="1" min="3597" max="3597" style="93" width="22.75"/>
-    <col customWidth="1" min="3598" max="3604" style="93" width="13.625"/>
-    <col min="3605" max="3840" style="93" width="9"/>
-    <col customWidth="1" min="3841" max="3841" style="93" width="5.125"/>
-    <col customWidth="1" min="3842" max="3849" style="93" width="9.625"/>
-    <col customWidth="1" min="3850" max="3850" style="93" width="5.125"/>
-    <col min="3851" max="3852" style="93" width="9"/>
-    <col customWidth="1" min="3853" max="3853" style="93" width="22.75"/>
-    <col customWidth="1" min="3854" max="3860" style="93" width="13.625"/>
-    <col min="3861" max="4096" style="93" width="9"/>
-    <col customWidth="1" min="4097" max="4097" style="93" width="5.125"/>
-    <col customWidth="1" min="4098" max="4105" style="93" width="9.625"/>
-    <col customWidth="1" min="4106" max="4106" style="93" width="5.125"/>
-    <col min="4107" max="4108" style="93" width="9"/>
-    <col customWidth="1" min="4109" max="4109" style="93" width="22.75"/>
-    <col customWidth="1" min="4110" max="4116" style="93" width="13.625"/>
-    <col min="4117" max="4352" style="93" width="9"/>
-    <col customWidth="1" min="4353" max="4353" style="93" width="5.125"/>
-    <col customWidth="1" min="4354" max="4361" style="93" width="9.625"/>
-    <col customWidth="1" min="4362" max="4362" style="93" width="5.125"/>
-    <col min="4363" max="4364" style="93" width="9"/>
-    <col customWidth="1" min="4365" max="4365" style="93" width="22.75"/>
-    <col customWidth="1" min="4366" max="4372" style="93" width="13.625"/>
-    <col min="4373" max="4608" style="93" width="9"/>
-    <col customWidth="1" min="4609" max="4609" style="93" width="5.125"/>
-    <col customWidth="1" min="4610" max="4617" style="93" width="9.625"/>
-    <col customWidth="1" min="4618" max="4618" style="93" width="5.125"/>
-    <col min="4619" max="4620" style="93" width="9"/>
-    <col customWidth="1" min="4621" max="4621" style="93" width="22.75"/>
-    <col customWidth="1" min="4622" max="4628" style="93" width="13.625"/>
-    <col min="4629" max="4864" style="93" width="9"/>
-    <col customWidth="1" min="4865" max="4865" style="93" width="5.125"/>
-    <col customWidth="1" min="4866" max="4873" style="93" width="9.625"/>
-    <col customWidth="1" min="4874" max="4874" style="93" width="5.125"/>
-    <col min="4875" max="4876" style="93" width="9"/>
-    <col customWidth="1" min="4877" max="4877" style="93" width="22.75"/>
-    <col customWidth="1" min="4878" max="4884" style="93" width="13.625"/>
-    <col min="4885" max="5120" style="93" width="9"/>
-    <col customWidth="1" min="5121" max="5121" style="93" width="5.125"/>
-    <col customWidth="1" min="5122" max="5129" style="93" width="9.625"/>
-    <col customWidth="1" min="5130" max="5130" style="93" width="5.125"/>
-    <col min="5131" max="5132" style="93" width="9"/>
-    <col customWidth="1" min="5133" max="5133" style="93" width="22.75"/>
-    <col customWidth="1" min="5134" max="5140" style="93" width="13.625"/>
-    <col min="5141" max="5376" style="93" width="9"/>
-    <col customWidth="1" min="5377" max="5377" style="93" width="5.125"/>
-    <col customWidth="1" min="5378" max="5385" style="93" width="9.625"/>
-    <col customWidth="1" min="5386" max="5386" style="93" width="5.125"/>
-    <col min="5387" max="5388" style="93" width="9"/>
-    <col customWidth="1" min="5389" max="5389" style="93" width="22.75"/>
-    <col customWidth="1" min="5390" max="5396" style="93" width="13.625"/>
-    <col min="5397" max="5632" style="93" width="9"/>
-    <col customWidth="1" min="5633" max="5633" style="93" width="5.125"/>
-    <col customWidth="1" min="5634" max="5641" style="93" width="9.625"/>
-    <col customWidth="1" min="5642" max="5642" style="93" width="5.125"/>
-    <col min="5643" max="5644" style="93" width="9"/>
-    <col customWidth="1" min="5645" max="5645" style="93" width="22.75"/>
-    <col customWidth="1" min="5646" max="5652" style="93" width="13.625"/>
-    <col min="5653" max="5888" style="93" width="9"/>
-    <col customWidth="1" min="5889" max="5889" style="93" width="5.125"/>
-    <col customWidth="1" min="5890" max="5897" style="93" width="9.625"/>
-    <col customWidth="1" min="5898" max="5898" style="93" width="5.125"/>
-    <col min="5899" max="5900" style="93" width="9"/>
-    <col customWidth="1" min="5901" max="5901" style="93" width="22.75"/>
-    <col customWidth="1" min="5902" max="5908" style="93" width="13.625"/>
-    <col min="5909" max="6144" style="93" width="9"/>
-    <col customWidth="1" min="6145" max="6145" style="93" width="5.125"/>
-    <col customWidth="1" min="6146" max="6153" style="93" width="9.625"/>
-    <col customWidth="1" min="6154" max="6154" style="93" width="5.125"/>
-    <col min="6155" max="6156" style="93" width="9"/>
-    <col customWidth="1" min="6157" max="6157" style="93" width="22.75"/>
-    <col customWidth="1" min="6158" max="6164" style="93" width="13.625"/>
-    <col min="6165" max="6400" style="93" width="9"/>
-    <col customWidth="1" min="6401" max="6401" style="93" width="5.125"/>
-    <col customWidth="1" min="6402" max="6409" style="93" width="9.625"/>
-    <col customWidth="1" min="6410" max="6410" style="93" width="5.125"/>
-    <col min="6411" max="6412" style="93" width="9"/>
-    <col customWidth="1" min="6413" max="6413" style="93" width="22.75"/>
-    <col customWidth="1" min="6414" max="6420" style="93" width="13.625"/>
-    <col min="6421" max="6656" style="93" width="9"/>
-    <col customWidth="1" min="6657" max="6657" style="93" width="5.125"/>
-    <col customWidth="1" min="6658" max="6665" style="93" width="9.625"/>
-    <col customWidth="1" min="6666" max="6666" style="93" width="5.125"/>
-    <col min="6667" max="6668" style="93" width="9"/>
-    <col customWidth="1" min="6669" max="6669" style="93" width="22.75"/>
-    <col customWidth="1" min="6670" max="6676" style="93" width="13.625"/>
-    <col min="6677" max="6912" style="93" width="9"/>
-    <col customWidth="1" min="6913" max="6913" style="93" width="5.125"/>
-    <col customWidth="1" min="6914" max="6921" style="93" width="9.625"/>
-    <col customWidth="1" min="6922" max="6922" style="93" width="5.125"/>
-    <col min="6923" max="6924" style="93" width="9"/>
-    <col customWidth="1" min="6925" max="6925" style="93" width="22.75"/>
-    <col customWidth="1" min="6926" max="6932" style="93" width="13.625"/>
-    <col min="6933" max="7168" style="93" width="9"/>
-    <col customWidth="1" min="7169" max="7169" style="93" width="5.125"/>
-    <col customWidth="1" min="7170" max="7177" style="93" width="9.625"/>
-    <col customWidth="1" min="7178" max="7178" style="93" width="5.125"/>
-    <col min="7179" max="7180" style="93" width="9"/>
-    <col customWidth="1" min="7181" max="7181" style="93" width="22.75"/>
-    <col customWidth="1" min="7182" max="7188" style="93" width="13.625"/>
-    <col min="7189" max="7424" style="93" width="9"/>
-    <col customWidth="1" min="7425" max="7425" style="93" width="5.125"/>
-    <col customWidth="1" min="7426" max="7433" style="93" width="9.625"/>
-    <col customWidth="1" min="7434" max="7434" style="93" width="5.125"/>
-    <col min="7435" max="7436" style="93" width="9"/>
-    <col customWidth="1" min="7437" max="7437" style="93" width="22.75"/>
-    <col customWidth="1" min="7438" max="7444" style="93" width="13.625"/>
-    <col min="7445" max="7680" style="93" width="9"/>
-    <col customWidth="1" min="7681" max="7681" style="93" width="5.125"/>
-    <col customWidth="1" min="7682" max="7689" style="93" width="9.625"/>
-    <col customWidth="1" min="7690" max="7690" style="93" width="5.125"/>
-    <col min="7691" max="7692" style="93" width="9"/>
-    <col customWidth="1" min="7693" max="7693" style="93" width="22.75"/>
-    <col customWidth="1" min="7694" max="7700" style="93" width="13.625"/>
-    <col min="7701" max="7936" style="93" width="9"/>
-    <col customWidth="1" min="7937" max="7937" style="93" width="5.125"/>
-    <col customWidth="1" min="7938" max="7945" style="93" width="9.625"/>
-    <col customWidth="1" min="7946" max="7946" style="93" width="5.125"/>
-    <col min="7947" max="7948" style="93" width="9"/>
-    <col customWidth="1" min="7949" max="7949" style="93" width="22.75"/>
-    <col customWidth="1" min="7950" max="7956" style="93" width="13.625"/>
-    <col min="7957" max="8192" style="93" width="9"/>
-    <col customWidth="1" min="8193" max="8193" style="93" width="5.125"/>
-    <col customWidth="1" min="8194" max="8201" style="93" width="9.625"/>
-    <col customWidth="1" min="8202" max="8202" style="93" width="5.125"/>
-    <col min="8203" max="8204" style="93" width="9"/>
-    <col customWidth="1" min="8205" max="8205" style="93" width="22.75"/>
-    <col customWidth="1" min="8206" max="8212" style="93" width="13.625"/>
-    <col min="8213" max="8448" style="93" width="9"/>
-    <col customWidth="1" min="8449" max="8449" style="93" width="5.125"/>
-    <col customWidth="1" min="8450" max="8457" style="93" width="9.625"/>
-    <col customWidth="1" min="8458" max="8458" style="93" width="5.125"/>
-    <col min="8459" max="8460" style="93" width="9"/>
-    <col customWidth="1" min="8461" max="8461" style="93" width="22.75"/>
-    <col customWidth="1" min="8462" max="8468" style="93" width="13.625"/>
-    <col min="8469" max="8704" style="93" width="9"/>
-    <col customWidth="1" min="8705" max="8705" style="93" width="5.125"/>
-    <col customWidth="1" min="8706" max="8713" style="93" width="9.625"/>
-    <col customWidth="1" min="8714" max="8714" style="93" width="5.125"/>
-    <col min="8715" max="8716" style="93" width="9"/>
-    <col customWidth="1" min="8717" max="8717" style="93" width="22.75"/>
-    <col customWidth="1" min="8718" max="8724" style="93" width="13.625"/>
-    <col min="8725" max="8960" style="93" width="9"/>
-    <col customWidth="1" min="8961" max="8961" style="93" width="5.125"/>
-    <col customWidth="1" min="8962" max="8969" style="93" width="9.625"/>
-    <col customWidth="1" min="8970" max="8970" style="93" width="5.125"/>
-    <col min="8971" max="8972" style="93" width="9"/>
-    <col customWidth="1" min="8973" max="8973" style="93" width="22.75"/>
-    <col customWidth="1" min="8974" max="8980" style="93" width="13.625"/>
-    <col min="8981" max="9216" style="93" width="9"/>
-    <col customWidth="1" min="9217" max="9217" style="93" width="5.125"/>
-    <col customWidth="1" min="9218" max="9225" style="93" width="9.625"/>
-    <col customWidth="1" min="9226" max="9226" style="93" width="5.125"/>
-    <col min="9227" max="9228" style="93" width="9"/>
-    <col customWidth="1" min="9229" max="9229" style="93" width="22.75"/>
-    <col customWidth="1" min="9230" max="9236" style="93" width="13.625"/>
-    <col min="9237" max="9472" style="93" width="9"/>
-    <col customWidth="1" min="9473" max="9473" style="93" width="5.125"/>
-    <col customWidth="1" min="9474" max="9481" style="93" width="9.625"/>
-    <col customWidth="1" min="9482" max="9482" style="93" width="5.125"/>
-    <col min="9483" max="9484" style="93" width="9"/>
-    <col customWidth="1" min="9485" max="9485" style="93" width="22.75"/>
-    <col customWidth="1" min="9486" max="9492" style="93" width="13.625"/>
-    <col min="9493" max="9728" style="93" width="9"/>
-    <col customWidth="1" min="9729" max="9729" style="93" width="5.125"/>
-    <col customWidth="1" min="9730" max="9737" style="93" width="9.625"/>
-    <col customWidth="1" min="9738" max="9738" style="93" width="5.125"/>
-    <col min="9739" max="9740" style="93" width="9"/>
-    <col customWidth="1" min="9741" max="9741" style="93" width="22.75"/>
-    <col customWidth="1" min="9742" max="9748" style="93" width="13.625"/>
-    <col min="9749" max="9984" style="93" width="9"/>
-    <col customWidth="1" min="9985" max="9985" style="93" width="5.125"/>
-    <col customWidth="1" min="9986" max="9993" style="93" width="9.625"/>
-    <col customWidth="1" min="9994" max="9994" style="93" width="5.125"/>
-    <col min="9995" max="9996" style="93" width="9"/>
-    <col customWidth="1" min="9997" max="9997" style="93" width="22.75"/>
-    <col customWidth="1" min="9998" max="10004" style="93" width="13.625"/>
-    <col min="10005" max="10240" style="93" width="9"/>
-    <col customWidth="1" min="10241" max="10241" style="93" width="5.125"/>
-    <col customWidth="1" min="10242" max="10249" style="93" width="9.625"/>
-    <col customWidth="1" min="10250" max="10250" style="93" width="5.125"/>
-    <col min="10251" max="10252" style="93" width="9"/>
-    <col customWidth="1" min="10253" max="10253" style="93" width="22.75"/>
-    <col customWidth="1" min="10254" max="10260" style="93" width="13.625"/>
-    <col min="10261" max="10496" style="93" width="9"/>
-    <col customWidth="1" min="10497" max="10497" style="93" width="5.125"/>
-    <col customWidth="1" min="10498" max="10505" style="93" width="9.625"/>
-    <col customWidth="1" min="10506" max="10506" style="93" width="5.125"/>
-    <col min="10507" max="10508" style="93" width="9"/>
-    <col customWidth="1" min="10509" max="10509" style="93" width="22.75"/>
-    <col customWidth="1" min="10510" max="10516" style="93" width="13.625"/>
-    <col min="10517" max="10752" style="93" width="9"/>
-    <col customWidth="1" min="10753" max="10753" style="93" width="5.125"/>
-    <col customWidth="1" min="10754" max="10761" style="93" width="9.625"/>
-    <col customWidth="1" min="10762" max="10762" style="93" width="5.125"/>
-    <col min="10763" max="10764" style="93" width="9"/>
-    <col customWidth="1" min="10765" max="10765" style="93" width="22.75"/>
-    <col customWidth="1" min="10766" max="10772" style="93" width="13.625"/>
-    <col min="10773" max="11008" style="93" width="9"/>
-    <col customWidth="1" min="11009" max="11009" style="93" width="5.125"/>
-    <col customWidth="1" min="11010" max="11017" style="93" width="9.625"/>
-    <col customWidth="1" min="11018" max="11018" style="93" width="5.125"/>
-    <col min="11019" max="11020" style="93" width="9"/>
-    <col customWidth="1" min="11021" max="11021" style="93" width="22.75"/>
-    <col customWidth="1" min="11022" max="11028" style="93" width="13.625"/>
-    <col min="11029" max="11264" style="93" width="9"/>
-    <col customWidth="1" min="11265" max="11265" style="93" width="5.125"/>
-    <col customWidth="1" min="11266" max="11273" style="93" width="9.625"/>
-    <col customWidth="1" min="11274" max="11274" style="93" width="5.125"/>
-    <col min="11275" max="11276" style="93" width="9"/>
-    <col customWidth="1" min="11277" max="11277" style="93" width="22.75"/>
-    <col customWidth="1" min="11278" max="11284" style="93" width="13.625"/>
-    <col min="11285" max="11520" style="93" width="9"/>
-    <col customWidth="1" min="11521" max="11521" style="93" width="5.125"/>
-    <col customWidth="1" min="11522" max="11529" style="93" width="9.625"/>
-    <col customWidth="1" min="11530" max="11530" style="93" width="5.125"/>
-    <col min="11531" max="11532" style="93" width="9"/>
-    <col customWidth="1" min="11533" max="11533" style="93" width="22.75"/>
-    <col customWidth="1" min="11534" max="11540" style="93" width="13.625"/>
-    <col min="11541" max="11776" style="93" width="9"/>
-    <col customWidth="1" min="11777" max="11777" style="93" width="5.125"/>
-    <col customWidth="1" min="11778" max="11785" style="93" width="9.625"/>
-    <col customWidth="1" min="11786" max="11786" style="93" width="5.125"/>
-    <col min="11787" max="11788" style="93" width="9"/>
-    <col customWidth="1" min="11789" max="11789" style="93" width="22.75"/>
-    <col customWidth="1" min="11790" max="11796" style="93" width="13.625"/>
-    <col min="11797" max="12032" style="93" width="9"/>
-    <col customWidth="1" min="12033" max="12033" style="93" width="5.125"/>
-    <col customWidth="1" min="12034" max="12041" style="93" width="9.625"/>
-    <col customWidth="1" min="12042" max="12042" style="93" width="5.125"/>
-    <col min="12043" max="12044" style="93" width="9"/>
-    <col customWidth="1" min="12045" max="12045" style="93" width="22.75"/>
-    <col customWidth="1" min="12046" max="12052" style="93" width="13.625"/>
-    <col min="12053" max="12288" style="93" width="9"/>
-    <col customWidth="1" min="12289" max="12289" style="93" width="5.125"/>
-    <col customWidth="1" min="12290" max="12297" style="93" width="9.625"/>
-    <col customWidth="1" min="12298" max="12298" style="93" width="5.125"/>
-    <col min="12299" max="12300" style="93" width="9"/>
-    <col customWidth="1" min="12301" max="12301" style="93" width="22.75"/>
-    <col customWidth="1" min="12302" max="12308" style="93" width="13.625"/>
-    <col min="12309" max="12544" style="93" width="9"/>
-    <col customWidth="1" min="12545" max="12545" style="93" width="5.125"/>
-    <col customWidth="1" min="12546" max="12553" style="93" width="9.625"/>
-    <col customWidth="1" min="12554" max="12554" style="93" width="5.125"/>
-    <col min="12555" max="12556" style="93" width="9"/>
-    <col customWidth="1" min="12557" max="12557" style="93" width="22.75"/>
-    <col customWidth="1" min="12558" max="12564" style="93" width="13.625"/>
-    <col min="12565" max="12800" style="93" width="9"/>
-    <col customWidth="1" min="12801" max="12801" style="93" width="5.125"/>
-    <col customWidth="1" min="12802" max="12809" style="93" width="9.625"/>
-    <col customWidth="1" min="12810" max="12810" style="93" width="5.125"/>
-    <col min="12811" max="12812" style="93" width="9"/>
-    <col customWidth="1" min="12813" max="12813" style="93" width="22.75"/>
-    <col customWidth="1" min="12814" max="12820" style="93" width="13.625"/>
-    <col min="12821" max="13056" style="93" width="9"/>
-    <col customWidth="1" min="13057" max="13057" style="93" width="5.125"/>
-    <col customWidth="1" min="13058" max="13065" style="93" width="9.625"/>
-    <col customWidth="1" min="13066" max="13066" style="93" width="5.125"/>
-    <col min="13067" max="13068" style="93" width="9"/>
-    <col customWidth="1" min="13069" max="13069" style="93" width="22.75"/>
-    <col customWidth="1" min="13070" max="13076" style="93" width="13.625"/>
-    <col min="13077" max="13312" style="93" width="9"/>
-    <col customWidth="1" min="13313" max="13313" style="93" width="5.125"/>
-    <col customWidth="1" min="13314" max="13321" style="93" width="9.625"/>
-    <col customWidth="1" min="13322" max="13322" style="93" width="5.125"/>
-    <col min="13323" max="13324" style="93" width="9"/>
-    <col customWidth="1" min="13325" max="13325" style="93" width="22.75"/>
-    <col customWidth="1" min="13326" max="13332" style="93" width="13.625"/>
-    <col min="13333" max="13568" style="93" width="9"/>
-    <col customWidth="1" min="13569" max="13569" style="93" width="5.125"/>
-    <col customWidth="1" min="13570" max="13577" style="93" width="9.625"/>
-    <col customWidth="1" min="13578" max="13578" style="93" width="5.125"/>
-    <col min="13579" max="13580" style="93" width="9"/>
-    <col customWidth="1" min="13581" max="13581" style="93" width="22.75"/>
-    <col customWidth="1" min="13582" max="13588" style="93" width="13.625"/>
-    <col min="13589" max="13824" style="93" width="9"/>
-    <col customWidth="1" min="13825" max="13825" style="93" width="5.125"/>
-    <col customWidth="1" min="13826" max="13833" style="93" width="9.625"/>
-    <col customWidth="1" min="13834" max="13834" style="93" width="5.125"/>
-    <col min="13835" max="13836" style="93" width="9"/>
-    <col customWidth="1" min="13837" max="13837" style="93" width="22.75"/>
-    <col customWidth="1" min="13838" max="13844" style="93" width="13.625"/>
-    <col min="13845" max="14080" style="93" width="9"/>
-    <col customWidth="1" min="14081" max="14081" style="93" width="5.125"/>
-    <col customWidth="1" min="14082" max="14089" style="93" width="9.625"/>
-    <col customWidth="1" min="14090" max="14090" style="93" width="5.125"/>
-    <col min="14091" max="14092" style="93" width="9"/>
-    <col customWidth="1" min="14093" max="14093" style="93" width="22.75"/>
-    <col customWidth="1" min="14094" max="14100" style="93" width="13.625"/>
-    <col min="14101" max="14336" style="93" width="9"/>
-    <col customWidth="1" min="14337" max="14337" style="93" width="5.125"/>
-    <col customWidth="1" min="14338" max="14345" style="93" width="9.625"/>
-    <col customWidth="1" min="14346" max="14346" style="93" width="5.125"/>
-    <col min="14347" max="14348" style="93" width="9"/>
-    <col customWidth="1" min="14349" max="14349" style="93" width="22.75"/>
-    <col customWidth="1" min="14350" max="14356" style="93" width="13.625"/>
-    <col min="14357" max="14592" style="93" width="9"/>
-    <col customWidth="1" min="14593" max="14593" style="93" width="5.125"/>
-    <col customWidth="1" min="14594" max="14601" style="93" width="9.625"/>
-    <col customWidth="1" min="14602" max="14602" style="93" width="5.125"/>
-    <col min="14603" max="14604" style="93" width="9"/>
-    <col customWidth="1" min="14605" max="14605" style="93" width="22.75"/>
-    <col customWidth="1" min="14606" max="14612" style="93" width="13.625"/>
-    <col min="14613" max="14848" style="93" width="9"/>
-    <col customWidth="1" min="14849" max="14849" style="93" width="5.125"/>
-    <col customWidth="1" min="14850" max="14857" style="93" width="9.625"/>
-    <col customWidth="1" min="14858" max="14858" style="93" width="5.125"/>
-    <col min="14859" max="14860" style="93" width="9"/>
-    <col customWidth="1" min="14861" max="14861" style="93" width="22.75"/>
-    <col customWidth="1" min="14862" max="14868" style="93" width="13.625"/>
-    <col min="14869" max="15104" style="93" width="9"/>
-    <col customWidth="1" min="15105" max="15105" style="93" width="5.125"/>
-    <col customWidth="1" min="15106" max="15113" style="93" width="9.625"/>
-    <col customWidth="1" min="15114" max="15114" style="93" width="5.125"/>
-    <col min="15115" max="15116" style="93" width="9"/>
-    <col customWidth="1" min="15117" max="15117" style="93" width="22.75"/>
-    <col customWidth="1" min="15118" max="15124" style="93" width="13.625"/>
-    <col min="15125" max="15360" style="93" width="9"/>
-    <col customWidth="1" min="15361" max="15361" style="93" width="5.125"/>
-    <col customWidth="1" min="15362" max="15369" style="93" width="9.625"/>
-    <col customWidth="1" min="15370" max="15370" style="93" width="5.125"/>
-    <col min="15371" max="15372" style="93" width="9"/>
-    <col customWidth="1" min="15373" max="15373" style="93" width="22.75"/>
-    <col customWidth="1" min="15374" max="15380" style="93" width="13.625"/>
-    <col min="15381" max="15616" style="93" width="9"/>
-    <col customWidth="1" min="15617" max="15617" style="93" width="5.125"/>
-    <col customWidth="1" min="15618" max="15625" style="93" width="9.625"/>
-    <col customWidth="1" min="15626" max="15626" style="93" width="5.125"/>
-    <col min="15627" max="15628" style="93" width="9"/>
-    <col customWidth="1" min="15629" max="15629" style="93" width="22.75"/>
-    <col customWidth="1" min="15630" max="15636" style="93" width="13.625"/>
-    <col min="15637" max="15872" style="93" width="9"/>
-    <col customWidth="1" min="15873" max="15873" style="93" width="5.125"/>
-    <col customWidth="1" min="15874" max="15881" style="93" width="9.625"/>
-    <col customWidth="1" min="15882" max="15882" style="93" width="5.125"/>
-    <col min="15883" max="15884" style="93" width="9"/>
-    <col customWidth="1" min="15885" max="15885" style="93" width="22.75"/>
-    <col customWidth="1" min="15886" max="15892" style="93" width="13.625"/>
-    <col min="15893" max="16128" style="93" width="9"/>
-    <col customWidth="1" min="16129" max="16129" style="93" width="5.125"/>
-    <col customWidth="1" min="16130" max="16137" style="93" width="9.625"/>
-    <col customWidth="1" min="16138" max="16138" style="93" width="5.125"/>
-    <col min="16139" max="16140" style="93" width="9"/>
-    <col customWidth="1" min="16141" max="16141" style="93" width="22.75"/>
-    <col customWidth="1" min="16142" max="16148" style="93" width="13.625"/>
-    <col min="16149" max="16384" style="93" width="9"/>
+    <col customWidth="1" min="1" max="1" style="94" width="5.125"/>
+    <col customWidth="1" min="2" max="9" style="94" width="9.625"/>
+    <col customWidth="1" min="10" max="10" style="94" width="5.125"/>
+    <col min="11" max="12" style="94" width="9"/>
+    <col customWidth="1" min="13" max="13" style="94" width="22.75"/>
+    <col customWidth="1" min="14" max="20" style="94" width="13.625"/>
+    <col min="21" max="256" style="94" width="9"/>
+    <col customWidth="1" min="257" max="257" style="94" width="5.125"/>
+    <col customWidth="1" min="258" max="265" style="94" width="9.625"/>
+    <col customWidth="1" min="266" max="266" style="94" width="5.125"/>
+    <col min="267" max="268" style="94" width="9"/>
+    <col customWidth="1" min="269" max="269" style="94" width="22.75"/>
+    <col customWidth="1" min="270" max="276" style="94" width="13.625"/>
+    <col min="277" max="512" style="94" width="9"/>
+    <col customWidth="1" min="513" max="513" style="94" width="5.125"/>
+    <col customWidth="1" min="514" max="521" style="94" width="9.625"/>
+    <col customWidth="1" min="522" max="522" style="94" width="5.125"/>
+    <col min="523" max="524" style="94" width="9"/>
+    <col customWidth="1" min="525" max="525" style="94" width="22.75"/>
+    <col customWidth="1" min="526" max="532" style="94" width="13.625"/>
+    <col min="533" max="768" style="94" width="9"/>
+    <col customWidth="1" min="769" max="769" style="94" width="5.125"/>
+    <col customWidth="1" min="770" max="777" style="94" width="9.625"/>
+    <col customWidth="1" min="778" max="778" style="94" width="5.125"/>
+    <col min="779" max="780" style="94" width="9"/>
+    <col customWidth="1" min="781" max="781" style="94" width="22.75"/>
+    <col customWidth="1" min="782" max="788" style="94" width="13.625"/>
+    <col min="789" max="1024" style="94" width="9"/>
+    <col customWidth="1" min="1025" max="1025" style="94" width="5.125"/>
+    <col customWidth="1" min="1026" max="1033" style="94" width="9.625"/>
+    <col customWidth="1" min="1034" max="1034" style="94" width="5.125"/>
+    <col min="1035" max="1036" style="94" width="9"/>
+    <col customWidth="1" min="1037" max="1037" style="94" width="22.75"/>
+    <col customWidth="1" min="1038" max="1044" style="94" width="13.625"/>
+    <col min="1045" max="1280" style="94" width="9"/>
+    <col customWidth="1" min="1281" max="1281" style="94" width="5.125"/>
+    <col customWidth="1" min="1282" max="1289" style="94" width="9.625"/>
+    <col customWidth="1" min="1290" max="1290" style="94" width="5.125"/>
+    <col min="1291" max="1292" style="94" width="9"/>
+    <col customWidth="1" min="1293" max="1293" style="94" width="22.75"/>
+    <col customWidth="1" min="1294" max="1300" style="94" width="13.625"/>
+    <col min="1301" max="1536" style="94" width="9"/>
+    <col customWidth="1" min="1537" max="1537" style="94" width="5.125"/>
+    <col customWidth="1" min="1538" max="1545" style="94" width="9.625"/>
+    <col customWidth="1" min="1546" max="1546" style="94" width="5.125"/>
+    <col min="1547" max="1548" style="94" width="9"/>
+    <col customWidth="1" min="1549" max="1549" style="94" width="22.75"/>
+    <col customWidth="1" min="1550" max="1556" style="94" width="13.625"/>
+    <col min="1557" max="1792" style="94" width="9"/>
+    <col customWidth="1" min="1793" max="1793" style="94" width="5.125"/>
+    <col customWidth="1" min="1794" max="1801" style="94" width="9.625"/>
+    <col customWidth="1" min="1802" max="1802" style="94" width="5.125"/>
+    <col min="1803" max="1804" style="94" width="9"/>
+    <col customWidth="1" min="1805" max="1805" style="94" width="22.75"/>
+    <col customWidth="1" min="1806" max="1812" style="94" width="13.625"/>
+    <col min="1813" max="2048" style="94" width="9"/>
+    <col customWidth="1" min="2049" max="2049" style="94" width="5.125"/>
+    <col customWidth="1" min="2050" max="2057" style="94" width="9.625"/>
+    <col customWidth="1" min="2058" max="2058" style="94" width="5.125"/>
+    <col min="2059" max="2060" style="94" width="9"/>
+    <col customWidth="1" min="2061" max="2061" style="94" width="22.75"/>
+    <col customWidth="1" min="2062" max="2068" style="94" width="13.625"/>
+    <col min="2069" max="2304" style="94" width="9"/>
+    <col customWidth="1" min="2305" max="2305" style="94" width="5.125"/>
+    <col customWidth="1" min="2306" max="2313" style="94" width="9.625"/>
+    <col customWidth="1" min="2314" max="2314" style="94" width="5.125"/>
+    <col min="2315" max="2316" style="94" width="9"/>
+    <col customWidth="1" min="2317" max="2317" style="94" width="22.75"/>
+    <col customWidth="1" min="2318" max="2324" style="94" width="13.625"/>
+    <col min="2325" max="2560" style="94" width="9"/>
+    <col customWidth="1" min="2561" max="2561" style="94" width="5.125"/>
+    <col customWidth="1" min="2562" max="2569" style="94" width="9.625"/>
+    <col customWidth="1" min="2570" max="2570" style="94" width="5.125"/>
+    <col min="2571" max="2572" style="94" width="9"/>
+    <col customWidth="1" min="2573" max="2573" style="94" width="22.75"/>
+    <col customWidth="1" min="2574" max="2580" style="94" width="13.625"/>
+    <col min="2581" max="2816" style="94" width="9"/>
+    <col customWidth="1" min="2817" max="2817" style="94" width="5.125"/>
+    <col customWidth="1" min="2818" max="2825" style="94" width="9.625"/>
+    <col customWidth="1" min="2826" max="2826" style="94" width="5.125"/>
+    <col min="2827" max="2828" style="94" width="9"/>
+    <col customWidth="1" min="2829" max="2829" style="94" width="22.75"/>
+    <col customWidth="1" min="2830" max="2836" style="94" width="13.625"/>
+    <col min="2837" max="3072" style="94" width="9"/>
+    <col customWidth="1" min="3073" max="3073" style="94" width="5.125"/>
+    <col customWidth="1" min="3074" max="3081" style="94" width="9.625"/>
+    <col customWidth="1" min="3082" max="3082" style="94" width="5.125"/>
+    <col min="3083" max="3084" style="94" width="9"/>
+    <col customWidth="1" min="3085" max="3085" style="94" width="22.75"/>
+    <col customWidth="1" min="3086" max="3092" style="94" width="13.625"/>
+    <col min="3093" max="3328" style="94" width="9"/>
+    <col customWidth="1" min="3329" max="3329" style="94" width="5.125"/>
+    <col customWidth="1" min="3330" max="3337" style="94" width="9.625"/>
+    <col customWidth="1" min="3338" max="3338" style="94" width="5.125"/>
+    <col min="3339" max="3340" style="94" width="9"/>
+    <col customWidth="1" min="3341" max="3341" style="94" width="22.75"/>
+    <col customWidth="1" min="3342" max="3348" style="94" width="13.625"/>
+    <col min="3349" max="3584" style="94" width="9"/>
+    <col customWidth="1" min="3585" max="3585" style="94" width="5.125"/>
+    <col customWidth="1" min="3586" max="3593" style="94" width="9.625"/>
+    <col customWidth="1" min="3594" max="3594" style="94" width="5.125"/>
+    <col min="3595" max="3596" style="94" width="9"/>
+    <col customWidth="1" min="3597" max="3597" style="94" width="22.75"/>
+    <col customWidth="1" min="3598" max="3604" style="94" width="13.625"/>
+    <col min="3605" max="3840" style="94" width="9"/>
+    <col customWidth="1" min="3841" max="3841" style="94" width="5.125"/>
+    <col customWidth="1" min="3842" max="3849" style="94" width="9.625"/>
+    <col customWidth="1" min="3850" max="3850" style="94" width="5.125"/>
+    <col min="3851" max="3852" style="94" width="9"/>
+    <col customWidth="1" min="3853" max="3853" style="94" width="22.75"/>
+    <col customWidth="1" min="3854" max="3860" style="94" width="13.625"/>
+    <col min="3861" max="4096" style="94" width="9"/>
+    <col customWidth="1" min="4097" max="4097" style="94" width="5.125"/>
+    <col customWidth="1" min="4098" max="4105" style="94" width="9.625"/>
+    <col customWidth="1" min="4106" max="4106" style="94" width="5.125"/>
+    <col min="4107" max="4108" style="94" width="9"/>
+    <col customWidth="1" min="4109" max="4109" style="94" width="22.75"/>
+    <col customWidth="1" min="4110" max="4116" style="94" width="13.625"/>
+    <col min="4117" max="4352" style="94" width="9"/>
+    <col customWidth="1" min="4353" max="4353" style="94" width="5.125"/>
+    <col customWidth="1" min="4354" max="4361" style="94" width="9.625"/>
+    <col customWidth="1" min="4362" max="4362" style="94" width="5.125"/>
+    <col min="4363" max="4364" style="94" width="9"/>
+    <col customWidth="1" min="4365" max="4365" style="94" width="22.75"/>
+    <col customWidth="1" min="4366" max="4372" style="94" width="13.625"/>
+    <col min="4373" max="4608" style="94" width="9"/>
+    <col customWidth="1" min="4609" max="4609" style="94" width="5.125"/>
+    <col customWidth="1" min="4610" max="4617" style="94" width="9.625"/>
+    <col customWidth="1" min="4618" max="4618" style="94" width="5.125"/>
+    <col min="4619" max="4620" style="94" width="9"/>
+    <col customWidth="1" min="4621" max="4621" style="94" width="22.75"/>
+    <col customWidth="1" min="4622" max="4628" style="94" width="13.625"/>
+    <col min="4629" max="4864" style="94" width="9"/>
+    <col customWidth="1" min="4865" max="4865" style="94" width="5.125"/>
+    <col customWidth="1" min="4866" max="4873" style="94" width="9.625"/>
+    <col customWidth="1" min="4874" max="4874" style="94" width="5.125"/>
+    <col min="4875" max="4876" style="94" width="9"/>
+    <col customWidth="1" min="4877" max="4877" style="94" width="22.75"/>
+    <col customWidth="1" min="4878" max="4884" style="94" width="13.625"/>
+    <col min="4885" max="5120" style="94" width="9"/>
+    <col customWidth="1" min="5121" max="5121" style="94" width="5.125"/>
+    <col customWidth="1" min="5122" max="5129" style="94" width="9.625"/>
+    <col customWidth="1" min="5130" max="5130" style="94" width="5.125"/>
+    <col min="5131" max="5132" style="94" width="9"/>
+    <col customWidth="1" min="5133" max="5133" style="94" width="22.75"/>
+    <col customWidth="1" min="5134" max="5140" style="94" width="13.625"/>
+    <col min="5141" max="5376" style="94" width="9"/>
+    <col customWidth="1" min="5377" max="5377" style="94" width="5.125"/>
+    <col customWidth="1" min="5378" max="5385" style="94" width="9.625"/>
+    <col customWidth="1" min="5386" max="5386" style="94" width="5.125"/>
+    <col min="5387" max="5388" style="94" width="9"/>
+    <col customWidth="1" min="5389" max="5389" style="94" width="22.75"/>
+    <col customWidth="1" min="5390" max="5396" style="94" width="13.625"/>
+    <col min="5397" max="5632" style="94" width="9"/>
+    <col customWidth="1" min="5633" max="5633" style="94" width="5.125"/>
+    <col customWidth="1" min="5634" max="5641" style="94" width="9.625"/>
+    <col customWidth="1" min="5642" max="5642" style="94" width="5.125"/>
+    <col min="5643" max="5644" style="94" width="9"/>
+    <col customWidth="1" min="5645" max="5645" style="94" width="22.75"/>
+    <col customWidth="1" min="5646" max="5652" style="94" width="13.625"/>
+    <col min="5653" max="5888" style="94" width="9"/>
+    <col customWidth="1" min="5889" max="5889" style="94" width="5.125"/>
+    <col customWidth="1" min="5890" max="5897" style="94" width="9.625"/>
+    <col customWidth="1" min="5898" max="5898" style="94" width="5.125"/>
+    <col min="5899" max="5900" style="94" width="9"/>
+    <col customWidth="1" min="5901" max="5901" style="94" width="22.75"/>
+    <col customWidth="1" min="5902" max="5908" style="94" width="13.625"/>
+    <col min="5909" max="6144" style="94" width="9"/>
+    <col customWidth="1" min="6145" max="6145" style="94" width="5.125"/>
+    <col customWidth="1" min="6146" max="6153" style="94" width="9.625"/>
+    <col customWidth="1" min="6154" max="6154" style="94" width="5.125"/>
+    <col min="6155" max="6156" style="94" width="9"/>
+    <col customWidth="1" min="6157" max="6157" style="94" width="22.75"/>
+    <col customWidth="1" min="6158" max="6164" style="94" width="13.625"/>
+    <col min="6165" max="6400" style="94" width="9"/>
+    <col customWidth="1" min="6401" max="6401" style="94" width="5.125"/>
+    <col customWidth="1" min="6402" max="6409" style="94" width="9.625"/>
+    <col customWidth="1" min="6410" max="6410" style="94" width="5.125"/>
+    <col min="6411" max="6412" style="94" width="9"/>
+    <col customWidth="1" min="6413" max="6413" style="94" width="22.75"/>
+    <col customWidth="1" min="6414" max="6420" style="94" width="13.625"/>
+    <col min="6421" max="6656" style="94" width="9"/>
+    <col customWidth="1" min="6657" max="6657" style="94" width="5.125"/>
+    <col customWidth="1" min="6658" max="6665" style="94" width="9.625"/>
+    <col customWidth="1" min="6666" max="6666" style="94" width="5.125"/>
+    <col min="6667" max="6668" style="94" width="9"/>
+    <col customWidth="1" min="6669" max="6669" style="94" width="22.75"/>
+    <col customWidth="1" min="6670" max="6676" style="94" width="13.625"/>
+    <col min="6677" max="6912" style="94" width="9"/>
+    <col customWidth="1" min="6913" max="6913" style="94" width="5.125"/>
+    <col customWidth="1" min="6914" max="6921" style="94" width="9.625"/>
+    <col customWidth="1" min="6922" max="6922" style="94" width="5.125"/>
+    <col min="6923" max="6924" style="94" width="9"/>
+    <col customWidth="1" min="6925" max="6925" style="94" width="22.75"/>
+    <col customWidth="1" min="6926" max="6932" style="94" width="13.625"/>
+    <col min="6933" max="7168" style="94" width="9"/>
+    <col customWidth="1" min="7169" max="7169" style="94" width="5.125"/>
+    <col customWidth="1" min="7170" max="7177" style="94" width="9.625"/>
+    <col customWidth="1" min="7178" max="7178" style="94" width="5.125"/>
+    <col min="7179" max="7180" style="94" width="9"/>
+    <col customWidth="1" min="7181" max="7181" style="94" width="22.75"/>
+    <col customWidth="1" min="7182" max="7188" style="94" width="13.625"/>
+    <col min="7189" max="7424" style="94" width="9"/>
+    <col customWidth="1" min="7425" max="7425" style="94" width="5.125"/>
+    <col customWidth="1" min="7426" max="7433" style="94" width="9.625"/>
+    <col customWidth="1" min="7434" max="7434" style="94" width="5.125"/>
+    <col min="7435" max="7436" style="94" width="9"/>
+    <col customWidth="1" min="7437" max="7437" style="94" width="22.75"/>
+    <col customWidth="1" min="7438" max="7444" style="94" width="13.625"/>
+    <col min="7445" max="7680" style="94" width="9"/>
+    <col customWidth="1" min="7681" max="7681" style="94" width="5.125"/>
+    <col customWidth="1" min="7682" max="7689" style="94" width="9.625"/>
+    <col customWidth="1" min="7690" max="7690" style="94" width="5.125"/>
+    <col min="7691" max="7692" style="94" width="9"/>
+    <col customWidth="1" min="7693" max="7693" style="94" width="22.75"/>
+    <col customWidth="1" min="7694" max="7700" style="94" width="13.625"/>
+    <col min="7701" max="7936" style="94" width="9"/>
+    <col customWidth="1" min="7937" max="7937" style="94" width="5.125"/>
+    <col customWidth="1" min="7938" max="7945" style="94" width="9.625"/>
+    <col customWidth="1" min="7946" max="7946" style="94" width="5.125"/>
+    <col min="7947" max="7948" style="94" width="9"/>
+    <col customWidth="1" min="7949" max="7949" style="94" width="22.75"/>
+    <col customWidth="1" min="7950" max="7956" style="94" width="13.625"/>
+    <col min="7957" max="8192" style="94" width="9"/>
+    <col customWidth="1" min="8193" max="8193" style="94" width="5.125"/>
+    <col customWidth="1" min="8194" max="8201" style="94" width="9.625"/>
+    <col customWidth="1" min="8202" max="8202" style="94" width="5.125"/>
+    <col min="8203" max="8204" style="94" width="9"/>
+    <col customWidth="1" min="8205" max="8205" style="94" width="22.75"/>
+    <col customWidth="1" min="8206" max="8212" style="94" width="13.625"/>
+    <col min="8213" max="8448" style="94" width="9"/>
+    <col customWidth="1" min="8449" max="8449" style="94" width="5.125"/>
+    <col customWidth="1" min="8450" max="8457" style="94" width="9.625"/>
+    <col customWidth="1" min="8458" max="8458" style="94" width="5.125"/>
+    <col min="8459" max="8460" style="94" width="9"/>
+    <col customWidth="1" min="8461" max="8461" style="94" width="22.75"/>
+    <col customWidth="1" min="8462" max="8468" style="94" width="13.625"/>
+    <col min="8469" max="8704" style="94" width="9"/>
+    <col customWidth="1" min="8705" max="8705" style="94" width="5.125"/>
+    <col customWidth="1" min="8706" max="8713" style="94" width="9.625"/>
+    <col customWidth="1" min="8714" max="8714" style="94" width="5.125"/>
+    <col min="8715" max="8716" style="94" width="9"/>
+    <col customWidth="1" min="8717" max="8717" style="94" width="22.75"/>
+    <col customWidth="1" min="8718" max="8724" style="94" width="13.625"/>
+    <col min="8725" max="8960" style="94" width="9"/>
+    <col customWidth="1" min="8961" max="8961" style="94" width="5.125"/>
+    <col customWidth="1" min="8962" max="8969" style="94" width="9.625"/>
+    <col customWidth="1" min="8970" max="8970" style="94" width="5.125"/>
+    <col min="8971" max="8972" style="94" width="9"/>
+    <col customWidth="1" min="8973" max="8973" style="94" width="22.75"/>
+    <col customWidth="1" min="8974" max="8980" style="94" width="13.625"/>
+    <col min="8981" max="9216" style="94" width="9"/>
+    <col customWidth="1" min="9217" max="9217" style="94" width="5.125"/>
+    <col customWidth="1" min="9218" max="9225" style="94" width="9.625"/>
+    <col customWidth="1" min="9226" max="9226" style="94" width="5.125"/>
+    <col min="9227" max="9228" style="94" width="9"/>
+    <col customWidth="1" min="9229" max="9229" style="94" width="22.75"/>
+    <col customWidth="1" min="9230" max="9236" style="94" width="13.625"/>
+    <col min="9237" max="9472" style="94" width="9"/>
+    <col customWidth="1" min="9473" max="9473" style="94" width="5.125"/>
+    <col customWidth="1" min="9474" max="9481" style="94" width="9.625"/>
+    <col customWidth="1" min="9482" max="9482" style="94" width="5.125"/>
+    <col min="9483" max="9484" style="94" width="9"/>
+    <col customWidth="1" min="9485" max="9485" style="94" width="22.75"/>
+    <col customWidth="1" min="9486" max="9492" style="94" width="13.625"/>
+    <col min="9493" max="9728" style="94" width="9"/>
+    <col customWidth="1" min="9729" max="9729" style="94" width="5.125"/>
+    <col customWidth="1" min="9730" max="9737" style="94" width="9.625"/>
+    <col customWidth="1" min="9738" max="9738" style="94" width="5.125"/>
+    <col min="9739" max="9740" style="94" width="9"/>
+    <col customWidth="1" min="9741" max="9741" style="94" width="22.75"/>
+    <col customWidth="1" min="9742" max="9748" style="94" width="13.625"/>
+    <col min="9749" max="9984" style="94" width="9"/>
+    <col customWidth="1" min="9985" max="9985" style="94" width="5.125"/>
+    <col customWidth="1" min="9986" max="9993" style="94" width="9.625"/>
+    <col customWidth="1" min="9994" max="9994" style="94" width="5.125"/>
+    <col min="9995" max="9996" style="94" width="9"/>
+    <col customWidth="1" min="9997" max="9997" style="94" width="22.75"/>
+    <col customWidth="1" min="9998" max="10004" style="94" width="13.625"/>
+    <col min="10005" max="10240" style="94" width="9"/>
+    <col customWidth="1" min="10241" max="10241" style="94" width="5.125"/>
+    <col customWidth="1" min="10242" max="10249" style="94" width="9.625"/>
+    <col customWidth="1" min="10250" max="10250" style="94" width="5.125"/>
+    <col min="10251" max="10252" style="94" width="9"/>
+    <col customWidth="1" min="10253" max="10253" style="94" width="22.75"/>
+    <col customWidth="1" min="10254" max="10260" style="94" width="13.625"/>
+    <col min="10261" max="10496" style="94" width="9"/>
+    <col customWidth="1" min="10497" max="10497" style="94" width="5.125"/>
+    <col customWidth="1" min="10498" max="10505" style="94" width="9.625"/>
+    <col customWidth="1" min="10506" max="10506" style="94" width="5.125"/>
+    <col min="10507" max="10508" style="94" width="9"/>
+    <col customWidth="1" min="10509" max="10509" style="94" width="22.75"/>
+    <col customWidth="1" min="10510" max="10516" style="94" width="13.625"/>
+    <col min="10517" max="10752" style="94" width="9"/>
+    <col customWidth="1" min="10753" max="10753" style="94" width="5.125"/>
+    <col customWidth="1" min="10754" max="10761" style="94" width="9.625"/>
+    <col customWidth="1" min="10762" max="10762" style="94" width="5.125"/>
+    <col min="10763" max="10764" style="94" width="9"/>
+    <col customWidth="1" min="10765" max="10765" style="94" width="22.75"/>
+    <col customWidth="1" min="10766" max="10772" style="94" width="13.625"/>
+    <col min="10773" max="11008" style="94" width="9"/>
+    <col customWidth="1" min="11009" max="11009" style="94" width="5.125"/>
+    <col customWidth="1" min="11010" max="11017" style="94" width="9.625"/>
+    <col customWidth="1" min="11018" max="11018" style="94" width="5.125"/>
+    <col min="11019" max="11020" style="94" width="9"/>
+    <col customWidth="1" min="11021" max="11021" style="94" width="22.75"/>
+    <col customWidth="1" min="11022" max="11028" style="94" width="13.625"/>
+    <col min="11029" max="11264" style="94" width="9"/>
+    <col customWidth="1" min="11265" max="11265" style="94" width="5.125"/>
+    <col customWidth="1" min="11266" max="11273" style="94" width="9.625"/>
+    <col customWidth="1" min="11274" max="11274" style="94" width="5.125"/>
+    <col min="11275" max="11276" style="94" width="9"/>
+    <col customWidth="1" min="11277" max="11277" style="94" width="22.75"/>
+    <col customWidth="1" min="11278" max="11284" style="94" width="13.625"/>
+    <col min="11285" max="11520" style="94" width="9"/>
+    <col customWidth="1" min="11521" max="11521" style="94" width="5.125"/>
+    <col customWidth="1" min="11522" max="11529" style="94" width="9.625"/>
+    <col customWidth="1" min="11530" max="11530" style="94" width="5.125"/>
+    <col min="11531" max="11532" style="94" width="9"/>
+    <col customWidth="1" min="11533" max="11533" style="94" width="22.75"/>
+    <col customWidth="1" min="11534" max="11540" style="94" width="13.625"/>
+    <col min="11541" max="11776" style="94" width="9"/>
+    <col customWidth="1" min="11777" max="11777" style="94" width="5.125"/>
+    <col customWidth="1" min="11778" max="11785" style="94" width="9.625"/>
+    <col customWidth="1" min="11786" max="11786" style="94" width="5.125"/>
+    <col min="11787" max="11788" style="94" width="9"/>
+    <col customWidth="1" min="11789" max="11789" style="94" width="22.75"/>
+    <col customWidth="1" min="11790" max="11796" style="94" width="13.625"/>
+    <col min="11797" max="12032" style="94" width="9"/>
+    <col customWidth="1" min="12033" max="12033" style="94" width="5.125"/>
+    <col customWidth="1" min="12034" max="12041" style="94" width="9.625"/>
+    <col customWidth="1" min="12042" max="12042" style="94" width="5.125"/>
+    <col min="12043" max="12044" style="94" width="9"/>
+    <col customWidth="1" min="12045" max="12045" style="94" width="22.75"/>
+    <col customWidth="1" min="12046" max="12052" style="94" width="13.625"/>
+    <col min="12053" max="12288" style="94" width="9"/>
+    <col customWidth="1" min="12289" max="12289" style="94" width="5.125"/>
+    <col customWidth="1" min="12290" max="12297" style="94" width="9.625"/>
+    <col customWidth="1" min="12298" max="12298" style="94" width="5.125"/>
+    <col min="12299" max="12300" style="94" width="9"/>
+    <col customWidth="1" min="12301" max="12301" style="94" width="22.75"/>
+    <col customWidth="1" min="12302" max="12308" style="94" width="13.625"/>
+    <col min="12309" max="12544" style="94" width="9"/>
+    <col customWidth="1" min="12545" max="12545" style="94" width="5.125"/>
+    <col customWidth="1" min="12546" max="12553" style="94" width="9.625"/>
+    <col customWidth="1" min="12554" max="12554" style="94" width="5.125"/>
+    <col min="12555" max="12556" style="94" width="9"/>
+    <col customWidth="1" min="12557" max="12557" style="94" width="22.75"/>
+    <col customWidth="1" min="12558" max="12564" style="94" width="13.625"/>
+    <col min="12565" max="12800" style="94" width="9"/>
+    <col customWidth="1" min="12801" max="12801" style="94" width="5.125"/>
+    <col customWidth="1" min="12802" max="12809" style="94" width="9.625"/>
+    <col customWidth="1" min="12810" max="12810" style="94" width="5.125"/>
+    <col min="12811" max="12812" style="94" width="9"/>
+    <col customWidth="1" min="12813" max="12813" style="94" width="22.75"/>
+    <col customWidth="1" min="12814" max="12820" style="94" width="13.625"/>
+    <col min="12821" max="13056" style="94" width="9"/>
+    <col customWidth="1" min="13057" max="13057" style="94" width="5.125"/>
+    <col customWidth="1" min="13058" max="13065" style="94" width="9.625"/>
+    <col customWidth="1" min="13066" max="13066" style="94" width="5.125"/>
+    <col min="13067" max="13068" style="94" width="9"/>
+    <col customWidth="1" min="13069" max="13069" style="94" width="22.75"/>
+    <col customWidth="1" min="13070" max="13076" style="94" width="13.625"/>
+    <col min="13077" max="13312" style="94" width="9"/>
+    <col customWidth="1" min="13313" max="13313" style="94" width="5.125"/>
+    <col customWidth="1" min="13314" max="13321" style="94" width="9.625"/>
+    <col customWidth="1" min="13322" max="13322" style="94" width="5.125"/>
+    <col min="13323" max="13324" style="94" width="9"/>
+    <col customWidth="1" min="13325" max="13325" style="94" width="22.75"/>
+    <col customWidth="1" min="13326" max="13332" style="94" width="13.625"/>
+    <col min="13333" max="13568" style="94" width="9"/>
+    <col customWidth="1" min="13569" max="13569" style="94" width="5.125"/>
+    <col customWidth="1" min="13570" max="13577" style="94" width="9.625"/>
+    <col customWidth="1" min="13578" max="13578" style="94" width="5.125"/>
+    <col min="13579" max="13580" style="94" width="9"/>
+    <col customWidth="1" min="13581" max="13581" style="94" width="22.75"/>
+    <col customWidth="1" min="13582" max="13588" style="94" width="13.625"/>
+    <col min="13589" max="13824" style="94" width="9"/>
+    <col customWidth="1" min="13825" max="13825" style="94" width="5.125"/>
+    <col customWidth="1" min="13826" max="13833" style="94" width="9.625"/>
+    <col customWidth="1" min="13834" max="13834" style="94" width="5.125"/>
+    <col min="13835" max="13836" style="94" width="9"/>
+    <col customWidth="1" min="13837" max="13837" style="94" width="22.75"/>
+    <col customWidth="1" min="13838" max="13844" style="94" width="13.625"/>
+    <col min="13845" max="14080" style="94" width="9"/>
+    <col customWidth="1" min="14081" max="14081" style="94" width="5.125"/>
+    <col customWidth="1" min="14082" max="14089" style="94" width="9.625"/>
+    <col customWidth="1" min="14090" max="14090" style="94" width="5.125"/>
+    <col min="14091" max="14092" style="94" width="9"/>
+    <col customWidth="1" min="14093" max="14093" style="94" width="22.75"/>
+    <col customWidth="1" min="14094" max="14100" style="94" width="13.625"/>
+    <col min="14101" max="14336" style="94" width="9"/>
+    <col customWidth="1" min="14337" max="14337" style="94" width="5.125"/>
+    <col customWidth="1" min="14338" max="14345" style="94" width="9.625"/>
+    <col customWidth="1" min="14346" max="14346" style="94" width="5.125"/>
+    <col min="14347" max="14348" style="94" width="9"/>
+    <col customWidth="1" min="14349" max="14349" style="94" width="22.75"/>
+    <col customWidth="1" min="14350" max="14356" style="94" width="13.625"/>
+    <col min="14357" max="14592" style="94" width="9"/>
+    <col customWidth="1" min="14593" max="14593" style="94" width="5.125"/>
+    <col customWidth="1" min="14594" max="14601" style="94" width="9.625"/>
+    <col customWidth="1" min="14602" max="14602" style="94" width="5.125"/>
+    <col min="14603" max="14604" style="94" width="9"/>
+    <col customWidth="1" min="14605" max="14605" style="94" width="22.75"/>
+    <col customWidth="1" min="14606" max="14612" style="94" width="13.625"/>
+    <col min="14613" max="14848" style="94" width="9"/>
+    <col customWidth="1" min="14849" max="14849" style="94" width="5.125"/>
+    <col customWidth="1" min="14850" max="14857" style="94" width="9.625"/>
+    <col customWidth="1" min="14858" max="14858" style="94" width="5.125"/>
+    <col min="14859" max="14860" style="94" width="9"/>
+    <col customWidth="1" min="14861" max="14861" style="94" width="22.75"/>
+    <col customWidth="1" min="14862" max="14868" style="94" width="13.625"/>
+    <col min="14869" max="15104" style="94" width="9"/>
+    <col customWidth="1" min="15105" max="15105" style="94" width="5.125"/>
+    <col customWidth="1" min="15106" max="15113" style="94" width="9.625"/>
+    <col customWidth="1" min="15114" max="15114" style="94" width="5.125"/>
+    <col min="15115" max="15116" style="94" width="9"/>
+    <col customWidth="1" min="15117" max="15117" style="94" width="22.75"/>
+    <col customWidth="1" min="15118" max="15124" style="94" width="13.625"/>
+    <col min="15125" max="15360" style="94" width="9"/>
+    <col customWidth="1" min="15361" max="15361" style="94" width="5.125"/>
+    <col customWidth="1" min="15362" max="15369" style="94" width="9.625"/>
+    <col customWidth="1" min="15370" max="15370" style="94" width="5.125"/>
+    <col min="15371" max="15372" style="94" width="9"/>
+    <col customWidth="1" min="15373" max="15373" style="94" width="22.75"/>
+    <col customWidth="1" min="15374" max="15380" style="94" width="13.625"/>
+    <col min="15381" max="15616" style="94" width="9"/>
+    <col customWidth="1" min="15617" max="15617" style="94" width="5.125"/>
+    <col customWidth="1" min="15618" max="15625" style="94" width="9.625"/>
+    <col customWidth="1" min="15626" max="15626" style="94" width="5.125"/>
+    <col min="15627" max="15628" style="94" width="9"/>
+    <col customWidth="1" min="15629" max="15629" style="94" width="22.75"/>
+    <col customWidth="1" min="15630" max="15636" style="94" width="13.625"/>
+    <col min="15637" max="15872" style="94" width="9"/>
+    <col customWidth="1" min="15873" max="15873" style="94" width="5.125"/>
+    <col customWidth="1" min="15874" max="15881" style="94" width="9.625"/>
+    <col customWidth="1" min="15882" max="15882" style="94" width="5.125"/>
+    <col min="15883" max="15884" style="94" width="9"/>
+    <col customWidth="1" min="15885" max="15885" style="94" width="22.75"/>
+    <col customWidth="1" min="15886" max="15892" style="94" width="13.625"/>
+    <col min="15893" max="16128" style="94" width="9"/>
+    <col customWidth="1" min="16129" max="16129" style="94" width="5.125"/>
+    <col customWidth="1" min="16130" max="16137" style="94" width="9.625"/>
+    <col customWidth="1" min="16138" max="16138" style="94" width="5.125"/>
+    <col min="16139" max="16140" style="94" width="9"/>
+    <col customWidth="1" min="16141" max="16141" style="94" width="22.75"/>
+    <col customWidth="1" min="16142" max="16148" style="94" width="13.625"/>
+    <col min="16149" max="16384" style="94" width="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="15">
-      <c r="A1" s="94" t="s">
-        <v>125</v>
-      </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="94"/>
-      <c r="L1" s="94"/>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
+      <c r="A1" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="94"/>
-      <c r="B2" s="94"/>
-      <c r="C2" s="94"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="94"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="94"/>
+      <c r="A2" s="95"/>
+      <c r="B2" s="95"/>
+      <c r="C2" s="95"/>
+      <c r="D2" s="95"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
     </row>
     <row r="3" ht="15"/>
     <row r="4" ht="15"/>
     <row r="5" ht="15">
-      <c r="A5" s="93" t="str">
+      <c r="A5" s="94" t="str">
         <f>CONCATENATE("■ 계  약  명 : ",환경설정!$B$1)</f>
         <v xml:space="preserve">■ 계  약  명 : 전라남도청 민원인 전용주차장 건립 전기공사 보안등주 등 구매</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
-      <c r="C6" s="95"/>
-      <c r="D6" s="96"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="96"/>
-      <c r="G6" s="96"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="97"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="93" t="s">
-        <v>127</v>
-      </c>
-      <c r="C7" s="96"/>
-      <c r="D7" s="96"/>
-      <c r="E7" s="96"/>
-      <c r="F7" s="96"/>
-      <c r="G7" s="96"/>
+      <c r="A7" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="C7" s="97"/>
+      <c r="D7" s="97"/>
+      <c r="E7" s="97"/>
+      <c r="F7" s="97"/>
+      <c r="G7" s="97"/>
     </row>
     <row r="8" ht="15" customHeight="1">
-      <c r="C8" s="96"/>
-      <c r="D8" s="96"/>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="96"/>
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
     </row>
     <row r="9" ht="15"/>
     <row r="10" ht="15"/>
     <row r="11" ht="15"/>
     <row r="12" ht="15"/>
     <row r="13" ht="15">
-      <c r="C13" s="97"/>
-      <c r="D13" s="97"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="97"/>
-      <c r="G13" s="97"/>
+      <c r="C13" s="98"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="98"/>
+      <c r="F13" s="98"/>
+      <c r="G13" s="98"/>
     </row>
     <row r="14" ht="15">
-      <c r="C14" s="97"/>
-      <c r="D14" s="97"/>
-      <c r="E14" s="97"/>
-      <c r="F14" s="97"/>
-      <c r="G14" s="97"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
     </row>
     <row r="15" ht="15"/>
     <row r="16" ht="15"/>
     <row r="17" ht="15"/>
     <row r="18" ht="15"/>
     <row r="19" ht="15">
-      <c r="C19" s="97"/>
-      <c r="D19" s="97"/>
-      <c r="E19" s="97"/>
-      <c r="F19" s="97"/>
-      <c r="G19" s="97"/>
+      <c r="C19" s="98"/>
+      <c r="D19" s="98"/>
+      <c r="E19" s="98"/>
+      <c r="F19" s="98"/>
+      <c r="G19" s="98"/>
     </row>
     <row r="20" ht="15">
-      <c r="C20" s="97"/>
-      <c r="D20" s="97"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
+      <c r="C20" s="98"/>
+      <c r="D20" s="98"/>
+      <c r="E20" s="98"/>
+      <c r="F20" s="98"/>
+      <c r="G20" s="98"/>
     </row>
     <row r="21" ht="15"/>
     <row r="22" ht="15"/>
     <row r="23" ht="15"/>
     <row r="24" ht="15"/>
     <row r="25" ht="15">
-      <c r="C25" s="97"/>
-      <c r="D25" s="97"/>
-      <c r="E25" s="97"/>
-      <c r="F25" s="97"/>
-      <c r="G25" s="97"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
     </row>
     <row r="26" ht="15">
-      <c r="C26" s="97"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="97"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
     </row>
     <row r="27" ht="15"/>
     <row r="28" ht="15"/>
     <row r="29" ht="15"/>
     <row r="30" ht="15"/>
     <row r="31" ht="15">
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
+      <c r="C31" s="98"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
     </row>
     <row r="32" ht="15">
-      <c r="C32" s="97"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
+      <c r="C32" s="98"/>
+      <c r="D32" s="98"/>
+      <c r="E32" s="98"/>
+      <c r="F32" s="98"/>
+      <c r="G32" s="98"/>
     </row>
     <row r="33" ht="15"/>
     <row r="34" ht="15"/>
     <row r="35" ht="15"/>
     <row r="36" ht="15"/>
     <row r="37" ht="26.25">
-      <c r="C37" s="97"/>
-      <c r="D37" s="97"/>
-      <c r="E37" s="97"/>
-      <c r="F37" s="97"/>
-      <c r="G37" s="97"/>
+      <c r="C37" s="98"/>
+      <c r="D37" s="98"/>
+      <c r="E37" s="98"/>
+      <c r="F37" s="98"/>
+      <c r="G37" s="98"/>
     </row>
     <row r="38" ht="15"/>
     <row r="39" ht="15"/>
@@ -7579,26 +7590,26 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1"/>
     <row r="2" ht="33.75" customHeight="1">
-      <c r="A2" s="98" t="s">
-        <v>128</v>
-      </c>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
+      <c r="A2" s="99" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="99"/>
+      <c r="C2" s="99"/>
+      <c r="D2" s="99"/>
+      <c r="E2" s="99"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="B3" s="99"/>
-      <c r="C3" s="99"/>
-      <c r="D3" s="99"/>
-      <c r="E3" s="99"/>
-      <c r="F3" s="99"/>
-      <c r="G3" s="99"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
     </row>
     <row r="4" ht="26.25" customHeight="1">
-      <c r="B4" s="100" t="s">
+      <c r="B4" s="101" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="45" t="str">
@@ -7611,168 +7622,168 @@
       <c r="G4" s="45"/>
     </row>
     <row r="5" ht="26.25" customHeight="1">
-      <c r="B5" s="100" t="s">
-        <v>129</v>
-      </c>
-      <c r="C5" s="101">
+      <c r="B5" s="101" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="102">
         <f>환경설정!B3</f>
         <v>45846</v>
       </c>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="103"/>
     </row>
     <row r="6" ht="26.25" customHeight="1">
-      <c r="B6" s="100" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="101">
+      <c r="B6" s="101" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="102">
         <f>환경설정!D3</f>
         <v>46380</v>
       </c>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
     </row>
     <row r="7" ht="26.25" customHeight="1">
-      <c r="B7" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="101" t="s">
-        <v>132</v>
-      </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
+      <c r="B7" s="101" t="s">
+        <v>129</v>
+      </c>
+      <c r="C7" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
     </row>
     <row r="8" ht="8.25" customHeight="1">
-      <c r="B8" s="103"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
       <c r="F8" s="40"/>
       <c r="G8" s="40"/>
     </row>
     <row r="9" ht="29.25" customHeight="1">
       <c r="B9" s="49" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="B10" s="106" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="105" t="s">
+      <c r="D10" s="107" t="s">
         <v>134</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="E10" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="F10" s="108" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="107" t="s">
-        <v>138</v>
-      </c>
     </row>
     <row r="11" ht="35.100000000000001" customHeight="1">
-      <c r="B11" s="108" t="str">
+      <c r="B11" s="109" t="str">
         <f>VLOOKUP(환경설정!$B$8,data!$A:$C,2,0)</f>
         <v>철제가로등주</v>
       </c>
-      <c r="C11" s="109" t="str">
+      <c r="C11" s="110" t="str">
         <f>VLOOKUP(환경설정!$B$8,data!$A:$C,3,0)</f>
         <v xml:space="preserve">철제가로등주, MTPF-201-5, 5m, 1등용, 원2단형</v>
       </c>
-      <c r="D11" s="110" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11" s="110">
+      <c r="D11" s="111" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="111">
         <f>환경설정!B9</f>
         <v>9</v>
       </c>
-      <c r="F11" s="111"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" ht="35.100000000000001" customHeight="1">
-      <c r="B12" s="112" t="e">
+      <c r="B12" s="113" t="e">
         <f>IF(환경설정!B5&gt;=2,VLOOKUP(환경설정!$G$8,data!$A:$C,2,0),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C12" s="109" t="e">
+      <c r="C12" s="110" t="e">
         <f>IF(환경설정!B5&gt;=2,VLOOKUP(환경설정!$G$8,data!$A:$C,3,0),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="D12" s="113" t="str">
+      <c r="D12" s="114" t="str">
         <f>IF(환경설정!B5&gt;=2,"EA","")</f>
         <v>EA</v>
       </c>
-      <c r="E12" s="113">
+      <c r="E12" s="114">
         <f>IF(환경설정!B5&gt;=2,환경설정!G9,"")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="111"/>
+      <c r="F12" s="112"/>
     </row>
     <row r="13" ht="35.100000000000001" customHeight="1">
-      <c r="B13" s="112" t="e">
+      <c r="B13" s="113" t="e">
         <f>IF(환경설정!B5&gt;=3,VLOOKUP(환경설정!$L$8,data!$A:$C,2,0),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="C13" s="114" t="e">
+      <c r="C13" s="115" t="e">
         <f>IF(환경설정!B5&gt;=3,VLOOKUP(환경설정!$L$8,data!$A:$C,3,0),"")</f>
         <v>#N/A</v>
       </c>
-      <c r="D13" s="113" t="str">
+      <c r="D13" s="114" t="str">
         <f>IF(환경설정!B5&gt;=3,"EA","")</f>
         <v>EA</v>
       </c>
-      <c r="E13" s="113">
+      <c r="E13" s="114">
         <f>IF(환경설정!B5&gt;=3,환경설정!L9,"")</f>
         <v>0</v>
       </c>
-      <c r="F13" s="115"/>
+      <c r="F13" s="116"/>
     </row>
     <row r="14" ht="35.100000000000001" customHeight="1">
-      <c r="B14" s="112"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="115"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="115"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="116"/>
     </row>
     <row r="15" ht="35.100000000000001" customHeight="1">
-      <c r="B15" s="112"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="115"/>
+      <c r="B15" s="113"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="114"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="116"/>
     </row>
     <row r="16" ht="35.100000000000001" customHeight="1">
-      <c r="B16" s="116"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="115"/>
+      <c r="B16" s="117"/>
+      <c r="C16" s="115"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="116"/>
     </row>
     <row r="17" ht="35.100000000000001" customHeight="1">
-      <c r="B17" s="112"/>
-      <c r="C17" s="114"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="115"/>
+      <c r="B17" s="113"/>
+      <c r="C17" s="115"/>
+      <c r="D17" s="114"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="116"/>
     </row>
     <row r="18" ht="35.100000000000001" customHeight="1">
-      <c r="B18" s="117"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="120"/>
+      <c r="E18" s="120"/>
+      <c r="F18" s="121"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="F19" s="49"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -7796,28 +7807,28 @@
     </row>
     <row r="23" ht="18" customHeight="1"/>
     <row r="24" ht="23.25" customHeight="1">
-      <c r="D24" s="121" t="s">
+      <c r="D24" s="122" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="121"/>
-      <c r="F24" s="121"/>
-      <c r="G24" s="121"/>
+      <c r="E24" s="122"/>
+      <c r="F24" s="122"/>
+      <c r="G24" s="122"/>
     </row>
     <row r="25" ht="23.25" customHeight="1">
-      <c r="D25" s="121" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
-      <c r="G25" s="121"/>
+      <c r="D25" s="123" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="123"/>
+      <c r="F25" s="123"/>
+      <c r="G25" s="123"/>
     </row>
     <row r="26" ht="23.25" customHeight="1">
-      <c r="D26" s="122" t="s">
-        <v>80</v>
-      </c>
-      <c r="E26" s="122"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="122"/>
+      <c r="D26" s="124" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
     </row>
     <row r="27" ht="20.100000000000001" customHeight="1"/>
     <row r="28" ht="24" customHeight="1">
@@ -7866,4007 +7877,4007 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C1" t="str">
         <f t="shared" ref="C1:C64" si="0">CONCATENATE(B1,", ",A1,", ",E1)</f>
         <v xml:space="preserve">LED투광등기구, ARENA-200S, 200W</v>
       </c>
       <c r="E1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C2" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-300S, 300W</v>
       </c>
       <c r="E2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-400(3000K), 400W</v>
       </c>
       <c r="E3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-400, 400W</v>
       </c>
       <c r="E4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-400S, 400W</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-500(3000K), 500W</v>
       </c>
       <c r="E6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-500, 500W</v>
       </c>
       <c r="E7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-600(3000K), 600W</v>
       </c>
       <c r="E8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B9" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C9" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-600, 600W</v>
       </c>
       <c r="E9" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-800(3000K), 800W</v>
       </c>
       <c r="E10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C11" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA-800, 800W</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-200S, 200W</v>
       </c>
       <c r="E12" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C13" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-300S, 300W</v>
       </c>
       <c r="E13" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-400, 400W</v>
       </c>
       <c r="E14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B15" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-400S, 400W</v>
       </c>
       <c r="E15" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-500, 500W</v>
       </c>
       <c r="E16" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B17" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C17" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-600, 600W</v>
       </c>
       <c r="E17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B18" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C18" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(M)-800, 800W</v>
       </c>
       <c r="E18" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C19" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-200S, 200W</v>
       </c>
       <c r="E19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-300S, 300W</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-400, 400W</v>
       </c>
       <c r="E21" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-400S, 400W</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-500, 500W</v>
       </c>
       <c r="E23" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-600, 600W</v>
       </c>
       <c r="E24" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, ARENA(X)-800, 800W</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED투광등기구, BATOO-200, 200W</v>
       </c>
       <c r="E26" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-008-01, 8W</v>
       </c>
       <c r="E27" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B28" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-008-02, 8W</v>
       </c>
       <c r="E28" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-008-03, 8W</v>
       </c>
       <c r="E29" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-01, 9W</v>
       </c>
       <c r="E30" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-02, 9W</v>
       </c>
       <c r="E31" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B32" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-03, 9W</v>
       </c>
       <c r="E32" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B33" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-04, 9W</v>
       </c>
       <c r="E33" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B34" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-05, 9W</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-06, 9W</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-07, 9W</v>
       </c>
       <c r="E36" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-009-08, 9W</v>
       </c>
       <c r="E37" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-010-01, 10W</v>
       </c>
       <c r="E38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-010-02, 10W</v>
       </c>
       <c r="E39" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-010-03, 10W</v>
       </c>
       <c r="E40" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B41" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-010-04, 10W</v>
       </c>
       <c r="E41" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B42" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-011-01, 11(3+8)W</v>
       </c>
       <c r="E42" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>195</v>
-      </c>
-      <c r="B43" s="123" t="s">
-        <v>196</v>
+        <v>193</v>
+      </c>
+      <c r="B43" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-012-01, 12(4+8)W</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>198</v>
-      </c>
-      <c r="B44" s="123" t="s">
         <v>196</v>
+      </c>
+      <c r="B44" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-012-02, 12W</v>
       </c>
       <c r="E44" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>200</v>
-      </c>
-      <c r="B45" s="123" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="B45" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-012-03, 12W</v>
       </c>
       <c r="E45" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>201</v>
-      </c>
-      <c r="B46" s="123" t="s">
-        <v>196</v>
+        <v>199</v>
+      </c>
+      <c r="B46" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-012-04, 12W</v>
       </c>
       <c r="E46" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>202</v>
-      </c>
-      <c r="B47" s="123" t="s">
-        <v>196</v>
+        <v>200</v>
+      </c>
+      <c r="B47" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-012-05, 12W</v>
       </c>
       <c r="E47" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>203</v>
-      </c>
-      <c r="B48" s="123" t="s">
-        <v>196</v>
+        <v>201</v>
+      </c>
+      <c r="B48" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-015-01, 15W</v>
       </c>
       <c r="E48" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>205</v>
-      </c>
-      <c r="B49" s="123" t="s">
-        <v>196</v>
+        <v>203</v>
+      </c>
+      <c r="B49" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-015-02, 15W</v>
       </c>
       <c r="E49" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>206</v>
-      </c>
-      <c r="B50" s="123" t="s">
-        <v>196</v>
+        <v>204</v>
+      </c>
+      <c r="B50" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-020-01, 20(10×2)W</v>
       </c>
       <c r="E50" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>208</v>
-      </c>
-      <c r="B51" s="123" t="s">
-        <v>196</v>
+        <v>206</v>
+      </c>
+      <c r="B51" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLCP-020-02, 20W</v>
       </c>
       <c r="E51" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>210</v>
-      </c>
-      <c r="B52" s="123" t="s">
-        <v>196</v>
+        <v>208</v>
+      </c>
+      <c r="B52" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-008-01, 8W</v>
       </c>
       <c r="E52" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>211</v>
-      </c>
-      <c r="B53" s="123" t="s">
-        <v>196</v>
+        <v>209</v>
+      </c>
+      <c r="B53" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-008-02, 8W</v>
       </c>
       <c r="E53" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>212</v>
-      </c>
-      <c r="B54" s="123" t="s">
-        <v>196</v>
+        <v>210</v>
+      </c>
+      <c r="B54" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-010-01, 10W</v>
       </c>
       <c r="E54" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>213</v>
-      </c>
-      <c r="B55" s="123" t="s">
-        <v>196</v>
+        <v>211</v>
+      </c>
+      <c r="B55" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-012-01, 12W</v>
       </c>
       <c r="E55" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>214</v>
-      </c>
-      <c r="B56" s="123" t="s">
-        <v>196</v>
+        <v>212</v>
+      </c>
+      <c r="B56" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-012-02, 12W</v>
       </c>
       <c r="E56" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>215</v>
-      </c>
-      <c r="B57" s="123" t="s">
-        <v>196</v>
+        <v>213</v>
+      </c>
+      <c r="B57" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-016-01, 16(8×2)W</v>
       </c>
       <c r="E57" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>217</v>
-      </c>
-      <c r="B58" s="123" t="s">
-        <v>196</v>
+        <v>215</v>
+      </c>
+      <c r="B58" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-020-01, 20W</v>
       </c>
       <c r="E58" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>218</v>
-      </c>
-      <c r="B59" s="123" t="s">
-        <v>196</v>
+        <v>216</v>
+      </c>
+      <c r="B59" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-022-01, 22W</v>
       </c>
       <c r="E59" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>220</v>
-      </c>
-      <c r="B60" s="123" t="s">
-        <v>196</v>
+        <v>218</v>
+      </c>
+      <c r="B60" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLSP-036-01, 36W</v>
       </c>
       <c r="E60" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>222</v>
-      </c>
-      <c r="B61" s="123" t="s">
-        <v>196</v>
+        <v>220</v>
+      </c>
+      <c r="B61" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-BLTP-010-01, 10W</v>
       </c>
       <c r="E61" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>223</v>
-      </c>
-      <c r="B62" s="123" t="s">
-        <v>196</v>
+        <v>221</v>
+      </c>
+      <c r="B62" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLCP-060-01, 60W</v>
       </c>
       <c r="E62" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>225</v>
-      </c>
-      <c r="B63" s="123" t="s">
-        <v>196</v>
+        <v>223</v>
+      </c>
+      <c r="B63" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLCP-120-01, 120W</v>
       </c>
       <c r="E63" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>227</v>
-      </c>
-      <c r="B64" s="123" t="s">
-        <v>196</v>
+        <v>225</v>
+      </c>
+      <c r="B64" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLCP-125-01, 125W</v>
       </c>
       <c r="E64" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>229</v>
-      </c>
-      <c r="B65" s="123" t="s">
-        <v>196</v>
+        <v>227</v>
+      </c>
+      <c r="B65" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" ref="C65:C128" si="1">CONCATENATE(B65,", ",A65,", ",E65)</f>
         <v xml:space="preserve">LED경관조명기구, MT-CLFL-100-01, 100W</v>
       </c>
       <c r="E65" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>231</v>
-      </c>
-      <c r="B66" s="123" t="s">
-        <v>196</v>
+        <v>229</v>
+      </c>
+      <c r="B66" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLFL-150-01, 150(50×3)W</v>
       </c>
       <c r="E66" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>233</v>
-      </c>
-      <c r="B67" s="123" t="s">
-        <v>196</v>
+        <v>231</v>
+      </c>
+      <c r="B67" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLFL-260-01, 259(37×7)W</v>
       </c>
       <c r="E67" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>235</v>
-      </c>
-      <c r="B68" s="123" t="s">
-        <v>196</v>
+        <v>233</v>
+      </c>
+      <c r="B68" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLPL-090-01, 90W</v>
       </c>
       <c r="E68" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>237</v>
-      </c>
-      <c r="B69" s="123" t="s">
-        <v>196</v>
+        <v>235</v>
+      </c>
+      <c r="B69" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLPL-120-01, 120W</v>
       </c>
       <c r="E69" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>238</v>
-      </c>
-      <c r="B70" s="123" t="s">
-        <v>196</v>
+        <v>236</v>
+      </c>
+      <c r="B70" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLSP-030-01, 30W</v>
       </c>
       <c r="E70" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>240</v>
-      </c>
-      <c r="B71" s="123" t="s">
-        <v>196</v>
+        <v>238</v>
+      </c>
+      <c r="B71" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-CLSP-030-02, 30W</v>
       </c>
       <c r="E71" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>241</v>
-      </c>
-      <c r="B72" s="123" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="B72" s="125" t="s">
+        <v>240</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED투광등기구, MT-FL-1000A, 1000W</v>
       </c>
       <c r="E72" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>244</v>
-      </c>
-      <c r="B73" s="123" t="s">
         <v>242</v>
+      </c>
+      <c r="B73" s="125" t="s">
+        <v>240</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED투광등기구, MT-FL-1200A, 1200W</v>
       </c>
       <c r="E73" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>246</v>
-      </c>
-      <c r="B74" s="123" t="s">
-        <v>242</v>
+        <v>244</v>
+      </c>
+      <c r="B74" s="125" t="s">
+        <v>240</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED투광등기구, MT-FL-300A, 300W</v>
       </c>
       <c r="E74" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>247</v>
-      </c>
-      <c r="B75" s="123" t="s">
-        <v>242</v>
+        <v>245</v>
+      </c>
+      <c r="B75" s="125" t="s">
+        <v>240</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED투광등기구, MT-FL-400S, 400W</v>
       </c>
       <c r="E75" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>248</v>
-      </c>
-      <c r="B76" s="123" t="s">
-        <v>242</v>
+        <v>246</v>
+      </c>
+      <c r="B76" s="125" t="s">
+        <v>240</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED투광등기구, MT-FL-600A, 600W</v>
       </c>
       <c r="E76" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>249</v>
-      </c>
-      <c r="B77" s="123" t="s">
-        <v>196</v>
+        <v>247</v>
+      </c>
+      <c r="B77" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-009-01, 9W</v>
       </c>
       <c r="E77" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>250</v>
-      </c>
-      <c r="B78" s="123" t="s">
-        <v>196</v>
+        <v>248</v>
+      </c>
+      <c r="B78" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-012-01, 12W</v>
       </c>
       <c r="E78" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>251</v>
-      </c>
-      <c r="B79" s="123" t="s">
-        <v>196</v>
+        <v>249</v>
+      </c>
+      <c r="B79" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-016-01, 16(8×2)W</v>
       </c>
       <c r="E79" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>252</v>
-      </c>
-      <c r="B80" s="123" t="s">
-        <v>196</v>
+        <v>250</v>
+      </c>
+      <c r="B80" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-018-01, 18W</v>
       </c>
       <c r="E80" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>254</v>
-      </c>
-      <c r="B81" s="123" t="s">
-        <v>196</v>
+        <v>252</v>
+      </c>
+      <c r="B81" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-018-02, 18W</v>
       </c>
       <c r="E81" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>255</v>
-      </c>
-      <c r="B82" s="123" t="s">
-        <v>196</v>
+        <v>253</v>
+      </c>
+      <c r="B82" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-024-01, 24W</v>
       </c>
       <c r="E82" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>257</v>
-      </c>
-      <c r="B83" s="123" t="s">
-        <v>196</v>
+        <v>255</v>
+      </c>
+      <c r="B83" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-024-02, 24W</v>
       </c>
       <c r="E83" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>258</v>
-      </c>
-      <c r="B84" s="123" t="s">
-        <v>196</v>
+        <v>256</v>
+      </c>
+      <c r="B84" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-025-01, 25W</v>
       </c>
       <c r="E84" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>260</v>
-      </c>
-      <c r="B85" s="123" t="s">
-        <v>196</v>
+        <v>258</v>
+      </c>
+      <c r="B85" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-036-01, 36W</v>
       </c>
       <c r="E85" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>261</v>
-      </c>
-      <c r="B86" s="123" t="s">
-        <v>196</v>
+        <v>259</v>
+      </c>
+      <c r="B86" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-045-01, 45W</v>
       </c>
       <c r="E86" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>263</v>
-      </c>
-      <c r="B87" s="123" t="s">
-        <v>196</v>
+        <v>261</v>
+      </c>
+      <c r="B87" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-048-01, 48W</v>
       </c>
       <c r="E87" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>265</v>
-      </c>
-      <c r="B88" s="123" t="s">
-        <v>196</v>
+        <v>263</v>
+      </c>
+      <c r="B88" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-050-01, 50W</v>
       </c>
       <c r="E88" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>267</v>
-      </c>
-      <c r="B89" s="123" t="s">
-        <v>196</v>
+        <v>265</v>
+      </c>
+      <c r="B89" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-060-01, 60W</v>
       </c>
       <c r="E89" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>268</v>
-      </c>
-      <c r="B90" s="123" t="s">
-        <v>196</v>
+        <v>266</v>
+      </c>
+      <c r="B90" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-060-02, 60W</v>
       </c>
       <c r="E90" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>269</v>
-      </c>
-      <c r="B91" s="123" t="s">
-        <v>196</v>
+        <v>267</v>
+      </c>
+      <c r="B91" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-060-03, 60W</v>
       </c>
       <c r="E91" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>270</v>
-      </c>
-      <c r="B92" s="123" t="s">
-        <v>196</v>
+        <v>268</v>
+      </c>
+      <c r="B92" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-072-01, 72W</v>
       </c>
       <c r="E92" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>272</v>
-      </c>
-      <c r="B93" s="123" t="s">
-        <v>196</v>
+        <v>270</v>
+      </c>
+      <c r="B93" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLCR-072-02, 72W</v>
       </c>
       <c r="E93" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>273</v>
-      </c>
-      <c r="B94" s="123" t="s">
-        <v>196</v>
+        <v>271</v>
+      </c>
+      <c r="B94" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-050-01, 50W</v>
       </c>
       <c r="E94" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>274</v>
-      </c>
-      <c r="B95" s="123" t="s">
-        <v>196</v>
+        <v>272</v>
+      </c>
+      <c r="B95" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-060-01, 60W</v>
       </c>
       <c r="E95" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>275</v>
-      </c>
-      <c r="B96" s="123" t="s">
-        <v>196</v>
+        <v>273</v>
+      </c>
+      <c r="B96" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-100-01, 100W</v>
       </c>
       <c r="E96" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>276</v>
-      </c>
-      <c r="B97" s="123" t="s">
-        <v>196</v>
+        <v>274</v>
+      </c>
+      <c r="B97" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-120-01, 120W</v>
       </c>
       <c r="E97" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>277</v>
-      </c>
-      <c r="B98" s="123" t="s">
-        <v>196</v>
+        <v>275</v>
+      </c>
+      <c r="B98" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-150-01, 150W</v>
       </c>
       <c r="E98" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>279</v>
-      </c>
-      <c r="B99" s="123" t="s">
-        <v>196</v>
+        <v>277</v>
+      </c>
+      <c r="B99" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-200-01, 200W</v>
       </c>
       <c r="E99" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>280</v>
-      </c>
-      <c r="B100" s="123" t="s">
-        <v>196</v>
+        <v>278</v>
+      </c>
+      <c r="B100" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-260-01, 260W</v>
       </c>
       <c r="E100" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>282</v>
-      </c>
-      <c r="B101" s="123" t="s">
-        <v>196</v>
+        <v>280</v>
+      </c>
+      <c r="B101" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-450-01, 450W</v>
       </c>
       <c r="E101" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>284</v>
-      </c>
-      <c r="B102" s="123" t="s">
-        <v>196</v>
+        <v>282</v>
+      </c>
+      <c r="B102" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-520-01, 520W</v>
       </c>
       <c r="E102" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>286</v>
-      </c>
-      <c r="B103" s="123" t="s">
-        <v>196</v>
+        <v>284</v>
+      </c>
+      <c r="B103" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FLSQ-900-01, 900W</v>
       </c>
       <c r="E103" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>288</v>
-      </c>
-      <c r="B104" s="123" t="s">
-        <v>196</v>
+        <v>286</v>
+      </c>
+      <c r="B104" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FXWR-012-01, 12W</v>
       </c>
       <c r="E104" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>289</v>
-      </c>
-      <c r="B105" s="123" t="s">
-        <v>196</v>
+        <v>287</v>
+      </c>
+      <c r="B105" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-FXWR-023-01, 23W</v>
       </c>
       <c r="E105" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>291</v>
-      </c>
-      <c r="B106" s="123" t="s">
-        <v>196</v>
+        <v>289</v>
+      </c>
+      <c r="B106" s="125" t="s">
+        <v>194</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBSQ-011-01, 11W</v>
       </c>
       <c r="E106" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B107" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBSQ-015-01, 15W</v>
       </c>
       <c r="E107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBSQ-015-02, 15W</v>
       </c>
       <c r="E108" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B109" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-008-01, 8W</v>
       </c>
       <c r="E109" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B110" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-012-01, 12W</v>
       </c>
       <c r="E110" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B111" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-015-01, 15W</v>
       </c>
       <c r="E111" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B112" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-018-01, 18W</v>
       </c>
       <c r="E112" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B113" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-018-02, 18W</v>
       </c>
       <c r="E113" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B114" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-021-01, 21W</v>
       </c>
       <c r="E114" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B115" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-021-02, 21W</v>
       </c>
       <c r="E115" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B116" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-024-01, 24W</v>
       </c>
       <c r="E116" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B117" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-024-02, 24W</v>
       </c>
       <c r="E117" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B118" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-024-03, 24W</v>
       </c>
       <c r="E118" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B119" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-036-01, 36W</v>
       </c>
       <c r="E119" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B120" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-036-02, 36W</v>
       </c>
       <c r="E120" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B121" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-036-03, 36W</v>
       </c>
       <c r="E121" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B122" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-036-04, 36W</v>
       </c>
       <c r="E122" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B123" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LBST-054-01, 54W</v>
       </c>
       <c r="E123" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B124" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LFST-048-01, 48W</v>
       </c>
       <c r="E124" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B125" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LFST-072-01, 72W</v>
       </c>
       <c r="E125" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B126" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LFST-072-02, 72W</v>
       </c>
       <c r="E126" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B127" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LFST-072-03, 72W</v>
       </c>
       <c r="E127" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B128" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">LED경관조명기구, MT-LFST-144-01, 144W</v>
       </c>
       <c r="E128" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" ref="C129:C192" si="2">CONCATENATE(B129,", ",A129,", ",E129)</f>
         <v xml:space="preserve">LED경관조명기구, MT-MLSP-012-01, 12W</v>
       </c>
       <c r="E129" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-MLSP-012-02, 12W</v>
       </c>
       <c r="E130" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B131" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-MLSQ-009-01, 9W</v>
       </c>
       <c r="E131" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B132" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBEL-005-01, 5W</v>
       </c>
       <c r="E132" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B133" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBEL-3_5-01, 3.5W</v>
       </c>
       <c r="E133" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B134" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSC-100-01, 100W</v>
       </c>
       <c r="E134" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B135" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSQ-005-01, 5W</v>
       </c>
       <c r="E135" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B136" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSQ-005-02, 3.5W</v>
       </c>
       <c r="E136" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B137" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSR-005-01, 3.5W</v>
       </c>
       <c r="E137" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B138" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSR-007-01, 7W</v>
       </c>
       <c r="E138" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B139" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-OBSR-007-02, 7W</v>
       </c>
       <c r="E139" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B140" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SCBC-005-01, 5W</v>
       </c>
       <c r="E140" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B141" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SCPL-120-01, 120W</v>
       </c>
       <c r="E141" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B142" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLA-030, 30W</v>
       </c>
       <c r="E142" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B143" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLA-040, 40W</v>
       </c>
       <c r="E143" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B144" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLA-050, 50W</v>
       </c>
       <c r="E144" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B145" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA-075, 75W</v>
       </c>
       <c r="E145" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B146" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA-100, 100W</v>
       </c>
       <c r="E146" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B147" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA-125, 125W</v>
       </c>
       <c r="E147" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B148" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA-150, 150W</v>
       </c>
       <c r="E148" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B149" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C149" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLA(D)-040, 40W</v>
       </c>
       <c r="E149" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B150" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C150" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLA(D)-050, 50W</v>
       </c>
       <c r="E150" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B151" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA(D)-100, 100W</v>
       </c>
       <c r="E151" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B152" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA(D)-125, 125W</v>
       </c>
       <c r="E152" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B153" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLA(D)-150, 150W</v>
       </c>
       <c r="E153" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B154" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLC-025-35, 25W</v>
       </c>
       <c r="E154" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B155" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLC-050-35, 50W</v>
       </c>
       <c r="E155" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B156" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED보안등기구, MT-SLC-060, 60W</v>
       </c>
       <c r="E156" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B157" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-075-40, 75W</v>
       </c>
       <c r="E157" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B158" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-075-45, 75W</v>
       </c>
       <c r="E158" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B159" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-075, 75W</v>
       </c>
       <c r="E159" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B160" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-100-40, 100W</v>
       </c>
       <c r="E160" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B161" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-100-45, 100W</v>
       </c>
       <c r="E161" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B162" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-125-40, 125W</v>
       </c>
       <c r="E162" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B163" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-125-45, 125W</v>
       </c>
       <c r="E163" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B164" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-150-40, 150W</v>
       </c>
       <c r="E164" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B165" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-150-45, 150W</v>
       </c>
       <c r="E165" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B166" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-200, 200W</v>
       </c>
       <c r="E166" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B167" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED가로등기구, MT-SLC-240, 240W</v>
       </c>
       <c r="E167" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B168" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SPAR-008-01, 8W</v>
       </c>
       <c r="E168" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B169" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SPCR-1_8-01, 1.8W</v>
       </c>
       <c r="E169" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B170" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SPEL-012-01, 12W</v>
       </c>
       <c r="E170" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B171" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-SPWR-005-01, 5W</v>
       </c>
       <c r="E171" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B172" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-003-01, 3W</v>
       </c>
       <c r="E172" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B173" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-004-01, 4W</v>
       </c>
       <c r="E173" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B174" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-005-01, 5W</v>
       </c>
       <c r="E174" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-012-01, 12W</v>
       </c>
       <c r="E175" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-014-01, 14W</v>
       </c>
       <c r="E176" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B177" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-016-01, 16(8×2)W</v>
       </c>
       <c r="E177" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B178" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-ULCR-032-01, 32W</v>
       </c>
       <c r="E178" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B179" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED투광등기구, MT-VM, (부품)눈부심방지장치</v>
       </c>
       <c r="E179" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B180" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMCP-024-01, 24W</v>
       </c>
       <c r="E180" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B181" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMCR-020-01, 20(10×2)W</v>
       </c>
       <c r="E181" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B182" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMCR-030-01, 30W</v>
       </c>
       <c r="E182" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B183" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMSQ-003-01, 3W</v>
       </c>
       <c r="E183" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B184" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMSQ-006-01, 6W</v>
       </c>
       <c r="E184" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B185" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMSQ-006-02, 6W</v>
       </c>
       <c r="E185" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B186" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMSQ-006-03, 6W</v>
       </c>
       <c r="E186" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B187" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WMSQ-006-04, 6W</v>
       </c>
       <c r="E187" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B188" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED경관조명기구, MT-WPCR-016-01, 16(8×2)W</v>
       </c>
       <c r="E188" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B189" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED투광등기구, STA-400, 400W</v>
       </c>
       <c r="E189" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B190" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED투광등기구, STA-500, 500W</v>
       </c>
       <c r="E190" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B191" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED투광등기구, STA-600, 600W</v>
       </c>
       <c r="E191" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B192" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">LED투광등기구, STA-700, 700W</v>
       </c>
       <c r="E192" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B193" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" ref="C193:C256" si="3">CONCATENATE(B193,", ",A193,", ",E193)</f>
         <v xml:space="preserve">LED투광등기구, STA-800, 800W</v>
       </c>
       <c r="E193" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B194" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">LED투광등기구, STA(M)-1000, 1000W</v>
       </c>
       <c r="E194" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B195" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">LED투광등기구, STA(M)-1200, 1200W</v>
       </c>
       <c r="E195" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B196" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E196" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B197" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-10-2, 10m, 2등용, 원2단형</v>
       </c>
       <c r="E197" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B198" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-12, 12m, 1등용, 원2단형</v>
       </c>
       <c r="E198" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B199" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-12-2, 12m, 2등용, 원2단형</v>
       </c>
       <c r="E199" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="B200" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-8-2, 8m, 2등용, 원2단형</v>
       </c>
       <c r="E200" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B201" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E201" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B202" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-9-2, 9m, 2등용, 원2단형</v>
       </c>
       <c r="E202" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B203" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-101-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E203" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B204" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-201-4-2, 4m, 2등용, 원2단형</v>
       </c>
       <c r="E204" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B205" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-201-4, 4m, 1등용, 원2단형</v>
       </c>
       <c r="E205" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B206" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-201-5-2, 5m, 2등용, 원2단형</v>
       </c>
       <c r="E206" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B207" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">철제가로등주, MTPF-201-5, 5m, 1등용, 원2단형</v>
       </c>
       <c r="E207" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B208" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-101-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E208" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B209" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-101-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E209" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B210" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-101-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E210" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B211" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-102-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E211" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B212" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-102-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E212" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B213" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C213" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-102-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E213" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B214" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C214" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-103-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E214" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B215" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-103-10-2, 10m, 2등용, 원2단형</v>
       </c>
       <c r="E215" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B216" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-103-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E216" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B217" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-103-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E217" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B218" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-104-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E218" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B219" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-104-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E219" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B220" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-104-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E220" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B221" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-105-10, 10m, 1등용, 원2단형</v>
       </c>
       <c r="E221" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B222" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-105-10-2, 10m, 2등용, 원2단형</v>
       </c>
       <c r="E222" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B223" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-105-8, 8m, 1등용, 원2단형</v>
       </c>
       <c r="E223" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B224" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-105-9-2, 9m, 2등용, 원2단형</v>
       </c>
       <c r="E224" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B225" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-105-9, 9m, 1등용, 원2단형</v>
       </c>
       <c r="E225" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B226" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-201-4, 4m, 1등용, 원2단형</v>
       </c>
       <c r="E226" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B227" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-201-5, 5m, 1등용, 원2단형</v>
       </c>
       <c r="E227" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B228" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-201-6, 6m, 1등용, 원2단형</v>
       </c>
       <c r="E228" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B229" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-202-4, 4m, 1등용, 원2단형</v>
       </c>
       <c r="E229" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B230" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-202-5, 5m, 1등용, 원2단형</v>
       </c>
       <c r="E230" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B231" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-202-6, 6m, 1등용, 원2단형</v>
       </c>
       <c r="E231" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B232" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-203-4, 4m, 1등용, 원1단형</v>
       </c>
       <c r="E232" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B233" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-203-5-2, 5m, 2등용, 원2단형</v>
       </c>
       <c r="E233" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B234" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-203-5, 5m, 1등용, 원1단형</v>
       </c>
       <c r="E234" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B235" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-203-6, 6m, 1등용, 원1단형</v>
       </c>
       <c r="E235" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B236" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-4-2, 4m, 2등용, 원2단형</v>
       </c>
       <c r="E236" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B237" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-4, 4m, 1등용, 원2단형</v>
       </c>
       <c r="E237" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B238" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-5-2, 5m, 2등용, 원2단형</v>
       </c>
       <c r="E238" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B239" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-5, 5m, 1등용, 원2단형</v>
       </c>
       <c r="E239" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B240" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-6-2, 6m, 2등용, 원2단형</v>
       </c>
       <c r="E240" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B241" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-204-6, 6m, 1등용, 원2단형</v>
       </c>
       <c r="E241" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B242" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">스테인리스가로등주, MTPS-205-65, 6.5m, 1등용, 원2단형</v>
       </c>
       <c r="E242" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B243" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-701, 베이스커버</v>
       </c>
       <c r="E243" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B244" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-702, 배너걸이</v>
       </c>
       <c r="E244" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B245" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-703, 로고판</v>
       </c>
       <c r="E245" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B246" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-704, 암대</v>
       </c>
       <c r="E246" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B247" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-705, 암대</v>
       </c>
       <c r="E247" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B248" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-706, 암대</v>
       </c>
       <c r="E248" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B249" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-707, 암대</v>
       </c>
       <c r="E249" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B250" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">가로등주부속자재, MTPS-708, 암대</v>
       </c>
       <c r="E250" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B251" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-BW, Φ138×68mm, 백색, LED/전지, 점등형</v>
       </c>
       <c r="E251" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B252" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-BY, Φ138×68mm, 황색, LED/전지, 점등형</v>
       </c>
       <c r="E252" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B253" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-HW, Φ138×68mm, 백색, 태양광/LED/전지, 점등형</v>
       </c>
       <c r="E253" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B254" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-HY, Φ138×68mm, 황색, 태양광/LED/전지, 점등형</v>
       </c>
       <c r="E254" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B255" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-SW, Φ138×47mm, 백색, 태양광/LED, 점등형</v>
       </c>
       <c r="E255" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B256" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">도로표지병, MT-RS138-SY, Φ138×47mm, 황색, 태양광/LED, 점등형</v>
       </c>
       <c r="E256" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B257" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" ref="C257:C267" si="4">CONCATENATE(B257,", ",A257,", ",E257)</f>
         <v xml:space="preserve">태양광가로등, MTSOLAR-50A, 50W, 5m</v>
       </c>
       <c r="E257" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B258" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">태양광가로등, MTSOLAR-50B, 50W, 5m</v>
       </c>
       <c r="E258" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B259" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT12B, 12m, 12등용</v>
       </c>
       <c r="E259" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B260" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT15A, 15m, 6등용</v>
       </c>
       <c r="E260" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B261" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT15B, 15m, 12등용</v>
       </c>
       <c r="E261" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B262" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT18A, 18m, 6등용</v>
       </c>
       <c r="E262" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B263" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT18B, 18m, 12등용</v>
       </c>
       <c r="E263" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B264" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT20A, 20m, 10등용</v>
       </c>
       <c r="E264" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B265" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT20B, 20m, 18등용</v>
       </c>
       <c r="E265" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B266" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT24A, 24m, 10등용</v>
       </c>
       <c r="E266" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B267" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="4"/>
         <v xml:space="preserve">조명타워, MTT24B, 24m, 18등용</v>
       </c>
       <c r="E267" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -13160,7 +13171,7 @@
       <c r="C31" s="74"/>
       <c r="D31" s="74"/>
       <c r="E31" s="76" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="F31" s="76"/>
       <c r="G31" s="76"/>
@@ -13172,7 +13183,7 @@
       <c r="C32" s="74"/>
       <c r="D32" s="74"/>
       <c r="E32" s="76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F32" s="76"/>
       <c r="G32" s="76"/>
@@ -13184,7 +13195,7 @@
       <c r="C33" s="74"/>
       <c r="D33" s="74"/>
       <c r="E33" s="76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F33" s="76"/>
       <c r="G33" s="76"/>
@@ -13305,7 +13316,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" style="45" width="10.625"/>
     <col customWidth="1" min="2" max="2" style="45" width="7.25"/>
@@ -13353,7 +13364,7 @@
     </row>
     <row r="5" ht="39" customHeight="1">
       <c r="A5" s="47" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -13400,7 +13411,7 @@
     </row>
     <row r="11" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="49" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B11" s="49"/>
       <c r="C11" s="49"/>
@@ -13434,7 +13445,7 @@
     </row>
     <row r="13" ht="30.75" customHeight="1">
       <c r="A13" s="83" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B13" s="49"/>
       <c r="C13" s="49"/>
@@ -13456,7 +13467,7 @@
     </row>
     <row r="15" s="74" customFormat="1" ht="24.949999999999999" customHeight="1">
       <c r="A15" s="84" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B15" s="84"/>
       <c r="C15" s="84"/>
@@ -13476,46 +13487,46 @@
       <c r="G16" s="49"/>
       <c r="H16" s="49"/>
       <c r="L16" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N16" s="45" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O16" s="45" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P16" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="39.950000000000003" customHeight="1">
       <c r="A17" s="49"/>
       <c r="B17" s="49" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" s="49"/>
-      <c r="D17" s="49" t="str">
+      <c r="D17" s="49" t="e">
         <f>CONCATENATE(VLOOKUP(환경설정!B10,현장대리인계!K17:M19,2,0)," / ",VLOOKUP(환경설정!B10,현장대리인계!K17:M19,3,0))</f>
-        <v xml:space="preserve">최  한  진 / 대 리</v>
+        <v>#N/A</v>
       </c>
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
       <c r="G17" s="49"/>
       <c r="H17" s="49"/>
       <c r="K17" s="45" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L17" s="45" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N17" s="45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O17" s="85">
         <v>32933</v>
@@ -13527,28 +13538,28 @@
     <row r="18" ht="39.950000000000003" customHeight="1">
       <c r="A18" s="49"/>
       <c r="B18" s="49" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C18" s="49"/>
-      <c r="D18" s="49" t="str">
+      <c r="D18" s="49" t="e">
         <f>VLOOKUP(환경설정!B10,현장대리인계!K17:P19,4,0)</f>
-        <v xml:space="preserve">광주광역시 광산구 신창동 1285</v>
+        <v>#N/A</v>
       </c>
       <c r="E18" s="49"/>
       <c r="F18" s="49"/>
       <c r="G18" s="49"/>
       <c r="H18" s="49"/>
       <c r="K18" s="45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" s="45" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M18" s="45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O18" s="85">
         <v>33530</v>
@@ -13560,34 +13571,34 @@
     <row r="19" ht="39.950000000000003" customHeight="1">
       <c r="A19" s="49"/>
       <c r="B19" s="49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C19" s="49"/>
-      <c r="D19" s="49" t="str">
+      <c r="D19" s="49" t="e">
         <f>TEXT(VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,5,0),"yyyy년 mm월 dd일")</f>
-        <v xml:space="preserve">1991년 10월 01일</v>
+        <v>#N/A</v>
       </c>
       <c r="E19" s="49"/>
       <c r="F19" s="49"/>
       <c r="G19" s="49"/>
       <c r="H19" s="49"/>
       <c r="K19" s="45" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="L19" s="45" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="M19" s="45" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N19" s="45" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="O19" s="85">
-        <v>33512</v>
+        <v>37057</v>
       </c>
       <c r="P19" s="86">
-        <v>45433</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="20" ht="24.949999999999999" customHeight="1">
@@ -13622,12 +13633,12 @@
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
-      <c r="E23" s="76" t="s">
+      <c r="E23" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
+      <c r="F23" s="88"/>
+      <c r="G23" s="88"/>
+      <c r="H23" s="88"/>
     </row>
     <row r="24" ht="24.949999999999999" customHeight="1">
       <c r="A24" s="74"/>
@@ -13635,7 +13646,7 @@
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
       <c r="E24" s="76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F24" s="76"/>
       <c r="G24" s="76"/>
@@ -13647,7 +13658,7 @@
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
       <c r="E25" s="76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F25" s="76"/>
       <c r="G25" s="76"/>
@@ -13671,32 +13682,32 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:H9"/>
     <mergeCell ref="C1:H1"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="C3:H3"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="E7:H7"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:H9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:E10"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A12:H12"/>
     <mergeCell ref="J12:K12"/>
     <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="A13:H13"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:G19"/>
     <mergeCell ref="A21:H21"/>
     <mergeCell ref="E23:H23"/>
     <mergeCell ref="E24:H24"/>
     <mergeCell ref="E25:H25"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="D19:G19"/>
   </mergeCells>
   <printOptions headings="0" gridLines="0" horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.39370078740157477" right="0.31496062992125984" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -13759,7 +13770,7 @@
     </row>
     <row r="5" ht="39" customHeight="1">
       <c r="A5" s="47" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B5" s="47"/>
       <c r="C5" s="47"/>
@@ -13782,61 +13793,61 @@
     </row>
     <row r="9" ht="32.100000000000001" customHeight="1">
       <c r="A9" s="49"/>
-      <c r="B9" s="88" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="88"/>
-      <c r="D9" s="89" t="str">
+      <c r="B9" s="89" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="89"/>
+      <c r="D9" s="90" t="e">
         <f>VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,2,0)</f>
-        <v xml:space="preserve">최  한  진</v>
-      </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
       <c r="H9" s="49"/>
     </row>
     <row r="10" ht="32.100000000000001" customHeight="1">
       <c r="A10" s="49"/>
-      <c r="B10" s="88" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="88"/>
-      <c r="D10" s="89" t="str">
+      <c r="B10" s="89" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="89"/>
+      <c r="D10" s="90" t="e">
         <f>TEXT(VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,5,0),"yyyy년 mm월 dd일")</f>
-        <v xml:space="preserve">1991년 10월 01일</v>
-      </c>
-      <c r="E10" s="89"/>
-      <c r="F10" s="89"/>
-      <c r="G10" s="89"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
       <c r="H10" s="49"/>
     </row>
     <row r="11" ht="32.100000000000001" customHeight="1">
       <c r="A11" s="49"/>
-      <c r="B11" s="88" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" s="88"/>
-      <c r="D11" s="89" t="str">
+      <c r="B11" s="89" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="89"/>
+      <c r="D11" s="90" t="e">
         <f>VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,3,0)</f>
-        <v xml:space="preserve">대 리</v>
-      </c>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
       <c r="H11" s="49"/>
     </row>
     <row r="12" ht="32.100000000000001" customHeight="1">
       <c r="A12" s="49"/>
-      <c r="B12" s="88" t="s">
-        <v>104</v>
-      </c>
-      <c r="C12" s="88"/>
-      <c r="D12" s="89" t="s">
-        <v>105</v>
-      </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
-      <c r="G12" s="89"/>
+      <c r="B12" s="89" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="89"/>
+      <c r="D12" s="90" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
       <c r="H12" s="49"/>
       <c r="J12" s="63" t="s">
         <v>66</v>
@@ -13853,93 +13864,93 @@
     </row>
     <row r="13" ht="32.100000000000001" customHeight="1">
       <c r="A13" s="49"/>
-      <c r="B13" s="88" t="s">
-        <v>87</v>
-      </c>
-      <c r="C13" s="88"/>
-      <c r="D13" s="89" t="str">
+      <c r="B13" s="89" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="89"/>
+      <c r="D13" s="90" t="e">
         <f>VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,4,0)</f>
-        <v xml:space="preserve">광주광역시 광산구 신창동 1285</v>
-      </c>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
-      <c r="G13" s="89"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
       <c r="H13" s="49"/>
     </row>
     <row r="14" ht="32.100000000000001" customHeight="1">
       <c r="A14" s="49"/>
-      <c r="B14" s="88" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="88"/>
-      <c r="D14" s="89" t="str">
+      <c r="B14" s="89" t="s">
+        <v>109</v>
+      </c>
+      <c r="C14" s="89"/>
+      <c r="D14" s="90" t="e">
         <f>CONCATENATE(TEXT(VLOOKUP(환경설정!$B$10,재직증명서!$K$16:$P$19,6,0),"yyyy. Mm. dd.")," ~ 현재")</f>
-        <v xml:space="preserve">2024. 05. 21. ~ 현재</v>
-      </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
+        <v>#N/A</v>
+      </c>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
       <c r="H14" s="49"/>
     </row>
     <row r="15" ht="32.100000000000001" customHeight="1">
       <c r="A15" s="49"/>
-      <c r="B15" s="88" t="s">
-        <v>107</v>
-      </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="89" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="89"/>
-      <c r="F15" s="89"/>
-      <c r="G15" s="89"/>
+      <c r="B15" s="89" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" s="89"/>
+      <c r="D15" s="90" t="s">
+        <v>111</v>
+      </c>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
       <c r="H15" s="49"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="49"/>
-      <c r="B16" s="90"/>
-      <c r="C16" s="90"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
       <c r="D16" s="49"/>
       <c r="E16" s="49"/>
       <c r="F16" s="49"/>
       <c r="G16" s="49"/>
       <c r="H16" s="49"/>
       <c r="L16" s="45" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="M16" s="45" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="N16" s="45" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="O16" s="45" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="P16" s="45" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="49"/>
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
+      <c r="B17" s="91"/>
+      <c r="C17" s="91"/>
       <c r="D17" s="49"/>
       <c r="E17" s="49"/>
       <c r="F17" s="49"/>
       <c r="G17" s="49"/>
       <c r="H17" s="49"/>
       <c r="K17" s="45" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="L17" s="45" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="M17" s="45" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="N17" s="45" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="O17" s="85">
         <v>32933</v>
@@ -13950,24 +13961,24 @@
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="49"/>
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="91"/>
       <c r="D18" s="49"/>
       <c r="E18" s="49"/>
       <c r="F18" s="49"/>
       <c r="G18" s="49"/>
       <c r="H18" s="49"/>
       <c r="K18" s="45" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="L18" s="45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="M18" s="45" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N18" s="45" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="O18" s="85">
         <v>33530</v>
@@ -13986,27 +13997,27 @@
       <c r="G19" s="49"/>
       <c r="H19" s="49"/>
       <c r="K19" s="45" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="L19" s="45" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="M19" s="45" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N19" s="45" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="O19" s="85">
-        <v>33512</v>
+        <v>37057</v>
       </c>
       <c r="P19" s="86">
-        <v>45433</v>
+        <v>45474</v>
       </c>
     </row>
     <row r="20" ht="24.949999999999999" customHeight="1">
       <c r="A20" s="49" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B20" s="49"/>
       <c r="C20" s="49"/>
@@ -14017,14 +14028,14 @@
       <c r="H20" s="49"/>
     </row>
     <row r="21" ht="24.949999999999999" customHeight="1">
-      <c r="A21" s="91"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="91"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="92"/>
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
     </row>
     <row r="22" ht="24.949999999999999" customHeight="1">
       <c r="A22" s="87">
@@ -14054,12 +14065,12 @@
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
       <c r="D24" s="74"/>
-      <c r="E24" s="76" t="s">
+      <c r="E24" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
+      <c r="F24" s="88"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="88"/>
     </row>
     <row r="25" ht="24.949999999999999" customHeight="1">
       <c r="A25" s="74"/>
@@ -14067,7 +14078,7 @@
       <c r="C25" s="74"/>
       <c r="D25" s="74"/>
       <c r="E25" s="76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="76"/>
       <c r="G25" s="76"/>
@@ -14079,7 +14090,7 @@
       <c r="C26" s="74"/>
       <c r="D26" s="74"/>
       <c r="E26" s="76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" s="76"/>
       <c r="G26" s="76"/>
